--- a/public/DOST_Performance_Template.xlsx
+++ b/public/DOST_Performance_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\do-performance-monitoring\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{531F0828-69B6-4230-B05F-3192CB97796F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2A74DDB-EA41-4EE1-9F41-6D5EDB96DB43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -438,7 +438,7 @@
     <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@"/>
     <numFmt numFmtId="167" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@"/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="34">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -553,12 +553,6 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -605,23 +599,46 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <color theme="0" tint="-0.34998626667073579"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="0" tint="-0.34998626667073579"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0" tint="-0.34998626667073579"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
+      <color theme="0" tint="-0.34998626667073579"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="0" tint="-0.34998626667073579"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0" tint="-0.34998626667073579"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="8">
@@ -934,7 +951,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="131">
+  <cellXfs count="134">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -990,9 +1007,6 @@
     <xf numFmtId="4" fontId="8" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1022,7 +1036,6 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="8" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1051,7 +1064,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1116,11 +1128,11 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1134,17 +1146,17 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="26" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1153,59 +1165,53 @@
     <xf numFmtId="0" fontId="19" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1221,32 +1227,48 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="167" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1535,12 +1557,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="75.75" customHeight="1">
-      <c r="A1" s="125"/>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
-      <c r="D1" s="106"/>
-      <c r="E1" s="106"/>
-      <c r="F1" s="106"/>
+      <c r="A1" s="90"/>
+      <c r="B1" s="91"/>
+      <c r="C1" s="91"/>
+      <c r="D1" s="91"/>
+      <c r="E1" s="91"/>
+      <c r="F1" s="91"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
@@ -1563,14 +1585,14 @@
       <c r="Z1" s="4"/>
     </row>
     <row r="2" spans="1:26" ht="18">
-      <c r="A2" s="126" t="s">
+      <c r="A2" s="92" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="106"/>
-      <c r="C2" s="106"/>
-      <c r="D2" s="106"/>
-      <c r="E2" s="106"/>
-      <c r="F2" s="106"/>
+      <c r="B2" s="91"/>
+      <c r="C2" s="91"/>
+      <c r="D2" s="91"/>
+      <c r="E2" s="91"/>
+      <c r="F2" s="91"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -1593,14 +1615,14 @@
       <c r="Z2" s="4"/>
     </row>
     <row r="3" spans="1:26" ht="18">
-      <c r="A3" s="126" t="s">
+      <c r="A3" s="92" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="106"/>
-      <c r="C3" s="106"/>
-      <c r="D3" s="106"/>
-      <c r="E3" s="106"/>
-      <c r="F3" s="106"/>
+      <c r="B3" s="91"/>
+      <c r="C3" s="91"/>
+      <c r="D3" s="91"/>
+      <c r="E3" s="91"/>
+      <c r="F3" s="91"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
@@ -1651,22 +1673,22 @@
       <c r="Z4" s="4"/>
     </row>
     <row r="5" spans="1:26" ht="20.399999999999999">
-      <c r="A5" s="127" t="s">
+      <c r="A5" s="93" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="129" t="s">
+      <c r="B5" s="95" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="101"/>
-      <c r="D5" s="101"/>
-      <c r="E5" s="102"/>
-      <c r="F5" s="130" t="s">
+      <c r="C5" s="96"/>
+      <c r="D5" s="96"/>
+      <c r="E5" s="97"/>
+      <c r="F5" s="98" t="s">
         <v>4</v>
       </c>
-      <c r="G5" s="121"/>
-      <c r="H5" s="106"/>
-      <c r="I5" s="106"/>
-      <c r="J5" s="106"/>
+      <c r="G5" s="100"/>
+      <c r="H5" s="91"/>
+      <c r="I5" s="91"/>
+      <c r="J5" s="91"/>
       <c r="K5" s="9"/>
       <c r="L5" s="10"/>
       <c r="M5" s="4"/>
@@ -1685,7 +1707,7 @@
       <c r="Z5" s="4"/>
     </row>
     <row r="6" spans="1:26" ht="21" customHeight="1">
-      <c r="A6" s="128"/>
+      <c r="A6" s="94"/>
       <c r="B6" s="11" t="s">
         <v>5</v>
       </c>
@@ -1698,11 +1720,11 @@
       <c r="E6" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="128"/>
-      <c r="G6" s="106"/>
-      <c r="H6" s="106"/>
-      <c r="I6" s="106"/>
-      <c r="J6" s="106"/>
+      <c r="F6" s="94"/>
+      <c r="G6" s="91"/>
+      <c r="H6" s="91"/>
+      <c r="I6" s="91"/>
+      <c r="J6" s="91"/>
       <c r="K6" s="9"/>
       <c r="L6" s="10"/>
       <c r="M6" s="4"/>
@@ -1721,14 +1743,14 @@
       <c r="Z6" s="4"/>
     </row>
     <row r="7" spans="1:26" ht="21" customHeight="1">
-      <c r="A7" s="109" t="s">
+      <c r="A7" s="101" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="101"/>
-      <c r="C7" s="101"/>
-      <c r="D7" s="101"/>
-      <c r="E7" s="101"/>
-      <c r="F7" s="102"/>
+      <c r="B7" s="96"/>
+      <c r="C7" s="96"/>
+      <c r="D7" s="96"/>
+      <c r="E7" s="96"/>
+      <c r="F7" s="97"/>
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
@@ -1751,14 +1773,14 @@
       <c r="Z7" s="4"/>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A8" s="122" t="s">
+      <c r="A8" s="102" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="123"/>
-      <c r="C8" s="123"/>
-      <c r="D8" s="123"/>
-      <c r="E8" s="123"/>
-      <c r="F8" s="124"/>
+      <c r="B8" s="103"/>
+      <c r="C8" s="103"/>
+      <c r="D8" s="103"/>
+      <c r="E8" s="103"/>
+      <c r="F8" s="104"/>
       <c r="G8" s="8"/>
       <c r="H8" s="8"/>
       <c r="I8" s="8"/>
@@ -1781,14 +1803,14 @@
       <c r="Z8" s="4"/>
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A9" s="110" t="s">
+      <c r="A9" s="105" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="101"/>
-      <c r="C9" s="101"/>
-      <c r="D9" s="101"/>
-      <c r="E9" s="101"/>
-      <c r="F9" s="102"/>
+      <c r="B9" s="96"/>
+      <c r="C9" s="96"/>
+      <c r="D9" s="96"/>
+      <c r="E9" s="96"/>
+      <c r="F9" s="97"/>
       <c r="G9" s="8"/>
       <c r="H9" s="8"/>
       <c r="I9" s="8"/>
@@ -1811,14 +1833,14 @@
       <c r="Z9" s="4"/>
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A10" s="120" t="s">
+      <c r="A10" s="99" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="101"/>
-      <c r="C10" s="101"/>
-      <c r="D10" s="101"/>
-      <c r="E10" s="101"/>
-      <c r="F10" s="102"/>
+      <c r="B10" s="96"/>
+      <c r="C10" s="96"/>
+      <c r="D10" s="96"/>
+      <c r="E10" s="96"/>
+      <c r="F10" s="97"/>
       <c r="G10" s="8"/>
       <c r="H10" s="8"/>
       <c r="I10" s="8"/>
@@ -1849,10 +1871,10 @@
       <c r="D11" s="14"/>
       <c r="E11" s="14"/>
       <c r="F11" s="15"/>
-      <c r="G11" s="92" t="s">
+      <c r="G11" s="121" t="s">
         <v>121</v>
       </c>
-      <c r="H11" s="8"/>
+      <c r="H11" s="122"/>
       <c r="I11" s="8"/>
       <c r="J11" s="12"/>
       <c r="K11" s="9"/>
@@ -1881,10 +1903,10 @@
       <c r="D12" s="17"/>
       <c r="E12" s="17"/>
       <c r="F12" s="18"/>
-      <c r="G12" s="92" t="s">
+      <c r="G12" s="121" t="s">
         <v>113</v>
       </c>
-      <c r="H12" s="8"/>
+      <c r="H12" s="122"/>
       <c r="I12" s="8"/>
       <c r="J12" s="12"/>
       <c r="K12" s="9"/>
@@ -1913,10 +1935,10 @@
       <c r="D13" s="19"/>
       <c r="E13" s="19"/>
       <c r="F13" s="18"/>
-      <c r="G13" s="92" t="s">
+      <c r="G13" s="121" t="s">
         <v>114</v>
       </c>
-      <c r="H13" s="8"/>
+      <c r="H13" s="122"/>
       <c r="I13" s="8"/>
       <c r="J13" s="12"/>
       <c r="K13" s="9"/>
@@ -1945,10 +1967,10 @@
       <c r="D14" s="14"/>
       <c r="E14" s="14"/>
       <c r="F14" s="18"/>
-      <c r="G14" s="92" t="s">
+      <c r="G14" s="121" t="s">
         <v>121</v>
       </c>
-      <c r="H14" s="8"/>
+      <c r="H14" s="122"/>
       <c r="I14" s="8"/>
       <c r="J14" s="12"/>
       <c r="K14" s="9"/>
@@ -1977,10 +1999,10 @@
       <c r="D15" s="21"/>
       <c r="E15" s="20"/>
       <c r="F15" s="18"/>
-      <c r="G15" s="92" t="s">
+      <c r="G15" s="121" t="s">
         <v>115</v>
       </c>
-      <c r="H15" s="8"/>
+      <c r="H15" s="122"/>
       <c r="I15" s="8"/>
       <c r="J15" s="12"/>
       <c r="K15" s="9"/>
@@ -2009,10 +2031,10 @@
       <c r="D16" s="22"/>
       <c r="E16" s="22"/>
       <c r="F16" s="18"/>
-      <c r="G16" s="92" t="s">
+      <c r="G16" s="121" t="s">
         <v>116</v>
       </c>
-      <c r="H16" s="23"/>
+      <c r="H16" s="123"/>
       <c r="I16" s="8"/>
       <c r="J16" s="12"/>
       <c r="K16" s="9"/>
@@ -2033,18 +2055,18 @@
       <c r="Z16" s="4"/>
     </row>
     <row r="17" spans="1:26" ht="21">
-      <c r="A17" s="24" t="s">
+      <c r="A17" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="25"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25"/>
+      <c r="B17" s="24"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="24"/>
       <c r="F17" s="18"/>
-      <c r="G17" s="92" t="s">
+      <c r="G17" s="121" t="s">
         <v>121</v>
       </c>
-      <c r="H17" s="8"/>
+      <c r="H17" s="122"/>
       <c r="I17" s="8"/>
       <c r="J17" s="12"/>
       <c r="K17" s="9"/>
@@ -2065,22 +2087,22 @@
       <c r="Z17" s="4"/>
     </row>
     <row r="18" spans="1:26" ht="30.75" customHeight="1">
-      <c r="A18" s="26" t="s">
+      <c r="A18" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="27"/>
-      <c r="C18" s="27"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="27"/>
+      <c r="B18" s="26"/>
+      <c r="C18" s="26"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="26"/>
       <c r="F18" s="18"/>
-      <c r="G18" s="92" t="s">
+      <c r="G18" s="121" t="s">
         <v>119</v>
       </c>
-      <c r="H18" s="8"/>
-      <c r="I18" s="28"/>
-      <c r="J18" s="28"/>
-      <c r="K18" s="29"/>
-      <c r="L18" s="30"/>
+      <c r="H18" s="122"/>
+      <c r="I18" s="27"/>
+      <c r="J18" s="27"/>
+      <c r="K18" s="28"/>
+      <c r="L18" s="29"/>
       <c r="M18" s="4"/>
       <c r="N18" s="4"/>
       <c r="O18" s="4"/>
@@ -2097,22 +2119,22 @@
       <c r="Z18" s="4"/>
     </row>
     <row r="19" spans="1:26" ht="35.25" customHeight="1">
-      <c r="A19" s="26" t="s">
+      <c r="A19" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="27"/>
-      <c r="C19" s="27"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="27"/>
+      <c r="B19" s="26"/>
+      <c r="C19" s="26"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="26"/>
       <c r="F19" s="18"/>
-      <c r="G19" s="92" t="s">
+      <c r="G19" s="121" t="s">
         <v>117</v>
       </c>
-      <c r="H19" s="8"/>
-      <c r="I19" s="28"/>
-      <c r="J19" s="28"/>
-      <c r="K19" s="29"/>
-      <c r="L19" s="30"/>
+      <c r="H19" s="122"/>
+      <c r="I19" s="27"/>
+      <c r="J19" s="27"/>
+      <c r="K19" s="28"/>
+      <c r="L19" s="29"/>
       <c r="M19" s="4"/>
       <c r="N19" s="4"/>
       <c r="O19" s="4"/>
@@ -2129,21 +2151,21 @@
       <c r="Z19" s="4"/>
     </row>
     <row r="20" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A20" s="31" t="s">
+      <c r="A20" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="27"/>
-      <c r="C20" s="27"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="27"/>
+      <c r="B20" s="26"/>
+      <c r="C20" s="26"/>
+      <c r="D20" s="26"/>
+      <c r="E20" s="26"/>
       <c r="F20" s="18"/>
-      <c r="G20" s="92" t="s">
+      <c r="G20" s="121" t="s">
         <v>118</v>
       </c>
-      <c r="H20" s="32"/>
-      <c r="I20" s="32"/>
-      <c r="J20" s="33"/>
-      <c r="K20" s="34"/>
+      <c r="H20" s="124"/>
+      <c r="I20" s="31"/>
+      <c r="J20" s="32"/>
+      <c r="K20" s="33"/>
       <c r="L20" s="10"/>
       <c r="M20" s="4"/>
       <c r="N20" s="4"/>
@@ -2161,18 +2183,18 @@
       <c r="Z20" s="4"/>
     </row>
     <row r="21" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A21" s="24" t="s">
+      <c r="A21" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="35"/>
-      <c r="C21" s="35"/>
-      <c r="D21" s="35"/>
-      <c r="E21" s="35"/>
+      <c r="B21" s="34"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="34"/>
       <c r="F21" s="18"/>
-      <c r="G21" s="92" t="s">
+      <c r="G21" s="121" t="s">
         <v>120</v>
       </c>
-      <c r="H21" s="37"/>
+      <c r="H21" s="125"/>
       <c r="I21" s="1"/>
       <c r="J21" s="2"/>
       <c r="K21" s="3"/>
@@ -2193,18 +2215,18 @@
       <c r="Z21" s="4"/>
     </row>
     <row r="22" spans="1:26" ht="26.25" customHeight="1">
-      <c r="A22" s="24" t="s">
+      <c r="A22" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="38"/>
-      <c r="C22" s="38"/>
-      <c r="D22" s="38"/>
-      <c r="E22" s="38"/>
+      <c r="B22" s="36"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="36"/>
       <c r="F22" s="18"/>
-      <c r="G22" s="92" t="s">
+      <c r="G22" s="121" t="s">
         <v>22</v>
       </c>
-      <c r="H22" s="1"/>
+      <c r="H22" s="126"/>
       <c r="I22" s="1"/>
       <c r="J22" s="2"/>
       <c r="K22" s="3"/>
@@ -2225,18 +2247,18 @@
       <c r="Z22" s="4"/>
     </row>
     <row r="23" spans="1:26" ht="21" customHeight="1">
-      <c r="A23" s="39" t="s">
+      <c r="A23" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="38"/>
-      <c r="C23" s="38"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
+      <c r="B23" s="36"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="36"/>
+      <c r="E23" s="36"/>
       <c r="F23" s="18"/>
-      <c r="G23" s="92" t="s">
+      <c r="G23" s="121" t="s">
         <v>23</v>
       </c>
-      <c r="H23" s="1"/>
+      <c r="H23" s="126"/>
       <c r="I23" s="1"/>
       <c r="J23" s="2"/>
       <c r="K23" s="3"/>
@@ -2257,18 +2279,18 @@
       <c r="Z23" s="4"/>
     </row>
     <row r="24" spans="1:26" ht="26.25" customHeight="1">
-      <c r="A24" s="24" t="s">
+      <c r="A24" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="38"/>
-      <c r="C24" s="38"/>
-      <c r="D24" s="38"/>
-      <c r="E24" s="40"/>
-      <c r="F24" s="41"/>
-      <c r="G24" s="92" t="s">
+      <c r="B24" s="36"/>
+      <c r="C24" s="36"/>
+      <c r="D24" s="36"/>
+      <c r="E24" s="38"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="121" t="s">
         <v>24</v>
       </c>
-      <c r="H24" s="1"/>
+      <c r="H24" s="126"/>
       <c r="I24" s="1"/>
       <c r="J24" s="2"/>
       <c r="K24" s="3"/>
@@ -2289,18 +2311,18 @@
       <c r="Z24" s="4"/>
     </row>
     <row r="25" spans="1:26" ht="26.25" customHeight="1">
-      <c r="A25" s="24" t="s">
+      <c r="A25" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="B25" s="38"/>
-      <c r="C25" s="38"/>
-      <c r="D25" s="38"/>
-      <c r="E25" s="40"/>
-      <c r="F25" s="41"/>
-      <c r="G25" s="92" t="s">
+      <c r="B25" s="36"/>
+      <c r="C25" s="36"/>
+      <c r="D25" s="36"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="39"/>
+      <c r="G25" s="121" t="s">
         <v>25</v>
       </c>
-      <c r="H25" s="1"/>
+      <c r="H25" s="126"/>
       <c r="I25" s="1"/>
       <c r="J25" s="2"/>
       <c r="K25" s="3"/>
@@ -2321,18 +2343,18 @@
       <c r="Z25" s="4"/>
     </row>
     <row r="26" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A26" s="120" t="s">
+      <c r="A26" s="99" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="101"/>
-      <c r="C26" s="101"/>
-      <c r="D26" s="101"/>
-      <c r="E26" s="101"/>
-      <c r="F26" s="102"/>
-      <c r="G26" s="92" t="s">
+      <c r="B26" s="96"/>
+      <c r="C26" s="96"/>
+      <c r="D26" s="96"/>
+      <c r="E26" s="96"/>
+      <c r="F26" s="97"/>
+      <c r="G26" s="121" t="s">
         <v>121</v>
       </c>
-      <c r="H26" s="1"/>
+      <c r="H26" s="126"/>
       <c r="I26" s="1"/>
       <c r="J26" s="2"/>
       <c r="K26" s="3"/>
@@ -2353,18 +2375,18 @@
       <c r="Z26" s="4"/>
     </row>
     <row r="27" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A27" s="42" t="s">
+      <c r="A27" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="B27" s="43"/>
-      <c r="C27" s="43"/>
-      <c r="D27" s="43"/>
-      <c r="E27" s="43"/>
-      <c r="F27" s="44"/>
-      <c r="G27" s="92" t="s">
+      <c r="B27" s="41"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="41"/>
+      <c r="E27" s="41"/>
+      <c r="F27" s="42"/>
+      <c r="G27" s="121" t="s">
         <v>121</v>
       </c>
-      <c r="H27" s="1"/>
+      <c r="H27" s="126"/>
       <c r="I27" s="1"/>
       <c r="J27" s="2"/>
       <c r="K27" s="3"/>
@@ -2385,20 +2407,20 @@
       <c r="Z27" s="4"/>
     </row>
     <row r="28" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A28" s="42" t="s">
+      <c r="A28" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="35"/>
-      <c r="C28" s="35"/>
-      <c r="D28" s="35"/>
-      <c r="E28" s="35"/>
+      <c r="B28" s="34"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="34"/>
       <c r="F28" s="18"/>
-      <c r="G28" s="92" t="s">
+      <c r="G28" s="121" t="s">
         <v>28</v>
       </c>
-      <c r="H28" s="1"/>
+      <c r="H28" s="126"/>
       <c r="I28" s="1"/>
-      <c r="J28" s="45"/>
+      <c r="J28" s="43"/>
       <c r="K28" s="3"/>
       <c r="L28" s="4"/>
       <c r="M28" s="4"/>
@@ -2417,19 +2439,19 @@
       <c r="Z28" s="4"/>
     </row>
     <row r="29" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A29" s="42" t="s">
+      <c r="A29" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="B29" s="35"/>
-      <c r="C29" s="35"/>
-      <c r="D29" s="35"/>
-      <c r="E29" s="35"/>
+      <c r="B29" s="34"/>
+      <c r="C29" s="34"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="34"/>
       <c r="F29" s="18"/>
-      <c r="G29" s="92" t="s">
+      <c r="G29" s="121" t="s">
         <v>122</v>
       </c>
-      <c r="H29" s="1"/>
-      <c r="I29" s="36"/>
+      <c r="H29" s="126"/>
+      <c r="I29" s="35"/>
       <c r="J29" s="2"/>
       <c r="K29" s="3"/>
       <c r="L29" s="4"/>
@@ -2449,18 +2471,18 @@
       <c r="Z29" s="4"/>
     </row>
     <row r="30" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A30" s="42" t="s">
+      <c r="A30" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="B30" s="35"/>
-      <c r="C30" s="35"/>
-      <c r="D30" s="35"/>
-      <c r="E30" s="35"/>
+      <c r="B30" s="34"/>
+      <c r="C30" s="34"/>
+      <c r="D30" s="34"/>
+      <c r="E30" s="34"/>
       <c r="F30" s="18"/>
-      <c r="G30" s="92" t="s">
+      <c r="G30" s="121" t="s">
         <v>30</v>
       </c>
-      <c r="H30" s="1"/>
+      <c r="H30" s="126"/>
       <c r="I30" s="1"/>
       <c r="J30" s="2"/>
       <c r="K30" s="3"/>
@@ -2481,18 +2503,18 @@
       <c r="Z30" s="4"/>
     </row>
     <row r="31" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A31" s="42" t="s">
+      <c r="A31" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="B31" s="46"/>
-      <c r="C31" s="46"/>
-      <c r="D31" s="46"/>
-      <c r="E31" s="46"/>
+      <c r="B31" s="44"/>
+      <c r="C31" s="44"/>
+      <c r="D31" s="44"/>
+      <c r="E31" s="44"/>
       <c r="F31" s="18"/>
-      <c r="G31" s="92" t="s">
+      <c r="G31" s="121" t="s">
         <v>121</v>
       </c>
-      <c r="H31" s="1"/>
+      <c r="H31" s="126"/>
       <c r="I31" s="1"/>
       <c r="J31" s="2"/>
       <c r="K31" s="3"/>
@@ -2513,18 +2535,18 @@
       <c r="Z31" s="4"/>
     </row>
     <row r="32" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A32" s="42" t="s">
+      <c r="A32" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="B32" s="35"/>
-      <c r="C32" s="35"/>
-      <c r="D32" s="35"/>
-      <c r="E32" s="35"/>
+      <c r="B32" s="34"/>
+      <c r="C32" s="34"/>
+      <c r="D32" s="34"/>
+      <c r="E32" s="34"/>
       <c r="F32" s="18"/>
-      <c r="G32" s="92" t="s">
+      <c r="G32" s="121" t="s">
         <v>32</v>
       </c>
-      <c r="H32" s="1"/>
+      <c r="H32" s="126"/>
       <c r="I32" s="1"/>
       <c r="J32" s="2"/>
       <c r="K32" s="3"/>
@@ -2545,18 +2567,18 @@
       <c r="Z32" s="4"/>
     </row>
     <row r="33" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A33" s="42" t="s">
+      <c r="A33" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="B33" s="35"/>
-      <c r="C33" s="35"/>
-      <c r="D33" s="35"/>
-      <c r="E33" s="35"/>
+      <c r="B33" s="34"/>
+      <c r="C33" s="34"/>
+      <c r="D33" s="34"/>
+      <c r="E33" s="34"/>
       <c r="F33" s="18"/>
-      <c r="G33" s="92" t="s">
+      <c r="G33" s="121" t="s">
         <v>123</v>
       </c>
-      <c r="H33" s="1"/>
+      <c r="H33" s="126"/>
       <c r="I33" s="1"/>
       <c r="J33" s="2"/>
       <c r="K33" s="3"/>
@@ -2577,18 +2599,18 @@
       <c r="Z33" s="4"/>
     </row>
     <row r="34" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A34" s="42" t="s">
+      <c r="A34" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="B34" s="35"/>
-      <c r="C34" s="35"/>
-      <c r="D34" s="35"/>
-      <c r="E34" s="35"/>
+      <c r="B34" s="34"/>
+      <c r="C34" s="34"/>
+      <c r="D34" s="34"/>
+      <c r="E34" s="34"/>
       <c r="F34" s="18"/>
-      <c r="G34" s="92" t="s">
+      <c r="G34" s="121" t="s">
         <v>33</v>
       </c>
-      <c r="H34" s="1"/>
+      <c r="H34" s="126"/>
       <c r="I34" s="1"/>
       <c r="J34" s="2"/>
       <c r="K34" s="3"/>
@@ -2609,18 +2631,18 @@
       <c r="Z34" s="4"/>
     </row>
     <row r="35" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A35" s="120" t="s">
+      <c r="A35" s="99" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="101"/>
-      <c r="C35" s="101"/>
-      <c r="D35" s="101"/>
-      <c r="E35" s="101"/>
-      <c r="F35" s="102"/>
-      <c r="G35" s="92" t="s">
+      <c r="B35" s="96"/>
+      <c r="C35" s="96"/>
+      <c r="D35" s="96"/>
+      <c r="E35" s="96"/>
+      <c r="F35" s="97"/>
+      <c r="G35" s="121" t="s">
         <v>121</v>
       </c>
-      <c r="H35" s="1"/>
+      <c r="H35" s="126"/>
       <c r="I35" s="1"/>
       <c r="J35" s="2"/>
       <c r="K35" s="3"/>
@@ -2641,18 +2663,18 @@
       <c r="Z35" s="4"/>
     </row>
     <row r="36" spans="1:26" ht="28.5" customHeight="1">
-      <c r="A36" s="26" t="s">
+      <c r="A36" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="B36" s="47"/>
-      <c r="C36" s="47"/>
-      <c r="D36" s="47"/>
-      <c r="E36" s="47"/>
-      <c r="F36" s="44"/>
-      <c r="G36" s="92" t="s">
+      <c r="B36" s="45"/>
+      <c r="C36" s="45"/>
+      <c r="D36" s="45"/>
+      <c r="E36" s="45"/>
+      <c r="F36" s="42"/>
+      <c r="G36" s="121" t="s">
         <v>35</v>
       </c>
-      <c r="H36" s="1"/>
+      <c r="H36" s="126"/>
       <c r="I36" s="1"/>
       <c r="J36" s="2"/>
       <c r="K36" s="3"/>
@@ -2673,18 +2695,18 @@
       <c r="Z36" s="4"/>
     </row>
     <row r="37" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A37" s="90" t="s">
+      <c r="A37" s="87" t="s">
         <v>36</v>
       </c>
-      <c r="B37" s="47"/>
-      <c r="C37" s="47"/>
-      <c r="D37" s="47"/>
-      <c r="E37" s="47"/>
-      <c r="F37" s="88"/>
-      <c r="G37" s="92" t="s">
+      <c r="B37" s="45"/>
+      <c r="C37" s="45"/>
+      <c r="D37" s="45"/>
+      <c r="E37" s="45"/>
+      <c r="F37" s="85"/>
+      <c r="G37" s="121" t="s">
         <v>36</v>
       </c>
-      <c r="H37" s="1"/>
+      <c r="H37" s="126"/>
       <c r="I37" s="1"/>
       <c r="J37" s="2"/>
       <c r="K37" s="3"/>
@@ -2705,18 +2727,18 @@
       <c r="Z37" s="4"/>
     </row>
     <row r="38" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A38" s="42" t="s">
+      <c r="A38" s="40" t="s">
         <v>37</v>
       </c>
-      <c r="B38" s="47"/>
-      <c r="C38" s="47"/>
-      <c r="D38" s="47"/>
-      <c r="E38" s="47"/>
-      <c r="F38" s="88"/>
-      <c r="G38" s="92" t="s">
+      <c r="B38" s="45"/>
+      <c r="C38" s="45"/>
+      <c r="D38" s="45"/>
+      <c r="E38" s="45"/>
+      <c r="F38" s="85"/>
+      <c r="G38" s="121" t="s">
         <v>37</v>
       </c>
-      <c r="H38" s="1"/>
+      <c r="H38" s="126"/>
       <c r="I38" s="1"/>
       <c r="J38" s="2"/>
       <c r="K38" s="3"/>
@@ -2737,18 +2759,18 @@
       <c r="Z38" s="4"/>
     </row>
     <row r="39" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A39" s="42" t="s">
+      <c r="A39" s="40" t="s">
         <v>38</v>
       </c>
-      <c r="B39" s="47"/>
-      <c r="C39" s="47"/>
-      <c r="D39" s="47"/>
-      <c r="E39" s="47"/>
-      <c r="F39" s="88"/>
-      <c r="G39" s="92" t="s">
+      <c r="B39" s="45"/>
+      <c r="C39" s="45"/>
+      <c r="D39" s="45"/>
+      <c r="E39" s="45"/>
+      <c r="F39" s="85"/>
+      <c r="G39" s="121" t="s">
         <v>38</v>
       </c>
-      <c r="H39" s="1"/>
+      <c r="H39" s="126"/>
       <c r="I39" s="1"/>
       <c r="J39" s="2"/>
       <c r="K39" s="3"/>
@@ -2769,18 +2791,18 @@
       <c r="Z39" s="4"/>
     </row>
     <row r="40" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A40" s="90" t="s">
+      <c r="A40" s="87" t="s">
         <v>39</v>
       </c>
-      <c r="B40" s="47"/>
-      <c r="C40" s="47"/>
-      <c r="D40" s="47"/>
-      <c r="E40" s="47"/>
-      <c r="F40" s="88"/>
-      <c r="G40" s="92" t="s">
+      <c r="B40" s="45"/>
+      <c r="C40" s="45"/>
+      <c r="D40" s="45"/>
+      <c r="E40" s="45"/>
+      <c r="F40" s="85"/>
+      <c r="G40" s="121" t="s">
         <v>39</v>
       </c>
-      <c r="H40" s="1"/>
+      <c r="H40" s="126"/>
       <c r="I40" s="1"/>
       <c r="J40" s="2"/>
       <c r="K40" s="3"/>
@@ -2801,18 +2823,18 @@
       <c r="Z40" s="4"/>
     </row>
     <row r="41" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A41" s="90" t="s">
+      <c r="A41" s="87" t="s">
         <v>40</v>
       </c>
-      <c r="B41" s="47"/>
-      <c r="C41" s="47"/>
-      <c r="D41" s="47"/>
-      <c r="E41" s="47"/>
-      <c r="F41" s="88"/>
-      <c r="G41" s="92" t="s">
+      <c r="B41" s="45"/>
+      <c r="C41" s="45"/>
+      <c r="D41" s="45"/>
+      <c r="E41" s="45"/>
+      <c r="F41" s="85"/>
+      <c r="G41" s="121" t="s">
         <v>40</v>
       </c>
-      <c r="H41" s="1"/>
+      <c r="H41" s="126"/>
       <c r="I41" s="1"/>
       <c r="J41" s="2"/>
       <c r="K41" s="3"/>
@@ -2833,18 +2855,18 @@
       <c r="Z41" s="4"/>
     </row>
     <row r="42" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A42" s="90" t="s">
+      <c r="A42" s="87" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="84"/>
-      <c r="C42" s="84"/>
-      <c r="D42" s="84"/>
-      <c r="E42" s="84"/>
-      <c r="F42" s="89"/>
-      <c r="G42" s="92" t="s">
+      <c r="B42" s="81"/>
+      <c r="C42" s="81"/>
+      <c r="D42" s="81"/>
+      <c r="E42" s="81"/>
+      <c r="F42" s="86"/>
+      <c r="G42" s="121" t="s">
         <v>41</v>
       </c>
-      <c r="H42" s="1"/>
+      <c r="H42" s="126"/>
       <c r="I42" s="1"/>
       <c r="J42" s="2"/>
       <c r="K42" s="3"/>
@@ -2865,18 +2887,18 @@
       <c r="Z42" s="4"/>
     </row>
     <row r="43" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A43" s="90" t="s">
+      <c r="A43" s="87" t="s">
         <v>42</v>
       </c>
-      <c r="B43" s="84"/>
-      <c r="C43" s="84"/>
-      <c r="D43" s="84"/>
-      <c r="E43" s="84"/>
-      <c r="F43" s="89"/>
-      <c r="G43" s="92" t="s">
+      <c r="B43" s="81"/>
+      <c r="C43" s="81"/>
+      <c r="D43" s="81"/>
+      <c r="E43" s="81"/>
+      <c r="F43" s="86"/>
+      <c r="G43" s="121" t="s">
         <v>42</v>
       </c>
-      <c r="H43" s="48"/>
+      <c r="H43" s="127"/>
       <c r="I43" s="1"/>
       <c r="J43" s="2"/>
       <c r="K43" s="3"/>
@@ -2897,18 +2919,18 @@
       <c r="Z43" s="4"/>
     </row>
     <row r="44" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A44" s="90" t="s">
+      <c r="A44" s="87" t="s">
         <v>43</v>
       </c>
-      <c r="B44" s="84"/>
-      <c r="C44" s="84"/>
-      <c r="D44" s="84"/>
-      <c r="E44" s="84"/>
-      <c r="F44" s="89"/>
-      <c r="G44" s="93" t="s">
+      <c r="B44" s="81"/>
+      <c r="C44" s="81"/>
+      <c r="D44" s="81"/>
+      <c r="E44" s="81"/>
+      <c r="F44" s="86"/>
+      <c r="G44" s="128" t="s">
         <v>43</v>
       </c>
-      <c r="H44" s="1"/>
+      <c r="H44" s="126"/>
       <c r="I44" s="1"/>
       <c r="J44" s="2"/>
       <c r="K44" s="3"/>
@@ -2929,18 +2951,18 @@
       <c r="Z44" s="4"/>
     </row>
     <row r="45" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A45" s="90" t="s">
+      <c r="A45" s="87" t="s">
         <v>44</v>
       </c>
-      <c r="B45" s="84"/>
-      <c r="C45" s="84"/>
-      <c r="D45" s="84"/>
-      <c r="E45" s="84"/>
-      <c r="F45" s="89"/>
-      <c r="G45" s="92" t="s">
+      <c r="B45" s="81"/>
+      <c r="C45" s="81"/>
+      <c r="D45" s="81"/>
+      <c r="E45" s="81"/>
+      <c r="F45" s="86"/>
+      <c r="G45" s="121" t="s">
         <v>44</v>
       </c>
-      <c r="H45" s="48"/>
+      <c r="H45" s="127"/>
       <c r="I45" s="1"/>
       <c r="J45" s="2"/>
       <c r="K45" s="3"/>
@@ -2961,18 +2983,18 @@
       <c r="Z45" s="4"/>
     </row>
     <row r="46" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A46" s="90" t="s">
+      <c r="A46" s="87" t="s">
         <v>45</v>
       </c>
-      <c r="B46" s="47"/>
-      <c r="C46" s="47"/>
-      <c r="D46" s="47"/>
-      <c r="E46" s="47"/>
-      <c r="F46" s="88"/>
-      <c r="G46" s="92" t="s">
+      <c r="B46" s="45"/>
+      <c r="C46" s="45"/>
+      <c r="D46" s="45"/>
+      <c r="E46" s="45"/>
+      <c r="F46" s="85"/>
+      <c r="G46" s="121" t="s">
         <v>45</v>
       </c>
-      <c r="H46" s="1"/>
+      <c r="H46" s="126"/>
       <c r="I46" s="1"/>
       <c r="J46" s="2"/>
       <c r="K46" s="3"/>
@@ -2993,18 +3015,18 @@
       <c r="Z46" s="4"/>
     </row>
     <row r="47" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A47" s="120" t="s">
+      <c r="A47" s="99" t="s">
         <v>46</v>
       </c>
-      <c r="B47" s="101"/>
-      <c r="C47" s="101"/>
-      <c r="D47" s="101"/>
-      <c r="E47" s="101"/>
-      <c r="F47" s="102"/>
-      <c r="G47" s="92" t="s">
+      <c r="B47" s="96"/>
+      <c r="C47" s="96"/>
+      <c r="D47" s="96"/>
+      <c r="E47" s="96"/>
+      <c r="F47" s="97"/>
+      <c r="G47" s="121" t="s">
         <v>121</v>
       </c>
-      <c r="H47" s="1"/>
+      <c r="H47" s="126"/>
       <c r="I47" s="1"/>
       <c r="J47" s="2"/>
       <c r="K47" s="3"/>
@@ -3025,18 +3047,18 @@
       <c r="Z47" s="4"/>
     </row>
     <row r="48" spans="1:26" ht="33" customHeight="1">
-      <c r="A48" s="91" t="s">
+      <c r="A48" s="88" t="s">
         <v>47</v>
       </c>
-      <c r="B48" s="47"/>
-      <c r="C48" s="47"/>
-      <c r="D48" s="47"/>
-      <c r="E48" s="47"/>
-      <c r="F48" s="50"/>
-      <c r="G48" s="92" t="s">
+      <c r="B48" s="45"/>
+      <c r="C48" s="45"/>
+      <c r="D48" s="45"/>
+      <c r="E48" s="45"/>
+      <c r="F48" s="47"/>
+      <c r="G48" s="121" t="s">
         <v>47</v>
       </c>
-      <c r="H48" s="1"/>
+      <c r="H48" s="126"/>
       <c r="I48" s="1"/>
       <c r="J48" s="2"/>
       <c r="K48" s="3"/>
@@ -3057,18 +3079,18 @@
       <c r="Z48" s="4"/>
     </row>
     <row r="49" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A49" s="90" t="s">
+      <c r="A49" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="B49" s="47"/>
-      <c r="C49" s="47"/>
-      <c r="D49" s="47"/>
-      <c r="E49" s="47"/>
-      <c r="F49" s="50"/>
-      <c r="G49" s="92" t="s">
+      <c r="B49" s="45"/>
+      <c r="C49" s="45"/>
+      <c r="D49" s="45"/>
+      <c r="E49" s="45"/>
+      <c r="F49" s="47"/>
+      <c r="G49" s="121" t="s">
         <v>48</v>
       </c>
-      <c r="H49" s="1"/>
+      <c r="H49" s="126"/>
       <c r="I49" s="1"/>
       <c r="J49" s="2"/>
       <c r="K49" s="3"/>
@@ -3089,18 +3111,18 @@
       <c r="Z49" s="4"/>
     </row>
     <row r="50" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A50" s="120" t="s">
+      <c r="A50" s="99" t="s">
         <v>49</v>
       </c>
-      <c r="B50" s="101"/>
-      <c r="C50" s="101"/>
-      <c r="D50" s="101"/>
-      <c r="E50" s="101"/>
-      <c r="F50" s="102"/>
-      <c r="G50" s="92" t="s">
+      <c r="B50" s="96"/>
+      <c r="C50" s="96"/>
+      <c r="D50" s="96"/>
+      <c r="E50" s="96"/>
+      <c r="F50" s="97"/>
+      <c r="G50" s="121" t="s">
         <v>121</v>
       </c>
-      <c r="H50" s="1"/>
+      <c r="H50" s="126"/>
       <c r="I50" s="1"/>
       <c r="J50" s="2"/>
       <c r="K50" s="3"/>
@@ -3121,18 +3143,18 @@
       <c r="Z50" s="4"/>
     </row>
     <row r="51" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A51" s="90" t="s">
+      <c r="A51" s="87" t="s">
         <v>50</v>
       </c>
-      <c r="B51" s="35"/>
-      <c r="C51" s="35"/>
-      <c r="D51" s="35"/>
-      <c r="E51" s="35"/>
+      <c r="B51" s="34"/>
+      <c r="C51" s="34"/>
+      <c r="D51" s="34"/>
+      <c r="E51" s="34"/>
       <c r="F51" s="18"/>
-      <c r="G51" s="92" t="s">
+      <c r="G51" s="121" t="s">
         <v>50</v>
       </c>
-      <c r="H51" s="1"/>
+      <c r="H51" s="126"/>
       <c r="I51" s="1"/>
       <c r="J51" s="2"/>
       <c r="K51" s="3"/>
@@ -3153,18 +3175,18 @@
       <c r="Z51" s="4"/>
     </row>
     <row r="52" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A52" s="90" t="s">
+      <c r="A52" s="87" t="s">
         <v>51</v>
       </c>
-      <c r="B52" s="35"/>
-      <c r="C52" s="35"/>
-      <c r="D52" s="35"/>
-      <c r="E52" s="35"/>
+      <c r="B52" s="34"/>
+      <c r="C52" s="34"/>
+      <c r="D52" s="34"/>
+      <c r="E52" s="34"/>
       <c r="F52" s="18"/>
-      <c r="G52" s="93" t="s">
+      <c r="G52" s="128" t="s">
         <v>51</v>
       </c>
-      <c r="H52" s="1"/>
+      <c r="H52" s="126"/>
       <c r="I52" s="1"/>
       <c r="J52" s="2"/>
       <c r="K52" s="3"/>
@@ -3185,16 +3207,16 @@
       <c r="Z52" s="4"/>
     </row>
     <row r="53" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A53" s="100" t="s">
+      <c r="A53" s="106" t="s">
         <v>52</v>
       </c>
-      <c r="B53" s="101"/>
-      <c r="C53" s="101"/>
-      <c r="D53" s="101"/>
-      <c r="E53" s="101"/>
-      <c r="F53" s="102"/>
-      <c r="G53" s="97"/>
-      <c r="H53" s="1"/>
+      <c r="B53" s="96"/>
+      <c r="C53" s="96"/>
+      <c r="D53" s="96"/>
+      <c r="E53" s="96"/>
+      <c r="F53" s="97"/>
+      <c r="G53" s="129"/>
+      <c r="H53" s="126"/>
       <c r="I53" s="1"/>
       <c r="J53" s="2"/>
       <c r="K53" s="3"/>
@@ -3218,15 +3240,15 @@
       <c r="A54" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="B54" s="35"/>
-      <c r="C54" s="40"/>
-      <c r="D54" s="35"/>
-      <c r="E54" s="40"/>
-      <c r="F54" s="51"/>
-      <c r="G54" s="97" t="s">
+      <c r="B54" s="34"/>
+      <c r="C54" s="38"/>
+      <c r="D54" s="34"/>
+      <c r="E54" s="38"/>
+      <c r="F54" s="48"/>
+      <c r="G54" s="129" t="s">
         <v>53</v>
       </c>
-      <c r="H54" s="1"/>
+      <c r="H54" s="126"/>
       <c r="I54" s="1"/>
       <c r="J54" s="2"/>
       <c r="K54" s="3"/>
@@ -3247,18 +3269,18 @@
       <c r="Z54" s="4"/>
     </row>
     <row r="55" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A55" s="52" t="s">
+      <c r="A55" s="49" t="s">
         <v>54</v>
       </c>
-      <c r="B55" s="35"/>
-      <c r="C55" s="40"/>
-      <c r="D55" s="35"/>
-      <c r="E55" s="40"/>
-      <c r="F55" s="51"/>
-      <c r="G55" s="97" t="s">
+      <c r="B55" s="34"/>
+      <c r="C55" s="38"/>
+      <c r="D55" s="34"/>
+      <c r="E55" s="38"/>
+      <c r="F55" s="48"/>
+      <c r="G55" s="129" t="s">
         <v>54</v>
       </c>
-      <c r="H55" s="94"/>
+      <c r="H55" s="130"/>
       <c r="I55" s="1"/>
       <c r="J55" s="2"/>
       <c r="K55" s="3"/>
@@ -3279,18 +3301,18 @@
       <c r="Z55" s="4"/>
     </row>
     <row r="56" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A56" s="52" t="s">
+      <c r="A56" s="49" t="s">
         <v>55</v>
       </c>
-      <c r="B56" s="35"/>
-      <c r="C56" s="53"/>
-      <c r="D56" s="35"/>
-      <c r="E56" s="53"/>
-      <c r="F56" s="54"/>
-      <c r="G56" s="97" t="s">
+      <c r="B56" s="34"/>
+      <c r="C56" s="50"/>
+      <c r="D56" s="34"/>
+      <c r="E56" s="50"/>
+      <c r="F56" s="51"/>
+      <c r="G56" s="129" t="s">
         <v>55</v>
       </c>
-      <c r="H56" s="95"/>
+      <c r="H56" s="131"/>
       <c r="I56" s="1"/>
       <c r="J56" s="2"/>
       <c r="K56" s="3"/>
@@ -3311,18 +3333,18 @@
       <c r="Z56" s="4"/>
     </row>
     <row r="57" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A57" s="52" t="s">
+      <c r="A57" s="49" t="s">
         <v>56</v>
       </c>
-      <c r="B57" s="35"/>
-      <c r="C57" s="40"/>
-      <c r="D57" s="35"/>
-      <c r="E57" s="40"/>
-      <c r="F57" s="51"/>
-      <c r="G57" s="97" t="s">
+      <c r="B57" s="34"/>
+      <c r="C57" s="38"/>
+      <c r="D57" s="34"/>
+      <c r="E57" s="38"/>
+      <c r="F57" s="48"/>
+      <c r="G57" s="129" t="s">
         <v>56</v>
       </c>
-      <c r="H57" s="1"/>
+      <c r="H57" s="126"/>
       <c r="I57" s="1"/>
       <c r="J57" s="2"/>
       <c r="K57" s="3"/>
@@ -3343,18 +3365,18 @@
       <c r="Z57" s="4"/>
     </row>
     <row r="58" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A58" s="52" t="s">
+      <c r="A58" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="B58" s="35"/>
-      <c r="C58" s="40"/>
-      <c r="D58" s="35"/>
-      <c r="E58" s="40"/>
-      <c r="F58" s="51"/>
-      <c r="G58" s="97" t="s">
+      <c r="B58" s="34"/>
+      <c r="C58" s="38"/>
+      <c r="D58" s="34"/>
+      <c r="E58" s="38"/>
+      <c r="F58" s="48"/>
+      <c r="G58" s="129" t="s">
         <v>57</v>
       </c>
-      <c r="H58" s="1"/>
+      <c r="H58" s="126"/>
       <c r="I58" s="1"/>
       <c r="J58" s="2"/>
       <c r="K58" s="3"/>
@@ -3375,18 +3397,18 @@
       <c r="Z58" s="4"/>
     </row>
     <row r="59" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A59" s="52" t="s">
+      <c r="A59" s="49" t="s">
         <v>58</v>
       </c>
-      <c r="B59" s="35"/>
-      <c r="C59" s="40"/>
-      <c r="D59" s="35"/>
-      <c r="E59" s="40"/>
-      <c r="F59" s="51"/>
-      <c r="G59" s="97" t="s">
+      <c r="B59" s="34"/>
+      <c r="C59" s="38"/>
+      <c r="D59" s="34"/>
+      <c r="E59" s="38"/>
+      <c r="F59" s="48"/>
+      <c r="G59" s="129" t="s">
         <v>58</v>
       </c>
-      <c r="H59" s="1"/>
+      <c r="H59" s="126"/>
       <c r="I59" s="1"/>
       <c r="J59" s="2"/>
       <c r="K59" s="3"/>
@@ -3407,18 +3429,18 @@
       <c r="Z59" s="4"/>
     </row>
     <row r="60" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A60" s="55" t="s">
+      <c r="A60" s="52" t="s">
         <v>59</v>
       </c>
-      <c r="B60" s="27"/>
-      <c r="C60" s="27"/>
-      <c r="D60" s="27"/>
-      <c r="E60" s="27"/>
+      <c r="B60" s="26"/>
+      <c r="C60" s="26"/>
+      <c r="D60" s="26"/>
+      <c r="E60" s="26"/>
       <c r="F60" s="18"/>
-      <c r="G60" s="97" t="s">
+      <c r="G60" s="129" t="s">
         <v>59</v>
       </c>
-      <c r="H60" s="1"/>
+      <c r="H60" s="126"/>
       <c r="I60" s="1"/>
       <c r="J60" s="2"/>
       <c r="K60" s="3"/>
@@ -3439,18 +3461,18 @@
       <c r="Z60" s="4"/>
     </row>
     <row r="61" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A61" s="55" t="s">
+      <c r="A61" s="52" t="s">
         <v>60</v>
       </c>
-      <c r="B61" s="27"/>
-      <c r="C61" s="27"/>
-      <c r="D61" s="27"/>
-      <c r="E61" s="27"/>
+      <c r="B61" s="26"/>
+      <c r="C61" s="26"/>
+      <c r="D61" s="26"/>
+      <c r="E61" s="26"/>
       <c r="F61" s="18"/>
-      <c r="G61" s="97" t="s">
+      <c r="G61" s="129" t="s">
         <v>60</v>
       </c>
-      <c r="H61" s="1"/>
+      <c r="H61" s="126"/>
       <c r="I61" s="1"/>
       <c r="J61" s="2"/>
       <c r="K61" s="3"/>
@@ -3471,18 +3493,18 @@
       <c r="Z61" s="4"/>
     </row>
     <row r="62" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A62" s="55" t="s">
+      <c r="A62" s="52" t="s">
         <v>61</v>
       </c>
-      <c r="B62" s="27"/>
-      <c r="C62" s="27"/>
-      <c r="D62" s="27"/>
-      <c r="E62" s="27"/>
+      <c r="B62" s="26"/>
+      <c r="C62" s="26"/>
+      <c r="D62" s="26"/>
+      <c r="E62" s="26"/>
       <c r="F62" s="18"/>
-      <c r="G62" s="97" t="s">
+      <c r="G62" s="129" t="s">
         <v>61</v>
       </c>
-      <c r="H62" s="1"/>
+      <c r="H62" s="126"/>
       <c r="I62" s="1"/>
       <c r="J62" s="2"/>
       <c r="K62" s="3"/>
@@ -3503,18 +3525,18 @@
       <c r="Z62" s="4"/>
     </row>
     <row r="63" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A63" s="55" t="s">
+      <c r="A63" s="52" t="s">
         <v>62</v>
       </c>
-      <c r="B63" s="27"/>
-      <c r="C63" s="56"/>
-      <c r="D63" s="27"/>
-      <c r="E63" s="56"/>
-      <c r="F63" s="41"/>
-      <c r="G63" s="97" t="s">
+      <c r="B63" s="26"/>
+      <c r="C63" s="53"/>
+      <c r="D63" s="26"/>
+      <c r="E63" s="53"/>
+      <c r="F63" s="39"/>
+      <c r="G63" s="129" t="s">
         <v>62</v>
       </c>
-      <c r="H63" s="1"/>
+      <c r="H63" s="126"/>
       <c r="I63" s="1"/>
       <c r="J63" s="2"/>
       <c r="K63" s="3"/>
@@ -3535,18 +3557,18 @@
       <c r="Z63" s="4"/>
     </row>
     <row r="64" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A64" s="55" t="s">
+      <c r="A64" s="52" t="s">
         <v>63</v>
       </c>
-      <c r="B64" s="27"/>
-      <c r="C64" s="56"/>
-      <c r="D64" s="27"/>
-      <c r="E64" s="56"/>
-      <c r="F64" s="41"/>
-      <c r="G64" s="97" t="s">
+      <c r="B64" s="26"/>
+      <c r="C64" s="53"/>
+      <c r="D64" s="26"/>
+      <c r="E64" s="53"/>
+      <c r="F64" s="39"/>
+      <c r="G64" s="129" t="s">
         <v>63</v>
       </c>
-      <c r="H64" s="1"/>
+      <c r="H64" s="126"/>
       <c r="I64" s="1"/>
       <c r="J64" s="2"/>
       <c r="K64" s="3"/>
@@ -3567,18 +3589,18 @@
       <c r="Z64" s="4"/>
     </row>
     <row r="65" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A65" s="55" t="s">
+      <c r="A65" s="52" t="s">
         <v>64</v>
       </c>
-      <c r="B65" s="27"/>
-      <c r="C65" s="27"/>
-      <c r="D65" s="27"/>
-      <c r="E65" s="27"/>
+      <c r="B65" s="26"/>
+      <c r="C65" s="26"/>
+      <c r="D65" s="26"/>
+      <c r="E65" s="26"/>
       <c r="F65" s="18"/>
-      <c r="G65" s="97" t="s">
+      <c r="G65" s="129" t="s">
         <v>64</v>
       </c>
-      <c r="H65" s="1"/>
+      <c r="H65" s="126"/>
       <c r="I65" s="1"/>
       <c r="J65" s="2"/>
       <c r="K65" s="3"/>
@@ -3599,16 +3621,16 @@
       <c r="Z65" s="4"/>
     </row>
     <row r="66" spans="1:26" ht="18" customHeight="1">
-      <c r="A66" s="112" t="s">
+      <c r="A66" s="107" t="s">
         <v>65</v>
       </c>
-      <c r="B66" s="113"/>
-      <c r="C66" s="113"/>
-      <c r="D66" s="113"/>
-      <c r="E66" s="113"/>
-      <c r="F66" s="114"/>
-      <c r="G66" s="98"/>
-      <c r="H66" s="1"/>
+      <c r="B66" s="108"/>
+      <c r="C66" s="108"/>
+      <c r="D66" s="108"/>
+      <c r="E66" s="108"/>
+      <c r="F66" s="109"/>
+      <c r="G66" s="132"/>
+      <c r="H66" s="126"/>
       <c r="I66" s="1"/>
       <c r="J66" s="2"/>
       <c r="K66" s="3"/>
@@ -3629,16 +3651,16 @@
       <c r="Z66" s="4"/>
     </row>
     <row r="67" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A67" s="110" t="s">
+      <c r="A67" s="105" t="s">
         <v>11</v>
       </c>
-      <c r="B67" s="101"/>
-      <c r="C67" s="101"/>
-      <c r="D67" s="101"/>
-      <c r="E67" s="101"/>
-      <c r="F67" s="102"/>
-      <c r="G67" s="98"/>
-      <c r="H67" s="1"/>
+      <c r="B67" s="96"/>
+      <c r="C67" s="96"/>
+      <c r="D67" s="96"/>
+      <c r="E67" s="96"/>
+      <c r="F67" s="97"/>
+      <c r="G67" s="132"/>
+      <c r="H67" s="126"/>
       <c r="I67" s="1"/>
       <c r="J67" s="2"/>
       <c r="K67" s="3"/>
@@ -3659,18 +3681,18 @@
       <c r="Z67" s="4"/>
     </row>
     <row r="68" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A68" s="24" t="s">
+      <c r="A68" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="B68" s="57"/>
-      <c r="C68" s="57"/>
-      <c r="D68" s="57"/>
-      <c r="E68" s="57"/>
-      <c r="F68" s="58"/>
-      <c r="G68" s="96" t="s">
+      <c r="B68" s="54"/>
+      <c r="C68" s="54"/>
+      <c r="D68" s="54"/>
+      <c r="E68" s="54"/>
+      <c r="F68" s="55"/>
+      <c r="G68" s="133" t="s">
         <v>121</v>
       </c>
-      <c r="H68" s="1"/>
+      <c r="H68" s="126"/>
       <c r="I68" s="1"/>
       <c r="J68" s="2"/>
       <c r="K68" s="3"/>
@@ -3691,18 +3713,18 @@
       <c r="Z68" s="4"/>
     </row>
     <row r="69" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A69" s="42" t="s">
+      <c r="A69" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="B69" s="59"/>
-      <c r="C69" s="59"/>
-      <c r="D69" s="59"/>
-      <c r="E69" s="59"/>
-      <c r="F69" s="58"/>
-      <c r="G69" s="97" t="s">
+      <c r="B69" s="56"/>
+      <c r="C69" s="56"/>
+      <c r="D69" s="56"/>
+      <c r="E69" s="56"/>
+      <c r="F69" s="55"/>
+      <c r="G69" s="129" t="s">
         <v>128</v>
       </c>
-      <c r="H69" s="95"/>
+      <c r="H69" s="131"/>
       <c r="I69" s="1"/>
       <c r="J69" s="2"/>
       <c r="K69" s="3"/>
@@ -3723,18 +3745,18 @@
       <c r="Z69" s="4"/>
     </row>
     <row r="70" spans="1:26" ht="20.25" customHeight="1">
-      <c r="A70" s="26" t="s">
+      <c r="A70" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="B70" s="60"/>
-      <c r="C70" s="60"/>
-      <c r="D70" s="60"/>
-      <c r="E70" s="60"/>
-      <c r="F70" s="58"/>
-      <c r="G70" s="97" t="s">
+      <c r="B70" s="57"/>
+      <c r="C70" s="57"/>
+      <c r="D70" s="57"/>
+      <c r="E70" s="57"/>
+      <c r="F70" s="55"/>
+      <c r="G70" s="129" t="s">
         <v>129</v>
       </c>
-      <c r="H70" s="95"/>
+      <c r="H70" s="131"/>
       <c r="I70" s="1"/>
       <c r="J70" s="2"/>
       <c r="K70" s="3"/>
@@ -3755,18 +3777,18 @@
       <c r="Z70" s="4"/>
     </row>
     <row r="71" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A71" s="39" t="s">
+      <c r="A71" s="37" t="s">
         <v>69</v>
       </c>
-      <c r="B71" s="61"/>
-      <c r="C71" s="61"/>
-      <c r="D71" s="61"/>
-      <c r="E71" s="61"/>
-      <c r="F71" s="62"/>
-      <c r="G71" s="97" t="s">
+      <c r="B71" s="58"/>
+      <c r="C71" s="58"/>
+      <c r="D71" s="58"/>
+      <c r="E71" s="58"/>
+      <c r="F71" s="59"/>
+      <c r="G71" s="129" t="s">
         <v>69</v>
       </c>
-      <c r="H71" s="95"/>
+      <c r="H71" s="131"/>
       <c r="I71" s="1"/>
       <c r="J71" s="2"/>
       <c r="K71" s="3"/>
@@ -3787,18 +3809,18 @@
       <c r="Z71" s="4"/>
     </row>
     <row r="72" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A72" s="115" t="s">
+      <c r="A72" s="110" t="s">
         <v>70</v>
       </c>
-      <c r="B72" s="106"/>
-      <c r="C72" s="106"/>
-      <c r="D72" s="106"/>
-      <c r="E72" s="106"/>
-      <c r="F72" s="116"/>
-      <c r="G72" s="97" t="s">
+      <c r="B72" s="91"/>
+      <c r="C72" s="91"/>
+      <c r="D72" s="91"/>
+      <c r="E72" s="91"/>
+      <c r="F72" s="111"/>
+      <c r="G72" s="129" t="s">
         <v>121</v>
       </c>
-      <c r="H72" s="95"/>
+      <c r="H72" s="131"/>
       <c r="I72" s="1"/>
       <c r="J72" s="2"/>
       <c r="K72" s="3"/>
@@ -3819,18 +3841,18 @@
       <c r="Z72" s="4"/>
     </row>
     <row r="73" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A73" s="42" t="s">
+      <c r="A73" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="B73" s="63"/>
-      <c r="C73" s="63"/>
-      <c r="D73" s="63"/>
-      <c r="E73" s="63"/>
-      <c r="F73" s="62"/>
-      <c r="G73" s="97" t="s">
+      <c r="B73" s="60"/>
+      <c r="C73" s="60"/>
+      <c r="D73" s="60"/>
+      <c r="E73" s="60"/>
+      <c r="F73" s="59"/>
+      <c r="G73" s="129" t="s">
         <v>71</v>
       </c>
-      <c r="H73" s="95"/>
+      <c r="H73" s="131"/>
       <c r="I73" s="1"/>
       <c r="J73" s="2"/>
       <c r="K73" s="3"/>
@@ -3851,18 +3873,18 @@
       <c r="Z73" s="4"/>
     </row>
     <row r="74" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A74" s="49" t="s">
+      <c r="A74" s="46" t="s">
         <v>72</v>
       </c>
-      <c r="B74" s="47"/>
-      <c r="C74" s="47"/>
-      <c r="D74" s="47"/>
-      <c r="E74" s="47"/>
-      <c r="F74" s="62"/>
-      <c r="G74" s="97" t="s">
+      <c r="B74" s="45"/>
+      <c r="C74" s="45"/>
+      <c r="D74" s="45"/>
+      <c r="E74" s="45"/>
+      <c r="F74" s="59"/>
+      <c r="G74" s="129" t="s">
         <v>72</v>
       </c>
-      <c r="H74" s="95"/>
+      <c r="H74" s="131"/>
       <c r="I74" s="1"/>
       <c r="J74" s="2"/>
       <c r="K74" s="3"/>
@@ -3883,18 +3905,18 @@
       <c r="Z74" s="4"/>
     </row>
     <row r="75" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A75" s="26" t="s">
+      <c r="A75" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="B75" s="47"/>
-      <c r="C75" s="47"/>
-      <c r="D75" s="47"/>
-      <c r="E75" s="47"/>
-      <c r="F75" s="62"/>
-      <c r="G75" s="97" t="s">
+      <c r="B75" s="45"/>
+      <c r="C75" s="45"/>
+      <c r="D75" s="45"/>
+      <c r="E75" s="45"/>
+      <c r="F75" s="59"/>
+      <c r="G75" s="129" t="s">
         <v>73</v>
       </c>
-      <c r="H75" s="95"/>
+      <c r="H75" s="131"/>
       <c r="I75" s="1"/>
       <c r="J75" s="2"/>
       <c r="K75" s="3"/>
@@ -3915,18 +3937,18 @@
       <c r="Z75" s="4"/>
     </row>
     <row r="76" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A76" s="26" t="s">
+      <c r="A76" s="25" t="s">
         <v>74</v>
       </c>
-      <c r="B76" s="47"/>
-      <c r="C76" s="47"/>
-      <c r="D76" s="47"/>
-      <c r="E76" s="47"/>
-      <c r="F76" s="62"/>
-      <c r="G76" s="97" t="s">
+      <c r="B76" s="45"/>
+      <c r="C76" s="45"/>
+      <c r="D76" s="45"/>
+      <c r="E76" s="45"/>
+      <c r="F76" s="59"/>
+      <c r="G76" s="129" t="s">
         <v>74</v>
       </c>
-      <c r="H76" s="95"/>
+      <c r="H76" s="131"/>
       <c r="I76" s="1"/>
       <c r="J76" s="2"/>
       <c r="K76" s="3"/>
@@ -3947,18 +3969,18 @@
       <c r="Z76" s="4"/>
     </row>
     <row r="77" spans="1:26" ht="28.5" customHeight="1">
-      <c r="A77" s="26" t="s">
+      <c r="A77" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="B77" s="47"/>
-      <c r="C77" s="47"/>
-      <c r="D77" s="47"/>
-      <c r="E77" s="47"/>
-      <c r="F77" s="62"/>
-      <c r="G77" s="97" t="s">
+      <c r="B77" s="45"/>
+      <c r="C77" s="45"/>
+      <c r="D77" s="45"/>
+      <c r="E77" s="45"/>
+      <c r="F77" s="59"/>
+      <c r="G77" s="129" t="s">
         <v>75</v>
       </c>
-      <c r="H77" s="95"/>
+      <c r="H77" s="131"/>
       <c r="I77" s="1"/>
       <c r="J77" s="2"/>
       <c r="K77" s="3"/>
@@ -3979,18 +4001,18 @@
       <c r="Z77" s="4"/>
     </row>
     <row r="78" spans="1:26" ht="28.5" customHeight="1">
-      <c r="A78" s="26" t="s">
+      <c r="A78" s="25" t="s">
         <v>76</v>
       </c>
-      <c r="B78" s="47"/>
-      <c r="C78" s="47"/>
-      <c r="D78" s="40"/>
-      <c r="E78" s="40"/>
-      <c r="F78" s="41"/>
-      <c r="G78" s="97" t="s">
+      <c r="B78" s="45"/>
+      <c r="C78" s="45"/>
+      <c r="D78" s="38"/>
+      <c r="E78" s="38"/>
+      <c r="F78" s="39"/>
+      <c r="G78" s="129" t="s">
         <v>76</v>
       </c>
-      <c r="H78" s="95"/>
+      <c r="H78" s="131"/>
       <c r="I78" s="1"/>
       <c r="J78" s="2"/>
       <c r="K78" s="3"/>
@@ -4011,18 +4033,18 @@
       <c r="Z78" s="4"/>
     </row>
     <row r="79" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A79" s="117" t="s">
+      <c r="A79" s="112" t="s">
         <v>77</v>
       </c>
-      <c r="B79" s="118"/>
-      <c r="C79" s="118"/>
-      <c r="D79" s="118"/>
-      <c r="E79" s="118"/>
-      <c r="F79" s="119"/>
-      <c r="G79" s="95" t="s">
+      <c r="B79" s="113"/>
+      <c r="C79" s="113"/>
+      <c r="D79" s="113"/>
+      <c r="E79" s="113"/>
+      <c r="F79" s="114"/>
+      <c r="G79" s="131" t="s">
         <v>121</v>
       </c>
-      <c r="H79" s="95"/>
+      <c r="H79" s="131"/>
       <c r="I79" s="1"/>
       <c r="J79" s="2"/>
       <c r="K79" s="3"/>
@@ -4043,18 +4065,18 @@
       <c r="Z79" s="4"/>
     </row>
     <row r="80" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A80" s="42" t="s">
+      <c r="A80" s="40" t="s">
         <v>78</v>
       </c>
-      <c r="B80" s="53"/>
-      <c r="C80" s="53"/>
-      <c r="D80" s="53"/>
-      <c r="E80" s="53"/>
+      <c r="B80" s="50"/>
+      <c r="C80" s="50"/>
+      <c r="D80" s="50"/>
+      <c r="E80" s="50"/>
       <c r="F80" s="15"/>
-      <c r="G80" s="95" t="s">
+      <c r="G80" s="131" t="s">
         <v>78</v>
       </c>
-      <c r="H80" s="95"/>
+      <c r="H80" s="131"/>
       <c r="I80" s="1"/>
       <c r="J80" s="2"/>
       <c r="K80" s="3"/>
@@ -4075,18 +4097,18 @@
       <c r="Z80" s="4"/>
     </row>
     <row r="81" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A81" s="42" t="s">
+      <c r="A81" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="B81" s="53"/>
-      <c r="C81" s="53"/>
-      <c r="D81" s="53"/>
-      <c r="E81" s="53"/>
+      <c r="B81" s="50"/>
+      <c r="C81" s="50"/>
+      <c r="D81" s="50"/>
+      <c r="E81" s="50"/>
       <c r="F81" s="15"/>
-      <c r="G81" s="95" t="s">
+      <c r="G81" s="131" t="s">
         <v>79</v>
       </c>
-      <c r="H81" s="95"/>
+      <c r="H81" s="131"/>
       <c r="I81" s="1"/>
       <c r="J81" s="2"/>
       <c r="K81" s="3"/>
@@ -4107,18 +4129,18 @@
       <c r="Z81" s="4"/>
     </row>
     <row r="82" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A82" s="42" t="s">
+      <c r="A82" s="40" t="s">
         <v>80</v>
       </c>
-      <c r="B82" s="53"/>
-      <c r="C82" s="53"/>
-      <c r="D82" s="53"/>
-      <c r="E82" s="53"/>
+      <c r="B82" s="50"/>
+      <c r="C82" s="50"/>
+      <c r="D82" s="50"/>
+      <c r="E82" s="50"/>
       <c r="F82" s="15"/>
-      <c r="G82" s="95" t="s">
+      <c r="G82" s="131" t="s">
         <v>80</v>
       </c>
-      <c r="H82" s="95"/>
+      <c r="H82" s="131"/>
       <c r="I82" s="1"/>
       <c r="J82" s="2"/>
       <c r="K82" s="3"/>
@@ -4139,18 +4161,18 @@
       <c r="Z82" s="4"/>
     </row>
     <row r="83" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A83" s="108" t="s">
+      <c r="A83" s="119" t="s">
         <v>81</v>
       </c>
-      <c r="B83" s="101"/>
-      <c r="C83" s="101"/>
-      <c r="D83" s="101"/>
-      <c r="E83" s="101"/>
-      <c r="F83" s="102"/>
-      <c r="G83" s="95" t="s">
+      <c r="B83" s="96"/>
+      <c r="C83" s="96"/>
+      <c r="D83" s="96"/>
+      <c r="E83" s="96"/>
+      <c r="F83" s="97"/>
+      <c r="G83" s="131" t="s">
         <v>121</v>
       </c>
-      <c r="H83" s="95"/>
+      <c r="H83" s="131"/>
       <c r="I83" s="1"/>
       <c r="J83" s="2"/>
       <c r="K83" s="3"/>
@@ -4171,18 +4193,18 @@
       <c r="Z83" s="4"/>
     </row>
     <row r="84" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A84" s="42" t="s">
+      <c r="A84" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="B84" s="35"/>
-      <c r="C84" s="35"/>
-      <c r="D84" s="35"/>
-      <c r="E84" s="35"/>
+      <c r="B84" s="34"/>
+      <c r="C84" s="34"/>
+      <c r="D84" s="34"/>
+      <c r="E84" s="34"/>
       <c r="F84" s="18"/>
-      <c r="G84" s="95" t="s">
+      <c r="G84" s="131" t="s">
         <v>126</v>
       </c>
-      <c r="H84" s="95"/>
+      <c r="H84" s="131"/>
       <c r="I84" s="1"/>
       <c r="J84" s="2"/>
       <c r="K84" s="3"/>
@@ -4203,18 +4225,18 @@
       <c r="Z84" s="4"/>
     </row>
     <row r="85" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A85" s="42" t="s">
+      <c r="A85" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="B85" s="64"/>
-      <c r="C85" s="64"/>
-      <c r="D85" s="64"/>
-      <c r="E85" s="64"/>
+      <c r="B85" s="61"/>
+      <c r="C85" s="61"/>
+      <c r="D85" s="61"/>
+      <c r="E85" s="61"/>
       <c r="F85" s="18"/>
-      <c r="G85" s="95" t="s">
+      <c r="G85" s="131" t="s">
         <v>121</v>
       </c>
-      <c r="H85" s="95"/>
+      <c r="H85" s="131"/>
       <c r="I85" s="1"/>
       <c r="J85" s="2"/>
       <c r="K85" s="3"/>
@@ -4235,18 +4257,18 @@
       <c r="Z85" s="4"/>
     </row>
     <row r="86" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A86" s="42" t="s">
+      <c r="A86" s="40" t="s">
         <v>84</v>
       </c>
-      <c r="B86" s="35"/>
-      <c r="C86" s="35"/>
-      <c r="D86" s="35"/>
-      <c r="E86" s="35"/>
+      <c r="B86" s="34"/>
+      <c r="C86" s="34"/>
+      <c r="D86" s="34"/>
+      <c r="E86" s="34"/>
       <c r="F86" s="18"/>
-      <c r="G86" s="95" t="s">
+      <c r="G86" s="131" t="s">
         <v>127</v>
       </c>
-      <c r="H86" s="95"/>
+      <c r="H86" s="131"/>
       <c r="I86" s="1"/>
       <c r="J86" s="2"/>
       <c r="K86" s="3"/>
@@ -4267,18 +4289,18 @@
       <c r="Z86" s="4"/>
     </row>
     <row r="87" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A87" s="26" t="s">
+      <c r="A87" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="B87" s="35"/>
-      <c r="C87" s="35"/>
-      <c r="D87" s="35"/>
-      <c r="E87" s="35"/>
+      <c r="B87" s="34"/>
+      <c r="C87" s="34"/>
+      <c r="D87" s="34"/>
+      <c r="E87" s="34"/>
       <c r="F87" s="18"/>
-      <c r="G87" s="95" t="s">
+      <c r="G87" s="131" t="s">
         <v>125</v>
       </c>
-      <c r="H87" s="95"/>
+      <c r="H87" s="131"/>
       <c r="I87" s="1"/>
       <c r="J87" s="2"/>
       <c r="K87" s="3"/>
@@ -4299,18 +4321,18 @@
       <c r="Z87" s="4"/>
     </row>
     <row r="88" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A88" s="42" t="s">
+      <c r="A88" s="40" t="s">
         <v>86</v>
       </c>
-      <c r="B88" s="64"/>
-      <c r="C88" s="64"/>
-      <c r="D88" s="64"/>
-      <c r="E88" s="64"/>
+      <c r="B88" s="61"/>
+      <c r="C88" s="61"/>
+      <c r="D88" s="61"/>
+      <c r="E88" s="61"/>
       <c r="F88" s="18"/>
-      <c r="G88" s="95" t="s">
+      <c r="G88" s="131" t="s">
         <v>121</v>
       </c>
-      <c r="H88" s="95"/>
+      <c r="H88" s="131"/>
       <c r="I88" s="1"/>
       <c r="J88" s="2"/>
       <c r="K88" s="3"/>
@@ -4331,18 +4353,18 @@
       <c r="Z88" s="4"/>
     </row>
     <row r="89" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A89" s="42" t="s">
+      <c r="A89" s="40" t="s">
         <v>84</v>
       </c>
-      <c r="B89" s="35"/>
-      <c r="C89" s="35"/>
-      <c r="D89" s="35"/>
-      <c r="E89" s="35"/>
+      <c r="B89" s="34"/>
+      <c r="C89" s="34"/>
+      <c r="D89" s="34"/>
+      <c r="E89" s="34"/>
       <c r="F89" s="18"/>
-      <c r="G89" s="95" t="s">
+      <c r="G89" s="131" t="s">
         <v>124</v>
       </c>
-      <c r="H89" s="95"/>
+      <c r="H89" s="131"/>
       <c r="I89" s="1"/>
       <c r="J89" s="2"/>
       <c r="K89" s="3"/>
@@ -4363,18 +4385,18 @@
       <c r="Z89" s="4"/>
     </row>
     <row r="90" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A90" s="26" t="s">
+      <c r="A90" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="B90" s="35"/>
-      <c r="C90" s="35"/>
-      <c r="D90" s="35"/>
-      <c r="E90" s="35"/>
+      <c r="B90" s="34"/>
+      <c r="C90" s="34"/>
+      <c r="D90" s="34"/>
+      <c r="E90" s="34"/>
       <c r="F90" s="18"/>
-      <c r="G90" s="95" t="s">
+      <c r="G90" s="131" t="s">
         <v>124</v>
       </c>
-      <c r="H90" s="95"/>
+      <c r="H90" s="131"/>
       <c r="I90" s="1"/>
       <c r="J90" s="2"/>
       <c r="K90" s="3"/>
@@ -4395,16 +4417,16 @@
       <c r="Z90" s="4"/>
     </row>
     <row r="91" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A91" s="100" t="s">
+      <c r="A91" s="106" t="s">
         <v>52</v>
       </c>
-      <c r="B91" s="101"/>
-      <c r="C91" s="101"/>
-      <c r="D91" s="101"/>
-      <c r="E91" s="101"/>
-      <c r="F91" s="102"/>
-      <c r="G91" s="1"/>
-      <c r="H91" s="1"/>
+      <c r="B91" s="96"/>
+      <c r="C91" s="96"/>
+      <c r="D91" s="96"/>
+      <c r="E91" s="96"/>
+      <c r="F91" s="97"/>
+      <c r="G91" s="126"/>
+      <c r="H91" s="126"/>
       <c r="I91" s="1"/>
       <c r="J91" s="2"/>
       <c r="K91" s="3"/>
@@ -4428,15 +4450,15 @@
       <c r="A92" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="B92" s="35"/>
-      <c r="C92" s="40"/>
-      <c r="D92" s="35"/>
-      <c r="E92" s="40"/>
-      <c r="F92" s="40"/>
-      <c r="G92" s="97" t="s">
+      <c r="B92" s="34"/>
+      <c r="C92" s="38"/>
+      <c r="D92" s="34"/>
+      <c r="E92" s="38"/>
+      <c r="F92" s="38"/>
+      <c r="G92" s="129" t="s">
         <v>88</v>
       </c>
-      <c r="H92" s="97"/>
+      <c r="H92" s="129"/>
       <c r="I92" s="1"/>
       <c r="J92" s="2"/>
       <c r="K92" s="3"/>
@@ -4460,15 +4482,15 @@
       <c r="A93" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="B93" s="35"/>
-      <c r="C93" s="35"/>
-      <c r="D93" s="35"/>
-      <c r="E93" s="35"/>
-      <c r="F93" s="65"/>
-      <c r="G93" s="97" t="s">
+      <c r="B93" s="34"/>
+      <c r="C93" s="34"/>
+      <c r="D93" s="34"/>
+      <c r="E93" s="34"/>
+      <c r="F93" s="62"/>
+      <c r="G93" s="129" t="s">
         <v>89</v>
       </c>
-      <c r="H93" s="97"/>
+      <c r="H93" s="129"/>
       <c r="I93" s="1"/>
       <c r="J93" s="2"/>
       <c r="K93" s="3"/>
@@ -4492,15 +4514,15 @@
       <c r="A94" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="B94" s="35"/>
-      <c r="C94" s="40"/>
-      <c r="D94" s="35"/>
-      <c r="E94" s="40"/>
-      <c r="F94" s="51"/>
-      <c r="G94" s="97" t="s">
+      <c r="B94" s="34"/>
+      <c r="C94" s="38"/>
+      <c r="D94" s="34"/>
+      <c r="E94" s="38"/>
+      <c r="F94" s="48"/>
+      <c r="G94" s="129" t="s">
         <v>90</v>
       </c>
-      <c r="H94" s="97"/>
+      <c r="H94" s="129"/>
       <c r="I94" s="1"/>
       <c r="J94" s="2"/>
       <c r="K94" s="3"/>
@@ -4524,15 +4546,15 @@
       <c r="A95" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="B95" s="35"/>
-      <c r="C95" s="35"/>
-      <c r="D95" s="35"/>
-      <c r="E95" s="40"/>
-      <c r="F95" s="51"/>
-      <c r="G95" s="97" t="s">
+      <c r="B95" s="34"/>
+      <c r="C95" s="34"/>
+      <c r="D95" s="34"/>
+      <c r="E95" s="38"/>
+      <c r="F95" s="48"/>
+      <c r="G95" s="129" t="s">
         <v>91</v>
       </c>
-      <c r="H95" s="97"/>
+      <c r="H95" s="129"/>
       <c r="I95" s="1"/>
       <c r="J95" s="2"/>
       <c r="K95" s="3"/>
@@ -4553,18 +4575,18 @@
       <c r="Z95" s="4"/>
     </row>
     <row r="96" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A96" s="99" t="s">
+      <c r="A96" s="89" t="s">
         <v>92</v>
       </c>
-      <c r="B96" s="35"/>
-      <c r="C96" s="35"/>
-      <c r="D96" s="35"/>
-      <c r="E96" s="35"/>
-      <c r="F96" s="65"/>
-      <c r="G96" s="97" t="s">
+      <c r="B96" s="34"/>
+      <c r="C96" s="34"/>
+      <c r="D96" s="34"/>
+      <c r="E96" s="34"/>
+      <c r="F96" s="62"/>
+      <c r="G96" s="129" t="s">
         <v>92</v>
       </c>
-      <c r="H96" s="97"/>
+      <c r="H96" s="129"/>
       <c r="I96" s="1"/>
       <c r="J96" s="2"/>
       <c r="K96" s="3"/>
@@ -4585,16 +4607,16 @@
       <c r="Z96" s="4"/>
     </row>
     <row r="97" spans="1:26" ht="21" customHeight="1">
-      <c r="A97" s="109" t="s">
+      <c r="A97" s="101" t="s">
         <v>93</v>
       </c>
-      <c r="B97" s="101"/>
-      <c r="C97" s="101"/>
-      <c r="D97" s="101"/>
-      <c r="E97" s="101"/>
-      <c r="F97" s="102"/>
-      <c r="G97" s="1"/>
-      <c r="H97" s="1"/>
+      <c r="B97" s="96"/>
+      <c r="C97" s="96"/>
+      <c r="D97" s="96"/>
+      <c r="E97" s="96"/>
+      <c r="F97" s="97"/>
+      <c r="G97" s="126"/>
+      <c r="H97" s="126"/>
       <c r="I97" s="1"/>
       <c r="J97" s="2"/>
       <c r="K97" s="3"/>
@@ -4615,16 +4637,16 @@
       <c r="Z97" s="4"/>
     </row>
     <row r="98" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A98" s="110" t="s">
+      <c r="A98" s="105" t="s">
         <v>11</v>
       </c>
-      <c r="B98" s="101"/>
-      <c r="C98" s="101"/>
-      <c r="D98" s="101"/>
-      <c r="E98" s="101"/>
-      <c r="F98" s="102"/>
-      <c r="G98" s="1"/>
-      <c r="H98" s="1"/>
+      <c r="B98" s="96"/>
+      <c r="C98" s="96"/>
+      <c r="D98" s="96"/>
+      <c r="E98" s="96"/>
+      <c r="F98" s="97"/>
+      <c r="G98" s="126"/>
+      <c r="H98" s="126"/>
       <c r="I98" s="1"/>
       <c r="J98" s="2"/>
       <c r="K98" s="3"/>
@@ -4648,15 +4670,15 @@
       <c r="A99" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="B99" s="35"/>
-      <c r="C99" s="35"/>
-      <c r="D99" s="35"/>
-      <c r="E99" s="35"/>
+      <c r="B99" s="34"/>
+      <c r="C99" s="34"/>
+      <c r="D99" s="34"/>
+      <c r="E99" s="34"/>
       <c r="F99" s="18"/>
-      <c r="G99" s="95" t="s">
+      <c r="G99" s="131" t="s">
         <v>94</v>
       </c>
-      <c r="H99" s="95"/>
+      <c r="H99" s="131"/>
       <c r="I99" s="1"/>
       <c r="J99" s="2"/>
       <c r="K99" s="3"/>
@@ -4677,16 +4699,16 @@
       <c r="Z99" s="4"/>
     </row>
     <row r="100" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A100" s="100" t="s">
+      <c r="A100" s="106" t="s">
         <v>52</v>
       </c>
-      <c r="B100" s="101"/>
-      <c r="C100" s="101"/>
-      <c r="D100" s="101"/>
-      <c r="E100" s="101"/>
-      <c r="F100" s="102"/>
-      <c r="G100" s="95"/>
-      <c r="H100" s="95"/>
+      <c r="B100" s="96"/>
+      <c r="C100" s="96"/>
+      <c r="D100" s="96"/>
+      <c r="E100" s="96"/>
+      <c r="F100" s="97"/>
+      <c r="G100" s="131"/>
+      <c r="H100" s="131"/>
       <c r="I100" s="1"/>
       <c r="J100" s="2"/>
       <c r="K100" s="3"/>
@@ -4707,18 +4729,18 @@
       <c r="Z100" s="4"/>
     </row>
     <row r="101" spans="1:26" ht="29.25" customHeight="1">
-      <c r="A101" s="87" t="s">
+      <c r="A101" s="84" t="s">
         <v>95</v>
       </c>
-      <c r="B101" s="35"/>
-      <c r="C101" s="40"/>
-      <c r="D101" s="35"/>
-      <c r="E101" s="40"/>
-      <c r="F101" s="51"/>
-      <c r="G101" s="95" t="s">
+      <c r="B101" s="34"/>
+      <c r="C101" s="38"/>
+      <c r="D101" s="34"/>
+      <c r="E101" s="38"/>
+      <c r="F101" s="48"/>
+      <c r="G101" s="131" t="s">
         <v>95</v>
       </c>
-      <c r="H101" s="95"/>
+      <c r="H101" s="131"/>
       <c r="I101" s="1"/>
       <c r="J101" s="2"/>
       <c r="K101" s="3"/>
@@ -4742,15 +4764,15 @@
       <c r="A102" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="B102" s="35"/>
-      <c r="C102" s="35"/>
-      <c r="D102" s="35"/>
-      <c r="E102" s="40"/>
-      <c r="F102" s="51"/>
-      <c r="G102" s="95" t="s">
+      <c r="B102" s="34"/>
+      <c r="C102" s="34"/>
+      <c r="D102" s="34"/>
+      <c r="E102" s="38"/>
+      <c r="F102" s="48"/>
+      <c r="G102" s="131" t="s">
         <v>96</v>
       </c>
-      <c r="H102" s="95"/>
+      <c r="H102" s="131"/>
       <c r="I102" s="1"/>
       <c r="J102" s="2"/>
       <c r="K102" s="3"/>
@@ -4774,15 +4796,15 @@
       <c r="A103" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="B103" s="35"/>
-      <c r="C103" s="35"/>
-      <c r="D103" s="35"/>
-      <c r="E103" s="40"/>
-      <c r="F103" s="51"/>
-      <c r="G103" s="95" t="s">
+      <c r="B103" s="34"/>
+      <c r="C103" s="34"/>
+      <c r="D103" s="34"/>
+      <c r="E103" s="38"/>
+      <c r="F103" s="48"/>
+      <c r="G103" s="131" t="s">
         <v>97</v>
       </c>
-      <c r="H103" s="95"/>
+      <c r="H103" s="131"/>
       <c r="I103" s="1"/>
       <c r="J103" s="2"/>
       <c r="K103" s="3"/>
@@ -4806,15 +4828,15 @@
       <c r="A104" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="B104" s="35"/>
-      <c r="C104" s="35"/>
-      <c r="D104" s="35"/>
-      <c r="E104" s="40"/>
-      <c r="F104" s="51"/>
-      <c r="G104" s="95" t="s">
+      <c r="B104" s="34"/>
+      <c r="C104" s="34"/>
+      <c r="D104" s="34"/>
+      <c r="E104" s="38"/>
+      <c r="F104" s="48"/>
+      <c r="G104" s="131" t="s">
         <v>98</v>
       </c>
-      <c r="H104" s="95"/>
+      <c r="H104" s="131"/>
       <c r="I104" s="1"/>
       <c r="J104" s="2"/>
       <c r="K104" s="3"/>
@@ -4835,16 +4857,16 @@
       <c r="Z104" s="4"/>
     </row>
     <row r="105" spans="1:26" ht="21" customHeight="1">
-      <c r="A105" s="109" t="s">
+      <c r="A105" s="101" t="s">
         <v>99</v>
       </c>
-      <c r="B105" s="101"/>
-      <c r="C105" s="101"/>
-      <c r="D105" s="101"/>
-      <c r="E105" s="101"/>
-      <c r="F105" s="102"/>
-      <c r="G105" s="95"/>
-      <c r="H105" s="95"/>
+      <c r="B105" s="96"/>
+      <c r="C105" s="96"/>
+      <c r="D105" s="96"/>
+      <c r="E105" s="96"/>
+      <c r="F105" s="97"/>
+      <c r="G105" s="131"/>
+      <c r="H105" s="131"/>
       <c r="I105" s="1"/>
       <c r="J105" s="2"/>
       <c r="K105" s="3"/>
@@ -4865,16 +4887,16 @@
       <c r="Z105" s="4"/>
     </row>
     <row r="106" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A106" s="110" t="s">
+      <c r="A106" s="105" t="s">
         <v>11</v>
       </c>
-      <c r="B106" s="101"/>
-      <c r="C106" s="101"/>
-      <c r="D106" s="101"/>
-      <c r="E106" s="101"/>
-      <c r="F106" s="102"/>
-      <c r="G106" s="95"/>
-      <c r="H106" s="95"/>
+      <c r="B106" s="96"/>
+      <c r="C106" s="96"/>
+      <c r="D106" s="96"/>
+      <c r="E106" s="96"/>
+      <c r="F106" s="97"/>
+      <c r="G106" s="131"/>
+      <c r="H106" s="131"/>
       <c r="I106" s="1"/>
       <c r="J106" s="2"/>
       <c r="K106" s="3"/>
@@ -4895,18 +4917,18 @@
       <c r="Z106" s="4"/>
     </row>
     <row r="107" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A107" s="26" t="s">
+      <c r="A107" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="B107" s="35"/>
-      <c r="C107" s="35"/>
-      <c r="D107" s="35"/>
-      <c r="E107" s="35"/>
-      <c r="F107" s="65"/>
-      <c r="G107" s="95" t="s">
+      <c r="B107" s="34"/>
+      <c r="C107" s="34"/>
+      <c r="D107" s="34"/>
+      <c r="E107" s="34"/>
+      <c r="F107" s="62"/>
+      <c r="G107" s="131" t="s">
         <v>100</v>
       </c>
-      <c r="H107" s="95"/>
+      <c r="H107" s="131"/>
       <c r="I107" s="1"/>
       <c r="J107" s="2"/>
       <c r="K107" s="3"/>
@@ -4927,18 +4949,18 @@
       <c r="Z107" s="4"/>
     </row>
     <row r="108" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A108" s="26" t="s">
+      <c r="A108" s="25" t="s">
         <v>101</v>
       </c>
-      <c r="B108" s="35"/>
-      <c r="C108" s="35"/>
-      <c r="D108" s="35"/>
-      <c r="E108" s="35"/>
-      <c r="F108" s="65"/>
-      <c r="G108" s="95" t="s">
+      <c r="B108" s="34"/>
+      <c r="C108" s="34"/>
+      <c r="D108" s="34"/>
+      <c r="E108" s="34"/>
+      <c r="F108" s="62"/>
+      <c r="G108" s="131" t="s">
         <v>101</v>
       </c>
-      <c r="H108" s="95"/>
+      <c r="H108" s="131"/>
       <c r="I108" s="1"/>
       <c r="J108" s="2"/>
       <c r="K108" s="3"/>
@@ -4959,18 +4981,18 @@
       <c r="Z108" s="4"/>
     </row>
     <row r="109" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A109" s="26" t="s">
+      <c r="A109" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="B109" s="35"/>
-      <c r="C109" s="35"/>
-      <c r="D109" s="35"/>
-      <c r="E109" s="35"/>
-      <c r="F109" s="66"/>
-      <c r="G109" s="95" t="s">
+      <c r="B109" s="34"/>
+      <c r="C109" s="34"/>
+      <c r="D109" s="34"/>
+      <c r="E109" s="34"/>
+      <c r="F109" s="63"/>
+      <c r="G109" s="131" t="s">
         <v>102</v>
       </c>
-      <c r="H109" s="95"/>
+      <c r="H109" s="131"/>
       <c r="I109" s="1"/>
       <c r="J109" s="2"/>
       <c r="K109" s="3"/>
@@ -4991,16 +5013,16 @@
       <c r="Z109" s="4"/>
     </row>
     <row r="110" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A110" s="100" t="s">
+      <c r="A110" s="106" t="s">
         <v>52</v>
       </c>
-      <c r="B110" s="101"/>
-      <c r="C110" s="101"/>
-      <c r="D110" s="101"/>
-      <c r="E110" s="101"/>
-      <c r="F110" s="102"/>
-      <c r="G110" s="1"/>
-      <c r="H110" s="1"/>
+      <c r="B110" s="96"/>
+      <c r="C110" s="96"/>
+      <c r="D110" s="96"/>
+      <c r="E110" s="96"/>
+      <c r="F110" s="97"/>
+      <c r="G110" s="126"/>
+      <c r="H110" s="126"/>
       <c r="I110" s="1"/>
       <c r="J110" s="2"/>
       <c r="K110" s="3"/>
@@ -5024,15 +5046,15 @@
       <c r="A111" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="B111" s="35"/>
-      <c r="C111" s="40"/>
-      <c r="D111" s="35"/>
-      <c r="E111" s="40"/>
-      <c r="F111" s="51"/>
-      <c r="G111" s="95" t="s">
+      <c r="B111" s="34"/>
+      <c r="C111" s="38"/>
+      <c r="D111" s="34"/>
+      <c r="E111" s="38"/>
+      <c r="F111" s="48"/>
+      <c r="G111" s="131" t="s">
         <v>103</v>
       </c>
-      <c r="H111" s="95"/>
+      <c r="H111" s="131"/>
       <c r="I111" s="1"/>
       <c r="J111" s="2"/>
       <c r="K111" s="3"/>
@@ -5056,15 +5078,15 @@
       <c r="A112" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="B112" s="35"/>
-      <c r="C112" s="40"/>
-      <c r="D112" s="35"/>
-      <c r="E112" s="40"/>
-      <c r="F112" s="51"/>
-      <c r="G112" s="95" t="s">
+      <c r="B112" s="34"/>
+      <c r="C112" s="38"/>
+      <c r="D112" s="34"/>
+      <c r="E112" s="38"/>
+      <c r="F112" s="48"/>
+      <c r="G112" s="131" t="s">
         <v>104</v>
       </c>
-      <c r="H112" s="95"/>
+      <c r="H112" s="131"/>
       <c r="I112" s="1"/>
       <c r="J112" s="2"/>
       <c r="K112" s="3"/>
@@ -5088,15 +5110,15 @@
       <c r="A113" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="B113" s="47"/>
-      <c r="C113" s="47"/>
-      <c r="D113" s="47"/>
-      <c r="E113" s="47"/>
-      <c r="F113" s="50"/>
-      <c r="G113" s="95" t="s">
+      <c r="B113" s="45"/>
+      <c r="C113" s="45"/>
+      <c r="D113" s="45"/>
+      <c r="E113" s="45"/>
+      <c r="F113" s="47"/>
+      <c r="G113" s="131" t="s">
         <v>105</v>
       </c>
-      <c r="H113" s="95"/>
+      <c r="H113" s="131"/>
       <c r="I113" s="1"/>
       <c r="J113" s="2"/>
       <c r="K113" s="3"/>
@@ -5120,15 +5142,15 @@
       <c r="A114" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="B114" s="47"/>
-      <c r="C114" s="47"/>
-      <c r="D114" s="47"/>
-      <c r="E114" s="47"/>
-      <c r="F114" s="50"/>
-      <c r="G114" s="95" t="s">
+      <c r="B114" s="45"/>
+      <c r="C114" s="45"/>
+      <c r="D114" s="45"/>
+      <c r="E114" s="45"/>
+      <c r="F114" s="47"/>
+      <c r="G114" s="131" t="s">
         <v>106</v>
       </c>
-      <c r="H114" s="95"/>
+      <c r="H114" s="131"/>
       <c r="I114" s="1"/>
       <c r="J114" s="2"/>
       <c r="K114" s="3"/>
@@ -5152,15 +5174,15 @@
       <c r="A115" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="B115" s="47"/>
-      <c r="C115" s="47"/>
-      <c r="D115" s="47"/>
-      <c r="E115" s="40"/>
-      <c r="F115" s="51"/>
-      <c r="G115" s="95" t="s">
+      <c r="B115" s="45"/>
+      <c r="C115" s="45"/>
+      <c r="D115" s="45"/>
+      <c r="E115" s="38"/>
+      <c r="F115" s="48"/>
+      <c r="G115" s="131" t="s">
         <v>107</v>
       </c>
-      <c r="H115" s="95"/>
+      <c r="H115" s="131"/>
       <c r="I115" s="1"/>
       <c r="J115" s="2"/>
       <c r="K115" s="3"/>
@@ -5181,18 +5203,18 @@
       <c r="Z115" s="4"/>
     </row>
     <row r="116" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A116" s="67" t="s">
+      <c r="A116" s="64" t="s">
         <v>108</v>
       </c>
-      <c r="B116" s="43"/>
-      <c r="C116" s="43"/>
-      <c r="D116" s="43"/>
-      <c r="E116" s="56"/>
-      <c r="F116" s="41"/>
-      <c r="G116" s="95" t="s">
+      <c r="B116" s="41"/>
+      <c r="C116" s="41"/>
+      <c r="D116" s="41"/>
+      <c r="E116" s="53"/>
+      <c r="F116" s="39"/>
+      <c r="G116" s="131" t="s">
         <v>108</v>
       </c>
-      <c r="H116" s="95"/>
+      <c r="H116" s="131"/>
       <c r="I116" s="1"/>
       <c r="J116" s="2"/>
       <c r="K116" s="3"/>
@@ -5213,11 +5235,11 @@
       <c r="Z116" s="4"/>
     </row>
     <row r="117" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A117" s="68"/>
+      <c r="A117" s="65"/>
       <c r="B117" s="7"/>
       <c r="C117" s="7"/>
-      <c r="D117" s="69"/>
-      <c r="E117" s="70"/>
+      <c r="D117" s="66"/>
+      <c r="E117" s="67"/>
       <c r="F117" s="7"/>
       <c r="G117" s="1"/>
       <c r="H117" s="1"/>
@@ -5241,16 +5263,16 @@
       <c r="Z117" s="4"/>
     </row>
     <row r="118" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A118" s="71" t="s">
+      <c r="A118" s="68" t="s">
         <v>110</v>
       </c>
-      <c r="B118" s="72"/>
-      <c r="C118" s="111" t="s">
+      <c r="B118" s="69"/>
+      <c r="C118" s="120" t="s">
         <v>111</v>
       </c>
-      <c r="D118" s="111"/>
-      <c r="E118" s="111"/>
-      <c r="F118" s="111"/>
+      <c r="D118" s="120"/>
+      <c r="E118" s="120"/>
+      <c r="F118" s="120"/>
       <c r="G118" s="1"/>
       <c r="H118" s="1"/>
       <c r="I118" s="1"/>
@@ -5273,11 +5295,11 @@
       <c r="Z118" s="4"/>
     </row>
     <row r="119" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A119" s="72"/>
-      <c r="B119" s="72"/>
-      <c r="C119" s="72"/>
-      <c r="D119" s="72"/>
-      <c r="E119" s="70"/>
+      <c r="A119" s="69"/>
+      <c r="B119" s="69"/>
+      <c r="C119" s="69"/>
+      <c r="D119" s="69"/>
+      <c r="E119" s="67"/>
       <c r="F119" s="7"/>
       <c r="G119" s="1"/>
       <c r="H119" s="1"/>
@@ -5301,11 +5323,11 @@
       <c r="Z119" s="4"/>
     </row>
     <row r="120" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A120" s="72"/>
-      <c r="B120" s="72"/>
-      <c r="C120" s="72"/>
+      <c r="A120" s="69"/>
+      <c r="B120" s="69"/>
+      <c r="C120" s="69"/>
       <c r="D120" s="3"/>
-      <c r="E120" s="70"/>
+      <c r="E120" s="67"/>
       <c r="F120" s="7"/>
       <c r="G120" s="1"/>
       <c r="H120" s="1"/>
@@ -5329,12 +5351,12 @@
       <c r="Z120" s="4"/>
     </row>
     <row r="121" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A121" s="73"/>
-      <c r="B121" s="72"/>
-      <c r="C121" s="85" t="s">
+      <c r="A121" s="70"/>
+      <c r="B121" s="69"/>
+      <c r="C121" s="82" t="s">
         <v>109</v>
       </c>
-      <c r="D121" s="72"/>
+      <c r="D121" s="69"/>
       <c r="E121" s="7"/>
       <c r="F121" s="7"/>
       <c r="G121" s="1"/>
@@ -5359,12 +5381,12 @@
       <c r="Z121" s="4"/>
     </row>
     <row r="122" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A122" s="86"/>
-      <c r="B122" s="72"/>
-      <c r="C122" s="103" t="s">
+      <c r="A122" s="83"/>
+      <c r="B122" s="69"/>
+      <c r="C122" s="115" t="s">
         <v>112</v>
       </c>
-      <c r="D122" s="104"/>
+      <c r="D122" s="116"/>
       <c r="E122" s="7"/>
       <c r="F122" s="7"/>
       <c r="G122" s="1"/>
@@ -5389,9 +5411,9 @@
       <c r="Z122" s="4"/>
     </row>
     <row r="123" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A123" s="74"/>
-      <c r="B123" s="69"/>
-      <c r="C123" s="75"/>
+      <c r="A123" s="71"/>
+      <c r="B123" s="66"/>
+      <c r="C123" s="72"/>
       <c r="D123" s="7"/>
       <c r="E123" s="7"/>
       <c r="F123" s="7"/>
@@ -5417,9 +5439,9 @@
       <c r="Z123" s="4"/>
     </row>
     <row r="124" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A124" s="74"/>
-      <c r="B124" s="69"/>
-      <c r="C124" s="75"/>
+      <c r="A124" s="71"/>
+      <c r="B124" s="66"/>
+      <c r="C124" s="72"/>
       <c r="D124" s="7"/>
       <c r="E124" s="7"/>
       <c r="F124" s="7"/>
@@ -5445,8 +5467,8 @@
       <c r="Z124" s="4"/>
     </row>
     <row r="125" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A125" s="76"/>
-      <c r="B125" s="77"/>
+      <c r="A125" s="73"/>
+      <c r="B125" s="74"/>
       <c r="C125" s="7"/>
       <c r="D125" s="7"/>
       <c r="E125" s="7"/>
@@ -5473,8 +5495,8 @@
       <c r="Z125" s="4"/>
     </row>
     <row r="126" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A126" s="105"/>
-      <c r="B126" s="106"/>
+      <c r="A126" s="117"/>
+      <c r="B126" s="91"/>
       <c r="C126" s="7"/>
       <c r="D126" s="7"/>
       <c r="E126" s="7"/>
@@ -5501,9 +5523,9 @@
       <c r="Z126" s="4"/>
     </row>
     <row r="127" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A127" s="107"/>
-      <c r="B127" s="106"/>
-      <c r="C127" s="106"/>
+      <c r="A127" s="118"/>
+      <c r="B127" s="91"/>
+      <c r="C127" s="91"/>
       <c r="D127" s="7"/>
       <c r="E127" s="7"/>
       <c r="F127" s="7"/>
@@ -5529,7 +5551,7 @@
       <c r="Z127" s="4"/>
     </row>
     <row r="128" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A128" s="78"/>
+      <c r="A128" s="75"/>
       <c r="B128" s="7"/>
       <c r="C128" s="7"/>
       <c r="D128" s="7"/>
@@ -5557,7 +5579,7 @@
       <c r="Z128" s="4"/>
     </row>
     <row r="129" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A129" s="78"/>
+      <c r="A129" s="75"/>
       <c r="B129" s="7"/>
       <c r="C129" s="7"/>
       <c r="D129" s="7"/>
@@ -5585,7 +5607,7 @@
       <c r="Z129" s="4"/>
     </row>
     <row r="130" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A130" s="78"/>
+      <c r="A130" s="75"/>
       <c r="B130" s="7"/>
       <c r="C130" s="7"/>
       <c r="D130" s="7"/>
@@ -5613,7 +5635,7 @@
       <c r="Z130" s="4"/>
     </row>
     <row r="131" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A131" s="78"/>
+      <c r="A131" s="75"/>
       <c r="B131" s="7"/>
       <c r="C131" s="7"/>
       <c r="D131" s="7"/>
@@ -5641,7 +5663,7 @@
       <c r="Z131" s="4"/>
     </row>
     <row r="132" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A132" s="78"/>
+      <c r="A132" s="75"/>
       <c r="B132" s="7"/>
       <c r="C132" s="7"/>
       <c r="D132" s="7"/>
@@ -5669,7 +5691,7 @@
       <c r="Z132" s="4"/>
     </row>
     <row r="133" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A133" s="78"/>
+      <c r="A133" s="75"/>
       <c r="B133" s="7"/>
       <c r="C133" s="7"/>
       <c r="D133" s="7"/>
@@ -5697,7 +5719,7 @@
       <c r="Z133" s="4"/>
     </row>
     <row r="134" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A134" s="78"/>
+      <c r="A134" s="75"/>
       <c r="B134" s="7"/>
       <c r="C134" s="7"/>
       <c r="D134" s="7"/>
@@ -5725,7 +5747,7 @@
       <c r="Z134" s="4"/>
     </row>
     <row r="135" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A135" s="78"/>
+      <c r="A135" s="75"/>
       <c r="B135" s="7"/>
       <c r="C135" s="7"/>
       <c r="D135" s="7"/>
@@ -5753,7 +5775,7 @@
       <c r="Z135" s="4"/>
     </row>
     <row r="136" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A136" s="78"/>
+      <c r="A136" s="75"/>
       <c r="B136" s="7"/>
       <c r="C136" s="7"/>
       <c r="D136" s="7"/>
@@ -5781,7 +5803,7 @@
       <c r="Z136" s="4"/>
     </row>
     <row r="137" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A137" s="78"/>
+      <c r="A137" s="75"/>
       <c r="B137" s="7"/>
       <c r="C137" s="7"/>
       <c r="D137" s="7"/>
@@ -5809,7 +5831,7 @@
       <c r="Z137" s="4"/>
     </row>
     <row r="138" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A138" s="78"/>
+      <c r="A138" s="75"/>
       <c r="B138" s="7"/>
       <c r="C138" s="7"/>
       <c r="D138" s="7"/>
@@ -5837,7 +5859,7 @@
       <c r="Z138" s="4"/>
     </row>
     <row r="139" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A139" s="78"/>
+      <c r="A139" s="75"/>
       <c r="B139" s="7"/>
       <c r="C139" s="7"/>
       <c r="D139" s="7"/>
@@ -5865,7 +5887,7 @@
       <c r="Z139" s="4"/>
     </row>
     <row r="140" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A140" s="78"/>
+      <c r="A140" s="75"/>
       <c r="B140" s="7"/>
       <c r="C140" s="7"/>
       <c r="D140" s="7"/>
@@ -5893,7 +5915,7 @@
       <c r="Z140" s="4"/>
     </row>
     <row r="141" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A141" s="78"/>
+      <c r="A141" s="75"/>
       <c r="B141" s="7"/>
       <c r="C141" s="7"/>
       <c r="D141" s="7"/>
@@ -5921,7 +5943,7 @@
       <c r="Z141" s="4"/>
     </row>
     <row r="142" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A142" s="78"/>
+      <c r="A142" s="75"/>
       <c r="B142" s="7"/>
       <c r="C142" s="7"/>
       <c r="D142" s="7"/>
@@ -5949,7 +5971,7 @@
       <c r="Z142" s="4"/>
     </row>
     <row r="143" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A143" s="78"/>
+      <c r="A143" s="75"/>
       <c r="B143" s="7"/>
       <c r="C143" s="7"/>
       <c r="D143" s="7"/>
@@ -5977,7 +5999,7 @@
       <c r="Z143" s="4"/>
     </row>
     <row r="144" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A144" s="78"/>
+      <c r="A144" s="75"/>
       <c r="B144" s="7"/>
       <c r="C144" s="7"/>
       <c r="D144" s="7"/>
@@ -6005,7 +6027,7 @@
       <c r="Z144" s="4"/>
     </row>
     <row r="145" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A145" s="78"/>
+      <c r="A145" s="75"/>
       <c r="B145" s="7"/>
       <c r="C145" s="7"/>
       <c r="D145" s="7"/>
@@ -6033,7 +6055,7 @@
       <c r="Z145" s="4"/>
     </row>
     <row r="146" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A146" s="78"/>
+      <c r="A146" s="75"/>
       <c r="B146" s="7"/>
       <c r="C146" s="7"/>
       <c r="D146" s="7"/>
@@ -6061,7 +6083,7 @@
       <c r="Z146" s="4"/>
     </row>
     <row r="147" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A147" s="78"/>
+      <c r="A147" s="75"/>
       <c r="B147" s="7"/>
       <c r="C147" s="7"/>
       <c r="D147" s="7"/>
@@ -6089,7 +6111,7 @@
       <c r="Z147" s="4"/>
     </row>
     <row r="148" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A148" s="78"/>
+      <c r="A148" s="75"/>
       <c r="B148" s="7"/>
       <c r="C148" s="7"/>
       <c r="D148" s="7"/>
@@ -6117,7 +6139,7 @@
       <c r="Z148" s="4"/>
     </row>
     <row r="149" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A149" s="78"/>
+      <c r="A149" s="75"/>
       <c r="B149" s="7"/>
       <c r="C149" s="7"/>
       <c r="D149" s="7"/>
@@ -6145,7 +6167,7 @@
       <c r="Z149" s="4"/>
     </row>
     <row r="150" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A150" s="78"/>
+      <c r="A150" s="75"/>
       <c r="B150" s="7"/>
       <c r="C150" s="7"/>
       <c r="D150" s="7"/>
@@ -6173,7 +6195,7 @@
       <c r="Z150" s="4"/>
     </row>
     <row r="151" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A151" s="78"/>
+      <c r="A151" s="75"/>
       <c r="B151" s="7"/>
       <c r="C151" s="7"/>
       <c r="D151" s="7"/>
@@ -6201,7 +6223,7 @@
       <c r="Z151" s="4"/>
     </row>
     <row r="152" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A152" s="78"/>
+      <c r="A152" s="75"/>
       <c r="B152" s="7"/>
       <c r="C152" s="7"/>
       <c r="D152" s="7"/>
@@ -6229,7 +6251,7 @@
       <c r="Z152" s="4"/>
     </row>
     <row r="153" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A153" s="78"/>
+      <c r="A153" s="75"/>
       <c r="B153" s="7"/>
       <c r="C153" s="7"/>
       <c r="D153" s="7"/>
@@ -6257,7 +6279,7 @@
       <c r="Z153" s="4"/>
     </row>
     <row r="154" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A154" s="78"/>
+      <c r="A154" s="75"/>
       <c r="B154" s="7"/>
       <c r="C154" s="7"/>
       <c r="D154" s="7"/>
@@ -6285,7 +6307,7 @@
       <c r="Z154" s="4"/>
     </row>
     <row r="155" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A155" s="78"/>
+      <c r="A155" s="75"/>
       <c r="B155" s="7"/>
       <c r="C155" s="7"/>
       <c r="D155" s="7"/>
@@ -6313,7 +6335,7 @@
       <c r="Z155" s="4"/>
     </row>
     <row r="156" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A156" s="78"/>
+      <c r="A156" s="75"/>
       <c r="B156" s="7"/>
       <c r="C156" s="7"/>
       <c r="D156" s="7"/>
@@ -6341,7 +6363,7 @@
       <c r="Z156" s="4"/>
     </row>
     <row r="157" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A157" s="78"/>
+      <c r="A157" s="75"/>
       <c r="B157" s="7"/>
       <c r="C157" s="7"/>
       <c r="D157" s="7"/>
@@ -6369,7 +6391,7 @@
       <c r="Z157" s="4"/>
     </row>
     <row r="158" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A158" s="78"/>
+      <c r="A158" s="75"/>
       <c r="B158" s="7"/>
       <c r="C158" s="7"/>
       <c r="D158" s="7"/>
@@ -6397,7 +6419,7 @@
       <c r="Z158" s="4"/>
     </row>
     <row r="159" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A159" s="78"/>
+      <c r="A159" s="75"/>
       <c r="B159" s="7"/>
       <c r="C159" s="7"/>
       <c r="D159" s="7"/>
@@ -6425,7 +6447,7 @@
       <c r="Z159" s="4"/>
     </row>
     <row r="160" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A160" s="78"/>
+      <c r="A160" s="75"/>
       <c r="B160" s="7"/>
       <c r="C160" s="7"/>
       <c r="D160" s="7"/>
@@ -6453,7 +6475,7 @@
       <c r="Z160" s="4"/>
     </row>
     <row r="161" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A161" s="78"/>
+      <c r="A161" s="75"/>
       <c r="B161" s="7"/>
       <c r="C161" s="7"/>
       <c r="D161" s="7"/>
@@ -6481,7 +6503,7 @@
       <c r="Z161" s="4"/>
     </row>
     <row r="162" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A162" s="78"/>
+      <c r="A162" s="75"/>
       <c r="B162" s="7"/>
       <c r="C162" s="7"/>
       <c r="D162" s="7"/>
@@ -6509,7 +6531,7 @@
       <c r="Z162" s="4"/>
     </row>
     <row r="163" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A163" s="78"/>
+      <c r="A163" s="75"/>
       <c r="B163" s="7"/>
       <c r="C163" s="7"/>
       <c r="D163" s="7"/>
@@ -6537,7 +6559,7 @@
       <c r="Z163" s="4"/>
     </row>
     <row r="164" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A164" s="78"/>
+      <c r="A164" s="75"/>
       <c r="B164" s="7"/>
       <c r="C164" s="7"/>
       <c r="D164" s="7"/>
@@ -6565,7 +6587,7 @@
       <c r="Z164" s="4"/>
     </row>
     <row r="165" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A165" s="78"/>
+      <c r="A165" s="75"/>
       <c r="B165" s="7"/>
       <c r="C165" s="7"/>
       <c r="D165" s="7"/>
@@ -6593,7 +6615,7 @@
       <c r="Z165" s="4"/>
     </row>
     <row r="166" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A166" s="78"/>
+      <c r="A166" s="75"/>
       <c r="B166" s="7"/>
       <c r="C166" s="7"/>
       <c r="D166" s="7"/>
@@ -6621,7 +6643,7 @@
       <c r="Z166" s="4"/>
     </row>
     <row r="167" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A167" s="78"/>
+      <c r="A167" s="75"/>
       <c r="B167" s="7"/>
       <c r="C167" s="7"/>
       <c r="D167" s="7"/>
@@ -6649,7 +6671,7 @@
       <c r="Z167" s="4"/>
     </row>
     <row r="168" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A168" s="78"/>
+      <c r="A168" s="75"/>
       <c r="B168" s="7"/>
       <c r="C168" s="7"/>
       <c r="D168" s="7"/>
@@ -6677,7 +6699,7 @@
       <c r="Z168" s="4"/>
     </row>
     <row r="169" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A169" s="78"/>
+      <c r="A169" s="75"/>
       <c r="B169" s="7"/>
       <c r="C169" s="7"/>
       <c r="D169" s="7"/>
@@ -6705,7 +6727,7 @@
       <c r="Z169" s="4"/>
     </row>
     <row r="170" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A170" s="78"/>
+      <c r="A170" s="75"/>
       <c r="B170" s="7"/>
       <c r="C170" s="7"/>
       <c r="D170" s="7"/>
@@ -6733,7 +6755,7 @@
       <c r="Z170" s="4"/>
     </row>
     <row r="171" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A171" s="78"/>
+      <c r="A171" s="75"/>
       <c r="B171" s="7"/>
       <c r="C171" s="7"/>
       <c r="D171" s="7"/>
@@ -6761,7 +6783,7 @@
       <c r="Z171" s="4"/>
     </row>
     <row r="172" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A172" s="78"/>
+      <c r="A172" s="75"/>
       <c r="B172" s="7"/>
       <c r="C172" s="7"/>
       <c r="D172" s="7"/>
@@ -6789,7 +6811,7 @@
       <c r="Z172" s="4"/>
     </row>
     <row r="173" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A173" s="78"/>
+      <c r="A173" s="75"/>
       <c r="B173" s="7"/>
       <c r="C173" s="7"/>
       <c r="D173" s="7"/>
@@ -6817,7 +6839,7 @@
       <c r="Z173" s="4"/>
     </row>
     <row r="174" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A174" s="78"/>
+      <c r="A174" s="75"/>
       <c r="B174" s="7"/>
       <c r="C174" s="7"/>
       <c r="D174" s="7"/>
@@ -6845,7 +6867,7 @@
       <c r="Z174" s="4"/>
     </row>
     <row r="175" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A175" s="78"/>
+      <c r="A175" s="75"/>
       <c r="B175" s="7"/>
       <c r="C175" s="7"/>
       <c r="D175" s="7"/>
@@ -6873,7 +6895,7 @@
       <c r="Z175" s="4"/>
     </row>
     <row r="176" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A176" s="78"/>
+      <c r="A176" s="75"/>
       <c r="B176" s="7"/>
       <c r="C176" s="7"/>
       <c r="D176" s="7"/>
@@ -6901,7 +6923,7 @@
       <c r="Z176" s="4"/>
     </row>
     <row r="177" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A177" s="78"/>
+      <c r="A177" s="75"/>
       <c r="B177" s="7"/>
       <c r="C177" s="7"/>
       <c r="D177" s="7"/>
@@ -6929,7 +6951,7 @@
       <c r="Z177" s="4"/>
     </row>
     <row r="178" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A178" s="78"/>
+      <c r="A178" s="75"/>
       <c r="B178" s="7"/>
       <c r="C178" s="7"/>
       <c r="D178" s="7"/>
@@ -6957,7 +6979,7 @@
       <c r="Z178" s="4"/>
     </row>
     <row r="179" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A179" s="78"/>
+      <c r="A179" s="75"/>
       <c r="B179" s="7"/>
       <c r="C179" s="7"/>
       <c r="D179" s="7"/>
@@ -6985,7 +7007,7 @@
       <c r="Z179" s="4"/>
     </row>
     <row r="180" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A180" s="78"/>
+      <c r="A180" s="75"/>
       <c r="B180" s="7"/>
       <c r="C180" s="7"/>
       <c r="D180" s="7"/>
@@ -7013,7 +7035,7 @@
       <c r="Z180" s="4"/>
     </row>
     <row r="181" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A181" s="78"/>
+      <c r="A181" s="75"/>
       <c r="B181" s="7"/>
       <c r="C181" s="7"/>
       <c r="D181" s="7"/>
@@ -7041,7 +7063,7 @@
       <c r="Z181" s="4"/>
     </row>
     <row r="182" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A182" s="78"/>
+      <c r="A182" s="75"/>
       <c r="B182" s="7"/>
       <c r="C182" s="7"/>
       <c r="D182" s="7"/>
@@ -7069,7 +7091,7 @@
       <c r="Z182" s="4"/>
     </row>
     <row r="183" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A183" s="78"/>
+      <c r="A183" s="75"/>
       <c r="B183" s="7"/>
       <c r="C183" s="7"/>
       <c r="D183" s="7"/>
@@ -7097,7 +7119,7 @@
       <c r="Z183" s="4"/>
     </row>
     <row r="184" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A184" s="78"/>
+      <c r="A184" s="75"/>
       <c r="B184" s="7"/>
       <c r="C184" s="7"/>
       <c r="D184" s="7"/>
@@ -7125,7 +7147,7 @@
       <c r="Z184" s="4"/>
     </row>
     <row r="185" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A185" s="78"/>
+      <c r="A185" s="75"/>
       <c r="B185" s="7"/>
       <c r="C185" s="7"/>
       <c r="D185" s="7"/>
@@ -7153,7 +7175,7 @@
       <c r="Z185" s="4"/>
     </row>
     <row r="186" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A186" s="78"/>
+      <c r="A186" s="75"/>
       <c r="B186" s="7"/>
       <c r="C186" s="7"/>
       <c r="D186" s="7"/>
@@ -7181,7 +7203,7 @@
       <c r="Z186" s="4"/>
     </row>
     <row r="187" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A187" s="78"/>
+      <c r="A187" s="75"/>
       <c r="B187" s="7"/>
       <c r="C187" s="7"/>
       <c r="D187" s="7"/>
@@ -7209,7 +7231,7 @@
       <c r="Z187" s="4"/>
     </row>
     <row r="188" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A188" s="78"/>
+      <c r="A188" s="75"/>
       <c r="B188" s="7"/>
       <c r="C188" s="7"/>
       <c r="D188" s="7"/>
@@ -7237,7 +7259,7 @@
       <c r="Z188" s="4"/>
     </row>
     <row r="189" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A189" s="78"/>
+      <c r="A189" s="75"/>
       <c r="B189" s="7"/>
       <c r="C189" s="7"/>
       <c r="D189" s="7"/>
@@ -7265,7 +7287,7 @@
       <c r="Z189" s="4"/>
     </row>
     <row r="190" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A190" s="78"/>
+      <c r="A190" s="75"/>
       <c r="B190" s="7"/>
       <c r="C190" s="7"/>
       <c r="D190" s="7"/>
@@ -7293,7 +7315,7 @@
       <c r="Z190" s="4"/>
     </row>
     <row r="191" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A191" s="78"/>
+      <c r="A191" s="75"/>
       <c r="B191" s="7"/>
       <c r="C191" s="7"/>
       <c r="D191" s="7"/>
@@ -7321,7 +7343,7 @@
       <c r="Z191" s="4"/>
     </row>
     <row r="192" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A192" s="78"/>
+      <c r="A192" s="75"/>
       <c r="B192" s="7"/>
       <c r="C192" s="7"/>
       <c r="D192" s="7"/>
@@ -7349,7 +7371,7 @@
       <c r="Z192" s="4"/>
     </row>
     <row r="193" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A193" s="78"/>
+      <c r="A193" s="75"/>
       <c r="B193" s="7"/>
       <c r="C193" s="7"/>
       <c r="D193" s="7"/>
@@ -7377,7 +7399,7 @@
       <c r="Z193" s="4"/>
     </row>
     <row r="194" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A194" s="78"/>
+      <c r="A194" s="75"/>
       <c r="B194" s="7"/>
       <c r="C194" s="7"/>
       <c r="D194" s="7"/>
@@ -7405,7 +7427,7 @@
       <c r="Z194" s="4"/>
     </row>
     <row r="195" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A195" s="78"/>
+      <c r="A195" s="75"/>
       <c r="B195" s="7"/>
       <c r="C195" s="7"/>
       <c r="D195" s="7"/>
@@ -7433,7 +7455,7 @@
       <c r="Z195" s="4"/>
     </row>
     <row r="196" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A196" s="78"/>
+      <c r="A196" s="75"/>
       <c r="B196" s="7"/>
       <c r="C196" s="7"/>
       <c r="D196" s="7"/>
@@ -7461,7 +7483,7 @@
       <c r="Z196" s="4"/>
     </row>
     <row r="197" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A197" s="78"/>
+      <c r="A197" s="75"/>
       <c r="B197" s="7"/>
       <c r="C197" s="7"/>
       <c r="D197" s="7"/>
@@ -7489,7 +7511,7 @@
       <c r="Z197" s="4"/>
     </row>
     <row r="198" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A198" s="78"/>
+      <c r="A198" s="75"/>
       <c r="B198" s="7"/>
       <c r="C198" s="7"/>
       <c r="D198" s="7"/>
@@ -7517,7 +7539,7 @@
       <c r="Z198" s="4"/>
     </row>
     <row r="199" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A199" s="78"/>
+      <c r="A199" s="75"/>
       <c r="B199" s="7"/>
       <c r="C199" s="7"/>
       <c r="D199" s="7"/>
@@ -7545,7 +7567,7 @@
       <c r="Z199" s="4"/>
     </row>
     <row r="200" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A200" s="78"/>
+      <c r="A200" s="75"/>
       <c r="B200" s="7"/>
       <c r="C200" s="7"/>
       <c r="D200" s="7"/>
@@ -7573,7 +7595,7 @@
       <c r="Z200" s="4"/>
     </row>
     <row r="201" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A201" s="78"/>
+      <c r="A201" s="75"/>
       <c r="B201" s="7"/>
       <c r="C201" s="7"/>
       <c r="D201" s="7"/>
@@ -7601,7 +7623,7 @@
       <c r="Z201" s="4"/>
     </row>
     <row r="202" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A202" s="78"/>
+      <c r="A202" s="75"/>
       <c r="B202" s="7"/>
       <c r="C202" s="7"/>
       <c r="D202" s="7"/>
@@ -7629,7 +7651,7 @@
       <c r="Z202" s="4"/>
     </row>
     <row r="203" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A203" s="78"/>
+      <c r="A203" s="75"/>
       <c r="B203" s="7"/>
       <c r="C203" s="7"/>
       <c r="D203" s="7"/>
@@ -7657,7 +7679,7 @@
       <c r="Z203" s="4"/>
     </row>
     <row r="204" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A204" s="78"/>
+      <c r="A204" s="75"/>
       <c r="B204" s="7"/>
       <c r="C204" s="7"/>
       <c r="D204" s="7"/>
@@ -7685,7 +7707,7 @@
       <c r="Z204" s="4"/>
     </row>
     <row r="205" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A205" s="78"/>
+      <c r="A205" s="75"/>
       <c r="B205" s="7"/>
       <c r="C205" s="7"/>
       <c r="D205" s="7"/>
@@ -7713,7 +7735,7 @@
       <c r="Z205" s="4"/>
     </row>
     <row r="206" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A206" s="78"/>
+      <c r="A206" s="75"/>
       <c r="B206" s="7"/>
       <c r="C206" s="7"/>
       <c r="D206" s="7"/>
@@ -7741,7 +7763,7 @@
       <c r="Z206" s="4"/>
     </row>
     <row r="207" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A207" s="78"/>
+      <c r="A207" s="75"/>
       <c r="B207" s="7"/>
       <c r="C207" s="7"/>
       <c r="D207" s="7"/>
@@ -7769,7 +7791,7 @@
       <c r="Z207" s="4"/>
     </row>
     <row r="208" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A208" s="78"/>
+      <c r="A208" s="75"/>
       <c r="B208" s="7"/>
       <c r="C208" s="7"/>
       <c r="D208" s="7"/>
@@ -7797,7 +7819,7 @@
       <c r="Z208" s="4"/>
     </row>
     <row r="209" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A209" s="78"/>
+      <c r="A209" s="75"/>
       <c r="B209" s="7"/>
       <c r="C209" s="7"/>
       <c r="D209" s="7"/>
@@ -7825,7 +7847,7 @@
       <c r="Z209" s="4"/>
     </row>
     <row r="210" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A210" s="78"/>
+      <c r="A210" s="75"/>
       <c r="B210" s="7"/>
       <c r="C210" s="7"/>
       <c r="D210" s="7"/>
@@ -7853,7 +7875,7 @@
       <c r="Z210" s="4"/>
     </row>
     <row r="211" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A211" s="78"/>
+      <c r="A211" s="75"/>
       <c r="B211" s="7"/>
       <c r="C211" s="7"/>
       <c r="D211" s="7"/>
@@ -7881,7 +7903,7 @@
       <c r="Z211" s="4"/>
     </row>
     <row r="212" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A212" s="78"/>
+      <c r="A212" s="75"/>
       <c r="B212" s="7"/>
       <c r="C212" s="7"/>
       <c r="D212" s="7"/>
@@ -7909,7 +7931,7 @@
       <c r="Z212" s="4"/>
     </row>
     <row r="213" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A213" s="78"/>
+      <c r="A213" s="75"/>
       <c r="B213" s="7"/>
       <c r="C213" s="7"/>
       <c r="D213" s="7"/>
@@ -7937,7 +7959,7 @@
       <c r="Z213" s="4"/>
     </row>
     <row r="214" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A214" s="78"/>
+      <c r="A214" s="75"/>
       <c r="B214" s="7"/>
       <c r="C214" s="7"/>
       <c r="D214" s="7"/>
@@ -7965,7 +7987,7 @@
       <c r="Z214" s="4"/>
     </row>
     <row r="215" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A215" s="78"/>
+      <c r="A215" s="75"/>
       <c r="B215" s="7"/>
       <c r="C215" s="7"/>
       <c r="D215" s="7"/>
@@ -7993,7 +8015,7 @@
       <c r="Z215" s="4"/>
     </row>
     <row r="216" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A216" s="78"/>
+      <c r="A216" s="75"/>
       <c r="B216" s="7"/>
       <c r="C216" s="7"/>
       <c r="D216" s="7"/>
@@ -8021,7 +8043,7 @@
       <c r="Z216" s="4"/>
     </row>
     <row r="217" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A217" s="78"/>
+      <c r="A217" s="75"/>
       <c r="B217" s="7"/>
       <c r="C217" s="7"/>
       <c r="D217" s="7"/>
@@ -8049,7 +8071,7 @@
       <c r="Z217" s="4"/>
     </row>
     <row r="218" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A218" s="78"/>
+      <c r="A218" s="75"/>
       <c r="B218" s="7"/>
       <c r="C218" s="7"/>
       <c r="D218" s="7"/>
@@ -8077,7 +8099,7 @@
       <c r="Z218" s="4"/>
     </row>
     <row r="219" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A219" s="78"/>
+      <c r="A219" s="75"/>
       <c r="B219" s="7"/>
       <c r="C219" s="7"/>
       <c r="D219" s="7"/>
@@ -8105,7 +8127,7 @@
       <c r="Z219" s="4"/>
     </row>
     <row r="220" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A220" s="78"/>
+      <c r="A220" s="75"/>
       <c r="B220" s="7"/>
       <c r="C220" s="7"/>
       <c r="D220" s="7"/>
@@ -8133,7 +8155,7 @@
       <c r="Z220" s="4"/>
     </row>
     <row r="221" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A221" s="78"/>
+      <c r="A221" s="75"/>
       <c r="B221" s="7"/>
       <c r="C221" s="7"/>
       <c r="D221" s="7"/>
@@ -8161,7 +8183,7 @@
       <c r="Z221" s="4"/>
     </row>
     <row r="222" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A222" s="78"/>
+      <c r="A222" s="75"/>
       <c r="B222" s="7"/>
       <c r="C222" s="7"/>
       <c r="D222" s="7"/>
@@ -8189,7 +8211,7 @@
       <c r="Z222" s="4"/>
     </row>
     <row r="223" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A223" s="78"/>
+      <c r="A223" s="75"/>
       <c r="B223" s="7"/>
       <c r="C223" s="7"/>
       <c r="D223" s="7"/>
@@ -8217,7 +8239,7 @@
       <c r="Z223" s="4"/>
     </row>
     <row r="224" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A224" s="78"/>
+      <c r="A224" s="75"/>
       <c r="B224" s="7"/>
       <c r="C224" s="7"/>
       <c r="D224" s="7"/>
@@ -8245,7 +8267,7 @@
       <c r="Z224" s="4"/>
     </row>
     <row r="225" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A225" s="78"/>
+      <c r="A225" s="75"/>
       <c r="B225" s="7"/>
       <c r="C225" s="7"/>
       <c r="D225" s="7"/>
@@ -8273,7 +8295,7 @@
       <c r="Z225" s="4"/>
     </row>
     <row r="226" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A226" s="78"/>
+      <c r="A226" s="75"/>
       <c r="B226" s="7"/>
       <c r="C226" s="7"/>
       <c r="D226" s="7"/>
@@ -8301,7 +8323,7 @@
       <c r="Z226" s="4"/>
     </row>
     <row r="227" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A227" s="78"/>
+      <c r="A227" s="75"/>
       <c r="B227" s="7"/>
       <c r="C227" s="7"/>
       <c r="D227" s="7"/>
@@ -8329,7 +8351,7 @@
       <c r="Z227" s="4"/>
     </row>
     <row r="228" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A228" s="78"/>
+      <c r="A228" s="75"/>
       <c r="B228" s="7"/>
       <c r="C228" s="7"/>
       <c r="D228" s="7"/>
@@ -8357,7 +8379,7 @@
       <c r="Z228" s="4"/>
     </row>
     <row r="229" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A229" s="78"/>
+      <c r="A229" s="75"/>
       <c r="B229" s="7"/>
       <c r="C229" s="7"/>
       <c r="D229" s="7"/>
@@ -8385,7 +8407,7 @@
       <c r="Z229" s="4"/>
     </row>
     <row r="230" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A230" s="78"/>
+      <c r="A230" s="75"/>
       <c r="B230" s="7"/>
       <c r="C230" s="7"/>
       <c r="D230" s="7"/>
@@ -8413,7 +8435,7 @@
       <c r="Z230" s="4"/>
     </row>
     <row r="231" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A231" s="78"/>
+      <c r="A231" s="75"/>
       <c r="B231" s="7"/>
       <c r="C231" s="7"/>
       <c r="D231" s="7"/>
@@ -8441,7 +8463,7 @@
       <c r="Z231" s="4"/>
     </row>
     <row r="232" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A232" s="78"/>
+      <c r="A232" s="75"/>
       <c r="B232" s="7"/>
       <c r="C232" s="7"/>
       <c r="D232" s="7"/>
@@ -8469,7 +8491,7 @@
       <c r="Z232" s="4"/>
     </row>
     <row r="233" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A233" s="78"/>
+      <c r="A233" s="75"/>
       <c r="B233" s="7"/>
       <c r="C233" s="7"/>
       <c r="D233" s="7"/>
@@ -8497,7 +8519,7 @@
       <c r="Z233" s="4"/>
     </row>
     <row r="234" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A234" s="78"/>
+      <c r="A234" s="75"/>
       <c r="B234" s="7"/>
       <c r="C234" s="7"/>
       <c r="D234" s="7"/>
@@ -8525,7 +8547,7 @@
       <c r="Z234" s="4"/>
     </row>
     <row r="235" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A235" s="78"/>
+      <c r="A235" s="75"/>
       <c r="B235" s="7"/>
       <c r="C235" s="7"/>
       <c r="D235" s="7"/>
@@ -8553,7 +8575,7 @@
       <c r="Z235" s="4"/>
     </row>
     <row r="236" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A236" s="78"/>
+      <c r="A236" s="75"/>
       <c r="B236" s="7"/>
       <c r="C236" s="7"/>
       <c r="D236" s="7"/>
@@ -8581,7 +8603,7 @@
       <c r="Z236" s="4"/>
     </row>
     <row r="237" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A237" s="78"/>
+      <c r="A237" s="75"/>
       <c r="B237" s="7"/>
       <c r="C237" s="7"/>
       <c r="D237" s="7"/>
@@ -8609,7 +8631,7 @@
       <c r="Z237" s="4"/>
     </row>
     <row r="238" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A238" s="78"/>
+      <c r="A238" s="75"/>
       <c r="B238" s="7"/>
       <c r="C238" s="7"/>
       <c r="D238" s="7"/>
@@ -8637,7 +8659,7 @@
       <c r="Z238" s="4"/>
     </row>
     <row r="239" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A239" s="78"/>
+      <c r="A239" s="75"/>
       <c r="B239" s="7"/>
       <c r="C239" s="7"/>
       <c r="D239" s="7"/>
@@ -8665,7 +8687,7 @@
       <c r="Z239" s="4"/>
     </row>
     <row r="240" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A240" s="78"/>
+      <c r="A240" s="75"/>
       <c r="B240" s="7"/>
       <c r="C240" s="7"/>
       <c r="D240" s="7"/>
@@ -8693,7 +8715,7 @@
       <c r="Z240" s="4"/>
     </row>
     <row r="241" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A241" s="78"/>
+      <c r="A241" s="75"/>
       <c r="B241" s="7"/>
       <c r="C241" s="7"/>
       <c r="D241" s="7"/>
@@ -8721,7 +8743,7 @@
       <c r="Z241" s="4"/>
     </row>
     <row r="242" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A242" s="78"/>
+      <c r="A242" s="75"/>
       <c r="B242" s="7"/>
       <c r="C242" s="7"/>
       <c r="D242" s="7"/>
@@ -8749,7 +8771,7 @@
       <c r="Z242" s="4"/>
     </row>
     <row r="243" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A243" s="78"/>
+      <c r="A243" s="75"/>
       <c r="B243" s="7"/>
       <c r="C243" s="7"/>
       <c r="D243" s="7"/>
@@ -8777,7 +8799,7 @@
       <c r="Z243" s="4"/>
     </row>
     <row r="244" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A244" s="78"/>
+      <c r="A244" s="75"/>
       <c r="B244" s="7"/>
       <c r="C244" s="7"/>
       <c r="D244" s="7"/>
@@ -8805,7 +8827,7 @@
       <c r="Z244" s="4"/>
     </row>
     <row r="245" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A245" s="78"/>
+      <c r="A245" s="75"/>
       <c r="B245" s="7"/>
       <c r="C245" s="7"/>
       <c r="D245" s="7"/>
@@ -8833,7 +8855,7 @@
       <c r="Z245" s="4"/>
     </row>
     <row r="246" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A246" s="78"/>
+      <c r="A246" s="75"/>
       <c r="B246" s="7"/>
       <c r="C246" s="7"/>
       <c r="D246" s="7"/>
@@ -8861,7 +8883,7 @@
       <c r="Z246" s="4"/>
     </row>
     <row r="247" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A247" s="78"/>
+      <c r="A247" s="75"/>
       <c r="B247" s="7"/>
       <c r="C247" s="7"/>
       <c r="D247" s="7"/>
@@ -8889,7 +8911,7 @@
       <c r="Z247" s="4"/>
     </row>
     <row r="248" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A248" s="78"/>
+      <c r="A248" s="75"/>
       <c r="B248" s="7"/>
       <c r="C248" s="7"/>
       <c r="D248" s="7"/>
@@ -8917,7 +8939,7 @@
       <c r="Z248" s="4"/>
     </row>
     <row r="249" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A249" s="78"/>
+      <c r="A249" s="75"/>
       <c r="B249" s="7"/>
       <c r="C249" s="7"/>
       <c r="D249" s="7"/>
@@ -8945,7 +8967,7 @@
       <c r="Z249" s="4"/>
     </row>
     <row r="250" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A250" s="78"/>
+      <c r="A250" s="75"/>
       <c r="B250" s="7"/>
       <c r="C250" s="7"/>
       <c r="D250" s="7"/>
@@ -8973,7 +8995,7 @@
       <c r="Z250" s="4"/>
     </row>
     <row r="251" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A251" s="78"/>
+      <c r="A251" s="75"/>
       <c r="B251" s="7"/>
       <c r="C251" s="7"/>
       <c r="D251" s="7"/>
@@ -9001,7 +9023,7 @@
       <c r="Z251" s="4"/>
     </row>
     <row r="252" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A252" s="78"/>
+      <c r="A252" s="75"/>
       <c r="B252" s="7"/>
       <c r="C252" s="7"/>
       <c r="D252" s="7"/>
@@ -9029,7 +9051,7 @@
       <c r="Z252" s="4"/>
     </row>
     <row r="253" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A253" s="78"/>
+      <c r="A253" s="75"/>
       <c r="B253" s="7"/>
       <c r="C253" s="7"/>
       <c r="D253" s="7"/>
@@ -9057,7 +9079,7 @@
       <c r="Z253" s="4"/>
     </row>
     <row r="254" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A254" s="78"/>
+      <c r="A254" s="75"/>
       <c r="B254" s="7"/>
       <c r="C254" s="7"/>
       <c r="D254" s="7"/>
@@ -9085,7 +9107,7 @@
       <c r="Z254" s="4"/>
     </row>
     <row r="255" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A255" s="78"/>
+      <c r="A255" s="75"/>
       <c r="B255" s="7"/>
       <c r="C255" s="7"/>
       <c r="D255" s="7"/>
@@ -9113,7 +9135,7 @@
       <c r="Z255" s="4"/>
     </row>
     <row r="256" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A256" s="78"/>
+      <c r="A256" s="75"/>
       <c r="B256" s="7"/>
       <c r="C256" s="7"/>
       <c r="D256" s="7"/>
@@ -9141,7 +9163,7 @@
       <c r="Z256" s="4"/>
     </row>
     <row r="257" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A257" s="78"/>
+      <c r="A257" s="75"/>
       <c r="B257" s="7"/>
       <c r="C257" s="7"/>
       <c r="D257" s="7"/>
@@ -9169,7 +9191,7 @@
       <c r="Z257" s="4"/>
     </row>
     <row r="258" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A258" s="78"/>
+      <c r="A258" s="75"/>
       <c r="B258" s="7"/>
       <c r="C258" s="7"/>
       <c r="D258" s="7"/>
@@ -9197,7 +9219,7 @@
       <c r="Z258" s="4"/>
     </row>
     <row r="259" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A259" s="78"/>
+      <c r="A259" s="75"/>
       <c r="B259" s="7"/>
       <c r="C259" s="7"/>
       <c r="D259" s="7"/>
@@ -9225,7 +9247,7 @@
       <c r="Z259" s="4"/>
     </row>
     <row r="260" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A260" s="78"/>
+      <c r="A260" s="75"/>
       <c r="B260" s="7"/>
       <c r="C260" s="7"/>
       <c r="D260" s="7"/>
@@ -9253,7 +9275,7 @@
       <c r="Z260" s="4"/>
     </row>
     <row r="261" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A261" s="78"/>
+      <c r="A261" s="75"/>
       <c r="B261" s="7"/>
       <c r="C261" s="7"/>
       <c r="D261" s="7"/>
@@ -9281,7 +9303,7 @@
       <c r="Z261" s="4"/>
     </row>
     <row r="262" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A262" s="78"/>
+      <c r="A262" s="75"/>
       <c r="B262" s="7"/>
       <c r="C262" s="7"/>
       <c r="D262" s="7"/>
@@ -9309,7 +9331,7 @@
       <c r="Z262" s="4"/>
     </row>
     <row r="263" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A263" s="78"/>
+      <c r="A263" s="75"/>
       <c r="B263" s="7"/>
       <c r="C263" s="7"/>
       <c r="D263" s="7"/>
@@ -9337,7 +9359,7 @@
       <c r="Z263" s="4"/>
     </row>
     <row r="264" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A264" s="78"/>
+      <c r="A264" s="75"/>
       <c r="B264" s="7"/>
       <c r="C264" s="7"/>
       <c r="D264" s="7"/>
@@ -9365,7 +9387,7 @@
       <c r="Z264" s="4"/>
     </row>
     <row r="265" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A265" s="78"/>
+      <c r="A265" s="75"/>
       <c r="B265" s="7"/>
       <c r="C265" s="7"/>
       <c r="D265" s="7"/>
@@ -9393,7 +9415,7 @@
       <c r="Z265" s="4"/>
     </row>
     <row r="266" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A266" s="78"/>
+      <c r="A266" s="75"/>
       <c r="B266" s="7"/>
       <c r="C266" s="7"/>
       <c r="D266" s="7"/>
@@ -9421,7 +9443,7 @@
       <c r="Z266" s="4"/>
     </row>
     <row r="267" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A267" s="78"/>
+      <c r="A267" s="75"/>
       <c r="B267" s="7"/>
       <c r="C267" s="7"/>
       <c r="D267" s="7"/>
@@ -9449,7 +9471,7 @@
       <c r="Z267" s="4"/>
     </row>
     <row r="268" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A268" s="78"/>
+      <c r="A268" s="75"/>
       <c r="B268" s="7"/>
       <c r="C268" s="7"/>
       <c r="D268" s="7"/>
@@ -9477,7 +9499,7 @@
       <c r="Z268" s="4"/>
     </row>
     <row r="269" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A269" s="78"/>
+      <c r="A269" s="75"/>
       <c r="B269" s="7"/>
       <c r="C269" s="7"/>
       <c r="D269" s="7"/>
@@ -9505,7 +9527,7 @@
       <c r="Z269" s="4"/>
     </row>
     <row r="270" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A270" s="78"/>
+      <c r="A270" s="75"/>
       <c r="B270" s="7"/>
       <c r="C270" s="7"/>
       <c r="D270" s="7"/>
@@ -9533,7 +9555,7 @@
       <c r="Z270" s="4"/>
     </row>
     <row r="271" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A271" s="78"/>
+      <c r="A271" s="75"/>
       <c r="B271" s="7"/>
       <c r="C271" s="7"/>
       <c r="D271" s="7"/>
@@ -9561,7 +9583,7 @@
       <c r="Z271" s="4"/>
     </row>
     <row r="272" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A272" s="78"/>
+      <c r="A272" s="75"/>
       <c r="B272" s="7"/>
       <c r="C272" s="7"/>
       <c r="D272" s="7"/>
@@ -9589,7 +9611,7 @@
       <c r="Z272" s="4"/>
     </row>
     <row r="273" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A273" s="78"/>
+      <c r="A273" s="75"/>
       <c r="B273" s="7"/>
       <c r="C273" s="7"/>
       <c r="D273" s="7"/>
@@ -9617,7 +9639,7 @@
       <c r="Z273" s="4"/>
     </row>
     <row r="274" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A274" s="78"/>
+      <c r="A274" s="75"/>
       <c r="B274" s="7"/>
       <c r="C274" s="7"/>
       <c r="D274" s="7"/>
@@ -9645,7 +9667,7 @@
       <c r="Z274" s="4"/>
     </row>
     <row r="275" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A275" s="78"/>
+      <c r="A275" s="75"/>
       <c r="B275" s="7"/>
       <c r="C275" s="7"/>
       <c r="D275" s="7"/>
@@ -9673,7 +9695,7 @@
       <c r="Z275" s="4"/>
     </row>
     <row r="276" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A276" s="78"/>
+      <c r="A276" s="75"/>
       <c r="B276" s="7"/>
       <c r="C276" s="7"/>
       <c r="D276" s="7"/>
@@ -9701,7 +9723,7 @@
       <c r="Z276" s="4"/>
     </row>
     <row r="277" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A277" s="78"/>
+      <c r="A277" s="75"/>
       <c r="B277" s="7"/>
       <c r="C277" s="7"/>
       <c r="D277" s="7"/>
@@ -9729,7 +9751,7 @@
       <c r="Z277" s="4"/>
     </row>
     <row r="278" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A278" s="78"/>
+      <c r="A278" s="75"/>
       <c r="B278" s="7"/>
       <c r="C278" s="7"/>
       <c r="D278" s="7"/>
@@ -9757,7 +9779,7 @@
       <c r="Z278" s="4"/>
     </row>
     <row r="279" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A279" s="78"/>
+      <c r="A279" s="75"/>
       <c r="B279" s="7"/>
       <c r="C279" s="7"/>
       <c r="D279" s="7"/>
@@ -9785,7 +9807,7 @@
       <c r="Z279" s="4"/>
     </row>
     <row r="280" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A280" s="78"/>
+      <c r="A280" s="75"/>
       <c r="B280" s="7"/>
       <c r="C280" s="7"/>
       <c r="D280" s="7"/>
@@ -9813,7 +9835,7 @@
       <c r="Z280" s="4"/>
     </row>
     <row r="281" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A281" s="78"/>
+      <c r="A281" s="75"/>
       <c r="B281" s="7"/>
       <c r="C281" s="7"/>
       <c r="D281" s="7"/>
@@ -9841,7 +9863,7 @@
       <c r="Z281" s="4"/>
     </row>
     <row r="282" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A282" s="78"/>
+      <c r="A282" s="75"/>
       <c r="B282" s="7"/>
       <c r="C282" s="7"/>
       <c r="D282" s="7"/>
@@ -9869,7 +9891,7 @@
       <c r="Z282" s="4"/>
     </row>
     <row r="283" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A283" s="78"/>
+      <c r="A283" s="75"/>
       <c r="B283" s="7"/>
       <c r="C283" s="7"/>
       <c r="D283" s="7"/>
@@ -9897,7 +9919,7 @@
       <c r="Z283" s="4"/>
     </row>
     <row r="284" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A284" s="78"/>
+      <c r="A284" s="75"/>
       <c r="B284" s="7"/>
       <c r="C284" s="7"/>
       <c r="D284" s="7"/>
@@ -9925,7 +9947,7 @@
       <c r="Z284" s="4"/>
     </row>
     <row r="285" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A285" s="78"/>
+      <c r="A285" s="75"/>
       <c r="B285" s="7"/>
       <c r="C285" s="7"/>
       <c r="D285" s="7"/>
@@ -9953,7 +9975,7 @@
       <c r="Z285" s="4"/>
     </row>
     <row r="286" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A286" s="78"/>
+      <c r="A286" s="75"/>
       <c r="B286" s="7"/>
       <c r="C286" s="7"/>
       <c r="D286" s="7"/>
@@ -9981,7 +10003,7 @@
       <c r="Z286" s="4"/>
     </row>
     <row r="287" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A287" s="78"/>
+      <c r="A287" s="75"/>
       <c r="B287" s="7"/>
       <c r="C287" s="7"/>
       <c r="D287" s="7"/>
@@ -10009,7 +10031,7 @@
       <c r="Z287" s="4"/>
     </row>
     <row r="288" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A288" s="78"/>
+      <c r="A288" s="75"/>
       <c r="B288" s="7"/>
       <c r="C288" s="7"/>
       <c r="D288" s="7"/>
@@ -10037,7 +10059,7 @@
       <c r="Z288" s="4"/>
     </row>
     <row r="289" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A289" s="78"/>
+      <c r="A289" s="75"/>
       <c r="B289" s="7"/>
       <c r="C289" s="7"/>
       <c r="D289" s="7"/>
@@ -10065,7 +10087,7 @@
       <c r="Z289" s="4"/>
     </row>
     <row r="290" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A290" s="78"/>
+      <c r="A290" s="75"/>
       <c r="B290" s="7"/>
       <c r="C290" s="7"/>
       <c r="D290" s="7"/>
@@ -10093,7 +10115,7 @@
       <c r="Z290" s="4"/>
     </row>
     <row r="291" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A291" s="78"/>
+      <c r="A291" s="75"/>
       <c r="B291" s="7"/>
       <c r="C291" s="7"/>
       <c r="D291" s="7"/>
@@ -10121,7 +10143,7 @@
       <c r="Z291" s="4"/>
     </row>
     <row r="292" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A292" s="78"/>
+      <c r="A292" s="75"/>
       <c r="B292" s="7"/>
       <c r="C292" s="7"/>
       <c r="D292" s="7"/>
@@ -10149,7 +10171,7 @@
       <c r="Z292" s="4"/>
     </row>
     <row r="293" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A293" s="78"/>
+      <c r="A293" s="75"/>
       <c r="B293" s="7"/>
       <c r="C293" s="7"/>
       <c r="D293" s="7"/>
@@ -10177,7 +10199,7 @@
       <c r="Z293" s="4"/>
     </row>
     <row r="294" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A294" s="78"/>
+      <c r="A294" s="75"/>
       <c r="B294" s="7"/>
       <c r="C294" s="7"/>
       <c r="D294" s="7"/>
@@ -10205,7 +10227,7 @@
       <c r="Z294" s="4"/>
     </row>
     <row r="295" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A295" s="78"/>
+      <c r="A295" s="75"/>
       <c r="B295" s="7"/>
       <c r="C295" s="7"/>
       <c r="D295" s="7"/>
@@ -10233,7 +10255,7 @@
       <c r="Z295" s="4"/>
     </row>
     <row r="296" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A296" s="78"/>
+      <c r="A296" s="75"/>
       <c r="B296" s="7"/>
       <c r="C296" s="7"/>
       <c r="D296" s="7"/>
@@ -10261,7 +10283,7 @@
       <c r="Z296" s="4"/>
     </row>
     <row r="297" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A297" s="78"/>
+      <c r="A297" s="75"/>
       <c r="B297" s="7"/>
       <c r="C297" s="7"/>
       <c r="D297" s="7"/>
@@ -10289,7 +10311,7 @@
       <c r="Z297" s="4"/>
     </row>
     <row r="298" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A298" s="78"/>
+      <c r="A298" s="75"/>
       <c r="B298" s="7"/>
       <c r="C298" s="7"/>
       <c r="D298" s="7"/>
@@ -10317,7 +10339,7 @@
       <c r="Z298" s="4"/>
     </row>
     <row r="299" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A299" s="78"/>
+      <c r="A299" s="75"/>
       <c r="B299" s="7"/>
       <c r="C299" s="7"/>
       <c r="D299" s="7"/>
@@ -10345,7 +10367,7 @@
       <c r="Z299" s="4"/>
     </row>
     <row r="300" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A300" s="78"/>
+      <c r="A300" s="75"/>
       <c r="B300" s="7"/>
       <c r="C300" s="7"/>
       <c r="D300" s="7"/>
@@ -10373,7 +10395,7 @@
       <c r="Z300" s="4"/>
     </row>
     <row r="301" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A301" s="78"/>
+      <c r="A301" s="75"/>
       <c r="B301" s="7"/>
       <c r="C301" s="7"/>
       <c r="D301" s="7"/>
@@ -10401,7 +10423,7 @@
       <c r="Z301" s="4"/>
     </row>
     <row r="302" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A302" s="78"/>
+      <c r="A302" s="75"/>
       <c r="B302" s="7"/>
       <c r="C302" s="7"/>
       <c r="D302" s="7"/>
@@ -10429,7 +10451,7 @@
       <c r="Z302" s="4"/>
     </row>
     <row r="303" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A303" s="78"/>
+      <c r="A303" s="75"/>
       <c r="B303" s="7"/>
       <c r="C303" s="7"/>
       <c r="D303" s="7"/>
@@ -10457,7 +10479,7 @@
       <c r="Z303" s="4"/>
     </row>
     <row r="304" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A304" s="78"/>
+      <c r="A304" s="75"/>
       <c r="B304" s="7"/>
       <c r="C304" s="7"/>
       <c r="D304" s="7"/>
@@ -10485,7 +10507,7 @@
       <c r="Z304" s="4"/>
     </row>
     <row r="305" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A305" s="78"/>
+      <c r="A305" s="75"/>
       <c r="B305" s="7"/>
       <c r="C305" s="7"/>
       <c r="D305" s="7"/>
@@ -10513,7 +10535,7 @@
       <c r="Z305" s="4"/>
     </row>
     <row r="306" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A306" s="78"/>
+      <c r="A306" s="75"/>
       <c r="B306" s="7"/>
       <c r="C306" s="7"/>
       <c r="D306" s="7"/>
@@ -10541,7 +10563,7 @@
       <c r="Z306" s="4"/>
     </row>
     <row r="307" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A307" s="78"/>
+      <c r="A307" s="75"/>
       <c r="B307" s="7"/>
       <c r="C307" s="7"/>
       <c r="D307" s="7"/>
@@ -10569,7 +10591,7 @@
       <c r="Z307" s="4"/>
     </row>
     <row r="308" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A308" s="78"/>
+      <c r="A308" s="75"/>
       <c r="B308" s="7"/>
       <c r="C308" s="7"/>
       <c r="D308" s="7"/>
@@ -10597,7 +10619,7 @@
       <c r="Z308" s="4"/>
     </row>
     <row r="309" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A309" s="78"/>
+      <c r="A309" s="75"/>
       <c r="B309" s="7"/>
       <c r="C309" s="7"/>
       <c r="D309" s="7"/>
@@ -10625,7 +10647,7 @@
       <c r="Z309" s="4"/>
     </row>
     <row r="310" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A310" s="78"/>
+      <c r="A310" s="75"/>
       <c r="B310" s="7"/>
       <c r="C310" s="7"/>
       <c r="D310" s="7"/>
@@ -10653,7 +10675,7 @@
       <c r="Z310" s="4"/>
     </row>
     <row r="311" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A311" s="78"/>
+      <c r="A311" s="75"/>
       <c r="B311" s="7"/>
       <c r="C311" s="7"/>
       <c r="D311" s="7"/>
@@ -10681,7 +10703,7 @@
       <c r="Z311" s="4"/>
     </row>
     <row r="312" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A312" s="78"/>
+      <c r="A312" s="75"/>
       <c r="B312" s="7"/>
       <c r="C312" s="7"/>
       <c r="D312" s="7"/>
@@ -10709,7 +10731,7 @@
       <c r="Z312" s="4"/>
     </row>
     <row r="313" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A313" s="78"/>
+      <c r="A313" s="75"/>
       <c r="B313" s="7"/>
       <c r="C313" s="7"/>
       <c r="D313" s="7"/>
@@ -10737,7 +10759,7 @@
       <c r="Z313" s="4"/>
     </row>
     <row r="314" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A314" s="78"/>
+      <c r="A314" s="75"/>
       <c r="B314" s="7"/>
       <c r="C314" s="7"/>
       <c r="D314" s="7"/>
@@ -10765,12 +10787,12 @@
       <c r="Z314" s="4"/>
     </row>
     <row r="315" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A315" s="79"/>
-      <c r="B315" s="80"/>
-      <c r="C315" s="80"/>
-      <c r="D315" s="80"/>
-      <c r="E315" s="80"/>
-      <c r="F315" s="80"/>
+      <c r="A315" s="76"/>
+      <c r="B315" s="77"/>
+      <c r="C315" s="77"/>
+      <c r="D315" s="77"/>
+      <c r="E315" s="77"/>
+      <c r="F315" s="77"/>
       <c r="G315" s="1"/>
       <c r="H315" s="1"/>
       <c r="I315" s="1"/>
@@ -10793,12 +10815,12 @@
       <c r="Z315" s="4"/>
     </row>
     <row r="316" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A316" s="79"/>
-      <c r="B316" s="80"/>
-      <c r="C316" s="80"/>
-      <c r="D316" s="80"/>
-      <c r="E316" s="80"/>
-      <c r="F316" s="80"/>
+      <c r="A316" s="76"/>
+      <c r="B316" s="77"/>
+      <c r="C316" s="77"/>
+      <c r="D316" s="77"/>
+      <c r="E316" s="77"/>
+      <c r="F316" s="77"/>
       <c r="G316" s="1"/>
       <c r="H316" s="1"/>
       <c r="I316" s="1"/>
@@ -10821,16 +10843,16 @@
       <c r="Z316" s="4"/>
     </row>
     <row r="317" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A317" s="81"/>
-      <c r="B317" s="82"/>
+      <c r="A317" s="78"/>
+      <c r="B317" s="79"/>
       <c r="C317" s="4"/>
       <c r="D317" s="4"/>
       <c r="E317" s="4"/>
       <c r="F317" s="4"/>
-      <c r="G317" s="83"/>
-      <c r="H317" s="83"/>
-      <c r="I317" s="83"/>
-      <c r="J317" s="83"/>
+      <c r="G317" s="80"/>
+      <c r="H317" s="80"/>
+      <c r="I317" s="80"/>
+      <c r="J317" s="80"/>
       <c r="K317" s="4"/>
       <c r="L317" s="4"/>
       <c r="M317" s="4"/>
@@ -10849,16 +10871,16 @@
       <c r="Z317" s="4"/>
     </row>
     <row r="318" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A318" s="81"/>
-      <c r="B318" s="82"/>
+      <c r="A318" s="78"/>
+      <c r="B318" s="79"/>
       <c r="C318" s="4"/>
       <c r="D318" s="4"/>
       <c r="E318" s="4"/>
       <c r="F318" s="4"/>
-      <c r="G318" s="83"/>
-      <c r="H318" s="83"/>
-      <c r="I318" s="83"/>
-      <c r="J318" s="83"/>
+      <c r="G318" s="80"/>
+      <c r="H318" s="80"/>
+      <c r="I318" s="80"/>
+      <c r="J318" s="80"/>
       <c r="K318" s="4"/>
       <c r="L318" s="4"/>
       <c r="M318" s="4"/>
@@ -10877,16 +10899,16 @@
       <c r="Z318" s="4"/>
     </row>
     <row r="319" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A319" s="81"/>
-      <c r="B319" s="82"/>
+      <c r="A319" s="78"/>
+      <c r="B319" s="79"/>
       <c r="C319" s="4"/>
       <c r="D319" s="4"/>
       <c r="E319" s="4"/>
       <c r="F319" s="4"/>
-      <c r="G319" s="83"/>
-      <c r="H319" s="83"/>
-      <c r="I319" s="83"/>
-      <c r="J319" s="83"/>
+      <c r="G319" s="80"/>
+      <c r="H319" s="80"/>
+      <c r="I319" s="80"/>
+      <c r="J319" s="80"/>
       <c r="K319" s="4"/>
       <c r="L319" s="4"/>
       <c r="M319" s="4"/>
@@ -10905,16 +10927,16 @@
       <c r="Z319" s="4"/>
     </row>
     <row r="320" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A320" s="81"/>
-      <c r="B320" s="82"/>
+      <c r="A320" s="78"/>
+      <c r="B320" s="79"/>
       <c r="C320" s="4"/>
       <c r="D320" s="4"/>
       <c r="E320" s="4"/>
       <c r="F320" s="4"/>
-      <c r="G320" s="83"/>
-      <c r="H320" s="83"/>
-      <c r="I320" s="83"/>
-      <c r="J320" s="83"/>
+      <c r="G320" s="80"/>
+      <c r="H320" s="80"/>
+      <c r="I320" s="80"/>
+      <c r="J320" s="80"/>
       <c r="K320" s="4"/>
       <c r="L320" s="4"/>
       <c r="M320" s="4"/>
@@ -10933,16 +10955,16 @@
       <c r="Z320" s="4"/>
     </row>
     <row r="321" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A321" s="81"/>
-      <c r="B321" s="82"/>
+      <c r="A321" s="78"/>
+      <c r="B321" s="79"/>
       <c r="C321" s="4"/>
       <c r="D321" s="4"/>
       <c r="E321" s="4"/>
       <c r="F321" s="4"/>
-      <c r="G321" s="83"/>
-      <c r="H321" s="83"/>
-      <c r="I321" s="83"/>
-      <c r="J321" s="83"/>
+      <c r="G321" s="80"/>
+      <c r="H321" s="80"/>
+      <c r="I321" s="80"/>
+      <c r="J321" s="80"/>
       <c r="K321" s="4"/>
       <c r="L321" s="4"/>
       <c r="M321" s="4"/>
@@ -10961,16 +10983,16 @@
       <c r="Z321" s="4"/>
     </row>
     <row r="322" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A322" s="81"/>
-      <c r="B322" s="82"/>
+      <c r="A322" s="78"/>
+      <c r="B322" s="79"/>
       <c r="C322" s="4"/>
       <c r="D322" s="4"/>
       <c r="E322" s="4"/>
       <c r="F322" s="4"/>
-      <c r="G322" s="83"/>
-      <c r="H322" s="83"/>
-      <c r="I322" s="83"/>
-      <c r="J322" s="83"/>
+      <c r="G322" s="80"/>
+      <c r="H322" s="80"/>
+      <c r="I322" s="80"/>
+      <c r="J322" s="80"/>
       <c r="K322" s="4"/>
       <c r="L322" s="4"/>
       <c r="M322" s="4"/>
@@ -15058,26 +15080,6 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="A26:F26"/>
-    <mergeCell ref="A35:F35"/>
-    <mergeCell ref="A47:F47"/>
-    <mergeCell ref="A50:F50"/>
-    <mergeCell ref="G5:J6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A53:F53"/>
-    <mergeCell ref="A66:F66"/>
-    <mergeCell ref="A67:F67"/>
-    <mergeCell ref="A72:F72"/>
-    <mergeCell ref="A79:F79"/>
     <mergeCell ref="A110:F110"/>
     <mergeCell ref="C122:D122"/>
     <mergeCell ref="A126:B126"/>
@@ -15090,6 +15092,26 @@
     <mergeCell ref="A105:F105"/>
     <mergeCell ref="A106:F106"/>
     <mergeCell ref="C118:F118"/>
+    <mergeCell ref="A53:F53"/>
+    <mergeCell ref="A66:F66"/>
+    <mergeCell ref="A67:F67"/>
+    <mergeCell ref="A72:F72"/>
+    <mergeCell ref="A79:F79"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="A50:F50"/>
+    <mergeCell ref="G5:J6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="F5:F6"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="46" fitToHeight="0" orientation="portrait" r:id="rId1"/>

--- a/public/DOST_Performance_Template.xlsx
+++ b/public/DOST_Performance_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\do-performance-monitoring\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2A74DDB-EA41-4EE1-9F41-6D5EDB96DB43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E11D9AA-0C02-4F08-9DA6-73067D6B7789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -438,7 +438,7 @@
     <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@"/>
     <numFmt numFmtId="167" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@"/>
   </numFmts>
-  <fonts count="34">
+  <fonts count="36">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -627,16 +627,30 @@
       <family val="2"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color theme="0" tint="-0.34998626667073579"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color theme="0" tint="-0.34998626667073579"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -951,7 +965,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="134">
+  <cellXfs count="137">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1174,44 +1188,48 @@
     <xf numFmtId="0" fontId="24" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="4" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="167" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1227,49 +1245,50 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1557,12 +1576,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="75.75" customHeight="1">
-      <c r="A1" s="90"/>
-      <c r="B1" s="91"/>
-      <c r="C1" s="91"/>
-      <c r="D1" s="91"/>
-      <c r="E1" s="91"/>
-      <c r="F1" s="91"/>
+      <c r="A1" s="124"/>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
+      <c r="D1" s="105"/>
+      <c r="E1" s="105"/>
+      <c r="F1" s="105"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
@@ -1585,14 +1604,14 @@
       <c r="Z1" s="4"/>
     </row>
     <row r="2" spans="1:26" ht="18">
-      <c r="A2" s="92" t="s">
+      <c r="A2" s="125" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="91"/>
-      <c r="C2" s="91"/>
-      <c r="D2" s="91"/>
-      <c r="E2" s="91"/>
-      <c r="F2" s="91"/>
+      <c r="B2" s="105"/>
+      <c r="C2" s="105"/>
+      <c r="D2" s="105"/>
+      <c r="E2" s="105"/>
+      <c r="F2" s="105"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -1615,14 +1634,14 @@
       <c r="Z2" s="4"/>
     </row>
     <row r="3" spans="1:26" ht="18">
-      <c r="A3" s="92" t="s">
+      <c r="A3" s="125" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="91"/>
-      <c r="C3" s="91"/>
-      <c r="D3" s="91"/>
-      <c r="E3" s="91"/>
-      <c r="F3" s="91"/>
+      <c r="B3" s="105"/>
+      <c r="C3" s="105"/>
+      <c r="D3" s="105"/>
+      <c r="E3" s="105"/>
+      <c r="F3" s="105"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
@@ -1673,22 +1692,22 @@
       <c r="Z4" s="4"/>
     </row>
     <row r="5" spans="1:26" ht="20.399999999999999">
-      <c r="A5" s="93" t="s">
+      <c r="A5" s="126" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="95" t="s">
+      <c r="B5" s="128" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="96"/>
-      <c r="D5" s="96"/>
-      <c r="E5" s="97"/>
-      <c r="F5" s="98" t="s">
+      <c r="C5" s="100"/>
+      <c r="D5" s="100"/>
+      <c r="E5" s="101"/>
+      <c r="F5" s="129" t="s">
         <v>4</v>
       </c>
-      <c r="G5" s="100"/>
-      <c r="H5" s="91"/>
-      <c r="I5" s="91"/>
-      <c r="J5" s="91"/>
+      <c r="G5" s="120"/>
+      <c r="H5" s="105"/>
+      <c r="I5" s="105"/>
+      <c r="J5" s="105"/>
       <c r="K5" s="9"/>
       <c r="L5" s="10"/>
       <c r="M5" s="4"/>
@@ -1707,7 +1726,7 @@
       <c r="Z5" s="4"/>
     </row>
     <row r="6" spans="1:26" ht="21" customHeight="1">
-      <c r="A6" s="94"/>
+      <c r="A6" s="127"/>
       <c r="B6" s="11" t="s">
         <v>5</v>
       </c>
@@ -1720,11 +1739,11 @@
       <c r="E6" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="94"/>
-      <c r="G6" s="91"/>
-      <c r="H6" s="91"/>
-      <c r="I6" s="91"/>
-      <c r="J6" s="91"/>
+      <c r="F6" s="127"/>
+      <c r="G6" s="105"/>
+      <c r="H6" s="105"/>
+      <c r="I6" s="105"/>
+      <c r="J6" s="105"/>
       <c r="K6" s="9"/>
       <c r="L6" s="10"/>
       <c r="M6" s="4"/>
@@ -1743,14 +1762,14 @@
       <c r="Z6" s="4"/>
     </row>
     <row r="7" spans="1:26" ht="21" customHeight="1">
-      <c r="A7" s="101" t="s">
+      <c r="A7" s="108" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="96"/>
-      <c r="C7" s="96"/>
-      <c r="D7" s="96"/>
-      <c r="E7" s="96"/>
-      <c r="F7" s="97"/>
+      <c r="B7" s="100"/>
+      <c r="C7" s="100"/>
+      <c r="D7" s="100"/>
+      <c r="E7" s="100"/>
+      <c r="F7" s="101"/>
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
@@ -1773,14 +1792,14 @@
       <c r="Z7" s="4"/>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A8" s="102" t="s">
+      <c r="A8" s="121" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="103"/>
-      <c r="C8" s="103"/>
-      <c r="D8" s="103"/>
-      <c r="E8" s="103"/>
-      <c r="F8" s="104"/>
+      <c r="B8" s="122"/>
+      <c r="C8" s="122"/>
+      <c r="D8" s="122"/>
+      <c r="E8" s="122"/>
+      <c r="F8" s="123"/>
       <c r="G8" s="8"/>
       <c r="H8" s="8"/>
       <c r="I8" s="8"/>
@@ -1803,14 +1822,14 @@
       <c r="Z8" s="4"/>
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A9" s="105" t="s">
+      <c r="A9" s="109" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="96"/>
-      <c r="C9" s="96"/>
-      <c r="D9" s="96"/>
-      <c r="E9" s="96"/>
-      <c r="F9" s="97"/>
+      <c r="B9" s="100"/>
+      <c r="C9" s="100"/>
+      <c r="D9" s="100"/>
+      <c r="E9" s="100"/>
+      <c r="F9" s="101"/>
       <c r="G9" s="8"/>
       <c r="H9" s="8"/>
       <c r="I9" s="8"/>
@@ -1833,14 +1852,14 @@
       <c r="Z9" s="4"/>
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A10" s="99" t="s">
+      <c r="A10" s="119" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="96"/>
-      <c r="C10" s="96"/>
-      <c r="D10" s="96"/>
-      <c r="E10" s="96"/>
-      <c r="F10" s="97"/>
+      <c r="B10" s="100"/>
+      <c r="C10" s="100"/>
+      <c r="D10" s="100"/>
+      <c r="E10" s="100"/>
+      <c r="F10" s="101"/>
       <c r="G10" s="8"/>
       <c r="H10" s="8"/>
       <c r="I10" s="8"/>
@@ -1871,10 +1890,10 @@
       <c r="D11" s="14"/>
       <c r="E11" s="14"/>
       <c r="F11" s="15"/>
-      <c r="G11" s="121" t="s">
+      <c r="G11" s="130" t="s">
         <v>121</v>
       </c>
-      <c r="H11" s="122"/>
+      <c r="H11" s="90"/>
       <c r="I11" s="8"/>
       <c r="J11" s="12"/>
       <c r="K11" s="9"/>
@@ -1903,10 +1922,10 @@
       <c r="D12" s="17"/>
       <c r="E12" s="17"/>
       <c r="F12" s="18"/>
-      <c r="G12" s="121" t="s">
+      <c r="G12" s="130" t="s">
         <v>113</v>
       </c>
-      <c r="H12" s="122"/>
+      <c r="H12" s="90"/>
       <c r="I12" s="8"/>
       <c r="J12" s="12"/>
       <c r="K12" s="9"/>
@@ -1935,10 +1954,10 @@
       <c r="D13" s="19"/>
       <c r="E13" s="19"/>
       <c r="F13" s="18"/>
-      <c r="G13" s="121" t="s">
+      <c r="G13" s="130" t="s">
         <v>114</v>
       </c>
-      <c r="H13" s="122"/>
+      <c r="H13" s="90"/>
       <c r="I13" s="8"/>
       <c r="J13" s="12"/>
       <c r="K13" s="9"/>
@@ -1967,10 +1986,10 @@
       <c r="D14" s="14"/>
       <c r="E14" s="14"/>
       <c r="F14" s="18"/>
-      <c r="G14" s="121" t="s">
+      <c r="G14" s="130" t="s">
         <v>121</v>
       </c>
-      <c r="H14" s="122"/>
+      <c r="H14" s="90"/>
       <c r="I14" s="8"/>
       <c r="J14" s="12"/>
       <c r="K14" s="9"/>
@@ -1999,10 +2018,10 @@
       <c r="D15" s="21"/>
       <c r="E15" s="20"/>
       <c r="F15" s="18"/>
-      <c r="G15" s="121" t="s">
+      <c r="G15" s="130" t="s">
         <v>115</v>
       </c>
-      <c r="H15" s="122"/>
+      <c r="H15" s="90"/>
       <c r="I15" s="8"/>
       <c r="J15" s="12"/>
       <c r="K15" s="9"/>
@@ -2031,10 +2050,10 @@
       <c r="D16" s="22"/>
       <c r="E16" s="22"/>
       <c r="F16" s="18"/>
-      <c r="G16" s="121" t="s">
+      <c r="G16" s="130" t="s">
         <v>116</v>
       </c>
-      <c r="H16" s="123"/>
+      <c r="H16" s="91"/>
       <c r="I16" s="8"/>
       <c r="J16" s="12"/>
       <c r="K16" s="9"/>
@@ -2063,10 +2082,10 @@
       <c r="D17" s="24"/>
       <c r="E17" s="24"/>
       <c r="F17" s="18"/>
-      <c r="G17" s="121" t="s">
+      <c r="G17" s="130" t="s">
         <v>121</v>
       </c>
-      <c r="H17" s="122"/>
+      <c r="H17" s="90"/>
       <c r="I17" s="8"/>
       <c r="J17" s="12"/>
       <c r="K17" s="9"/>
@@ -2095,10 +2114,10 @@
       <c r="D18" s="26"/>
       <c r="E18" s="26"/>
       <c r="F18" s="18"/>
-      <c r="G18" s="121" t="s">
+      <c r="G18" s="130" t="s">
         <v>119</v>
       </c>
-      <c r="H18" s="122"/>
+      <c r="H18" s="90"/>
       <c r="I18" s="27"/>
       <c r="J18" s="27"/>
       <c r="K18" s="28"/>
@@ -2127,10 +2146,10 @@
       <c r="D19" s="26"/>
       <c r="E19" s="26"/>
       <c r="F19" s="18"/>
-      <c r="G19" s="121" t="s">
+      <c r="G19" s="130" t="s">
         <v>117</v>
       </c>
-      <c r="H19" s="122"/>
+      <c r="H19" s="90"/>
       <c r="I19" s="27"/>
       <c r="J19" s="27"/>
       <c r="K19" s="28"/>
@@ -2159,10 +2178,10 @@
       <c r="D20" s="26"/>
       <c r="E20" s="26"/>
       <c r="F20" s="18"/>
-      <c r="G20" s="121" t="s">
+      <c r="G20" s="130" t="s">
         <v>118</v>
       </c>
-      <c r="H20" s="124"/>
+      <c r="H20" s="92"/>
       <c r="I20" s="31"/>
       <c r="J20" s="32"/>
       <c r="K20" s="33"/>
@@ -2191,10 +2210,10 @@
       <c r="D21" s="34"/>
       <c r="E21" s="34"/>
       <c r="F21" s="18"/>
-      <c r="G21" s="121" t="s">
+      <c r="G21" s="130" t="s">
         <v>120</v>
       </c>
-      <c r="H21" s="125"/>
+      <c r="H21" s="93"/>
       <c r="I21" s="1"/>
       <c r="J21" s="2"/>
       <c r="K21" s="3"/>
@@ -2223,10 +2242,10 @@
       <c r="D22" s="36"/>
       <c r="E22" s="36"/>
       <c r="F22" s="18"/>
-      <c r="G22" s="121" t="s">
+      <c r="G22" s="130" t="s">
         <v>22</v>
       </c>
-      <c r="H22" s="126"/>
+      <c r="H22" s="94"/>
       <c r="I22" s="1"/>
       <c r="J22" s="2"/>
       <c r="K22" s="3"/>
@@ -2255,10 +2274,10 @@
       <c r="D23" s="36"/>
       <c r="E23" s="36"/>
       <c r="F23" s="18"/>
-      <c r="G23" s="121" t="s">
+      <c r="G23" s="130" t="s">
         <v>23</v>
       </c>
-      <c r="H23" s="126"/>
+      <c r="H23" s="94"/>
       <c r="I23" s="1"/>
       <c r="J23" s="2"/>
       <c r="K23" s="3"/>
@@ -2287,10 +2306,10 @@
       <c r="D24" s="36"/>
       <c r="E24" s="38"/>
       <c r="F24" s="39"/>
-      <c r="G24" s="121" t="s">
+      <c r="G24" s="130" t="s">
         <v>24</v>
       </c>
-      <c r="H24" s="126"/>
+      <c r="H24" s="94"/>
       <c r="I24" s="1"/>
       <c r="J24" s="2"/>
       <c r="K24" s="3"/>
@@ -2319,10 +2338,10 @@
       <c r="D25" s="36"/>
       <c r="E25" s="38"/>
       <c r="F25" s="39"/>
-      <c r="G25" s="121" t="s">
+      <c r="G25" s="130" t="s">
         <v>25</v>
       </c>
-      <c r="H25" s="126"/>
+      <c r="H25" s="94"/>
       <c r="I25" s="1"/>
       <c r="J25" s="2"/>
       <c r="K25" s="3"/>
@@ -2343,18 +2362,18 @@
       <c r="Z25" s="4"/>
     </row>
     <row r="26" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A26" s="99" t="s">
+      <c r="A26" s="119" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="96"/>
-      <c r="C26" s="96"/>
-      <c r="D26" s="96"/>
-      <c r="E26" s="96"/>
-      <c r="F26" s="97"/>
-      <c r="G26" s="121" t="s">
+      <c r="B26" s="100"/>
+      <c r="C26" s="100"/>
+      <c r="D26" s="100"/>
+      <c r="E26" s="100"/>
+      <c r="F26" s="101"/>
+      <c r="G26" s="130" t="s">
         <v>121</v>
       </c>
-      <c r="H26" s="126"/>
+      <c r="H26" s="94"/>
       <c r="I26" s="1"/>
       <c r="J26" s="2"/>
       <c r="K26" s="3"/>
@@ -2383,10 +2402,10 @@
       <c r="D27" s="41"/>
       <c r="E27" s="41"/>
       <c r="F27" s="42"/>
-      <c r="G27" s="121" t="s">
+      <c r="G27" s="130" t="s">
         <v>121</v>
       </c>
-      <c r="H27" s="126"/>
+      <c r="H27" s="94"/>
       <c r="I27" s="1"/>
       <c r="J27" s="2"/>
       <c r="K27" s="3"/>
@@ -2415,10 +2434,10 @@
       <c r="D28" s="34"/>
       <c r="E28" s="34"/>
       <c r="F28" s="18"/>
-      <c r="G28" s="121" t="s">
+      <c r="G28" s="130" t="s">
         <v>28</v>
       </c>
-      <c r="H28" s="126"/>
+      <c r="H28" s="94"/>
       <c r="I28" s="1"/>
       <c r="J28" s="43"/>
       <c r="K28" s="3"/>
@@ -2447,10 +2466,10 @@
       <c r="D29" s="34"/>
       <c r="E29" s="34"/>
       <c r="F29" s="18"/>
-      <c r="G29" s="121" t="s">
+      <c r="G29" s="130" t="s">
         <v>122</v>
       </c>
-      <c r="H29" s="126"/>
+      <c r="H29" s="94"/>
       <c r="I29" s="35"/>
       <c r="J29" s="2"/>
       <c r="K29" s="3"/>
@@ -2479,10 +2498,10 @@
       <c r="D30" s="34"/>
       <c r="E30" s="34"/>
       <c r="F30" s="18"/>
-      <c r="G30" s="121" t="s">
+      <c r="G30" s="130" t="s">
         <v>30</v>
       </c>
-      <c r="H30" s="126"/>
+      <c r="H30" s="94"/>
       <c r="I30" s="1"/>
       <c r="J30" s="2"/>
       <c r="K30" s="3"/>
@@ -2511,10 +2530,10 @@
       <c r="D31" s="44"/>
       <c r="E31" s="44"/>
       <c r="F31" s="18"/>
-      <c r="G31" s="121" t="s">
+      <c r="G31" s="130" t="s">
         <v>121</v>
       </c>
-      <c r="H31" s="126"/>
+      <c r="H31" s="94"/>
       <c r="I31" s="1"/>
       <c r="J31" s="2"/>
       <c r="K31" s="3"/>
@@ -2543,10 +2562,10 @@
       <c r="D32" s="34"/>
       <c r="E32" s="34"/>
       <c r="F32" s="18"/>
-      <c r="G32" s="121" t="s">
+      <c r="G32" s="130" t="s">
         <v>32</v>
       </c>
-      <c r="H32" s="126"/>
+      <c r="H32" s="94"/>
       <c r="I32" s="1"/>
       <c r="J32" s="2"/>
       <c r="K32" s="3"/>
@@ -2575,10 +2594,10 @@
       <c r="D33" s="34"/>
       <c r="E33" s="34"/>
       <c r="F33" s="18"/>
-      <c r="G33" s="121" t="s">
+      <c r="G33" s="130" t="s">
         <v>123</v>
       </c>
-      <c r="H33" s="126"/>
+      <c r="H33" s="94"/>
       <c r="I33" s="1"/>
       <c r="J33" s="2"/>
       <c r="K33" s="3"/>
@@ -2607,10 +2626,10 @@
       <c r="D34" s="34"/>
       <c r="E34" s="34"/>
       <c r="F34" s="18"/>
-      <c r="G34" s="121" t="s">
+      <c r="G34" s="130" t="s">
         <v>33</v>
       </c>
-      <c r="H34" s="126"/>
+      <c r="H34" s="94"/>
       <c r="I34" s="1"/>
       <c r="J34" s="2"/>
       <c r="K34" s="3"/>
@@ -2631,18 +2650,18 @@
       <c r="Z34" s="4"/>
     </row>
     <row r="35" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A35" s="99" t="s">
+      <c r="A35" s="119" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="96"/>
-      <c r="C35" s="96"/>
-      <c r="D35" s="96"/>
-      <c r="E35" s="96"/>
-      <c r="F35" s="97"/>
-      <c r="G35" s="121" t="s">
+      <c r="B35" s="100"/>
+      <c r="C35" s="100"/>
+      <c r="D35" s="100"/>
+      <c r="E35" s="100"/>
+      <c r="F35" s="101"/>
+      <c r="G35" s="130" t="s">
         <v>121</v>
       </c>
-      <c r="H35" s="126"/>
+      <c r="H35" s="94"/>
       <c r="I35" s="1"/>
       <c r="J35" s="2"/>
       <c r="K35" s="3"/>
@@ -2671,10 +2690,10 @@
       <c r="D36" s="45"/>
       <c r="E36" s="45"/>
       <c r="F36" s="42"/>
-      <c r="G36" s="121" t="s">
+      <c r="G36" s="130" t="s">
         <v>35</v>
       </c>
-      <c r="H36" s="126"/>
+      <c r="H36" s="94"/>
       <c r="I36" s="1"/>
       <c r="J36" s="2"/>
       <c r="K36" s="3"/>
@@ -2703,10 +2722,10 @@
       <c r="D37" s="45"/>
       <c r="E37" s="45"/>
       <c r="F37" s="85"/>
-      <c r="G37" s="121" t="s">
+      <c r="G37" s="130" t="s">
         <v>36</v>
       </c>
-      <c r="H37" s="126"/>
+      <c r="H37" s="94"/>
       <c r="I37" s="1"/>
       <c r="J37" s="2"/>
       <c r="K37" s="3"/>
@@ -2735,10 +2754,10 @@
       <c r="D38" s="45"/>
       <c r="E38" s="45"/>
       <c r="F38" s="85"/>
-      <c r="G38" s="121" t="s">
+      <c r="G38" s="130" t="s">
         <v>37</v>
       </c>
-      <c r="H38" s="126"/>
+      <c r="H38" s="94"/>
       <c r="I38" s="1"/>
       <c r="J38" s="2"/>
       <c r="K38" s="3"/>
@@ -2767,10 +2786,10 @@
       <c r="D39" s="45"/>
       <c r="E39" s="45"/>
       <c r="F39" s="85"/>
-      <c r="G39" s="121" t="s">
+      <c r="G39" s="130" t="s">
         <v>38</v>
       </c>
-      <c r="H39" s="126"/>
+      <c r="H39" s="94"/>
       <c r="I39" s="1"/>
       <c r="J39" s="2"/>
       <c r="K39" s="3"/>
@@ -2799,10 +2818,10 @@
       <c r="D40" s="45"/>
       <c r="E40" s="45"/>
       <c r="F40" s="85"/>
-      <c r="G40" s="121" t="s">
+      <c r="G40" s="130" t="s">
         <v>39</v>
       </c>
-      <c r="H40" s="126"/>
+      <c r="H40" s="94"/>
       <c r="I40" s="1"/>
       <c r="J40" s="2"/>
       <c r="K40" s="3"/>
@@ -2831,10 +2850,10 @@
       <c r="D41" s="45"/>
       <c r="E41" s="45"/>
       <c r="F41" s="85"/>
-      <c r="G41" s="121" t="s">
+      <c r="G41" s="130" t="s">
         <v>40</v>
       </c>
-      <c r="H41" s="126"/>
+      <c r="H41" s="94"/>
       <c r="I41" s="1"/>
       <c r="J41" s="2"/>
       <c r="K41" s="3"/>
@@ -2863,10 +2882,10 @@
       <c r="D42" s="81"/>
       <c r="E42" s="81"/>
       <c r="F42" s="86"/>
-      <c r="G42" s="121" t="s">
+      <c r="G42" s="130" t="s">
         <v>41</v>
       </c>
-      <c r="H42" s="126"/>
+      <c r="H42" s="94"/>
       <c r="I42" s="1"/>
       <c r="J42" s="2"/>
       <c r="K42" s="3"/>
@@ -2895,10 +2914,10 @@
       <c r="D43" s="81"/>
       <c r="E43" s="81"/>
       <c r="F43" s="86"/>
-      <c r="G43" s="121" t="s">
+      <c r="G43" s="130" t="s">
         <v>42</v>
       </c>
-      <c r="H43" s="127"/>
+      <c r="H43" s="95"/>
       <c r="I43" s="1"/>
       <c r="J43" s="2"/>
       <c r="K43" s="3"/>
@@ -2927,10 +2946,10 @@
       <c r="D44" s="81"/>
       <c r="E44" s="81"/>
       <c r="F44" s="86"/>
-      <c r="G44" s="128" t="s">
+      <c r="G44" s="131" t="s">
         <v>43</v>
       </c>
-      <c r="H44" s="126"/>
+      <c r="H44" s="94"/>
       <c r="I44" s="1"/>
       <c r="J44" s="2"/>
       <c r="K44" s="3"/>
@@ -2959,10 +2978,10 @@
       <c r="D45" s="81"/>
       <c r="E45" s="81"/>
       <c r="F45" s="86"/>
-      <c r="G45" s="121" t="s">
+      <c r="G45" s="130" t="s">
         <v>44</v>
       </c>
-      <c r="H45" s="127"/>
+      <c r="H45" s="95"/>
       <c r="I45" s="1"/>
       <c r="J45" s="2"/>
       <c r="K45" s="3"/>
@@ -2991,10 +3010,10 @@
       <c r="D46" s="45"/>
       <c r="E46" s="45"/>
       <c r="F46" s="85"/>
-      <c r="G46" s="121" t="s">
+      <c r="G46" s="130" t="s">
         <v>45</v>
       </c>
-      <c r="H46" s="126"/>
+      <c r="H46" s="94"/>
       <c r="I46" s="1"/>
       <c r="J46" s="2"/>
       <c r="K46" s="3"/>
@@ -3015,18 +3034,18 @@
       <c r="Z46" s="4"/>
     </row>
     <row r="47" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A47" s="99" t="s">
+      <c r="A47" s="119" t="s">
         <v>46</v>
       </c>
-      <c r="B47" s="96"/>
-      <c r="C47" s="96"/>
-      <c r="D47" s="96"/>
-      <c r="E47" s="96"/>
-      <c r="F47" s="97"/>
-      <c r="G47" s="121" t="s">
+      <c r="B47" s="100"/>
+      <c r="C47" s="100"/>
+      <c r="D47" s="100"/>
+      <c r="E47" s="100"/>
+      <c r="F47" s="101"/>
+      <c r="G47" s="130" t="s">
         <v>121</v>
       </c>
-      <c r="H47" s="126"/>
+      <c r="H47" s="94"/>
       <c r="I47" s="1"/>
       <c r="J47" s="2"/>
       <c r="K47" s="3"/>
@@ -3055,10 +3074,10 @@
       <c r="D48" s="45"/>
       <c r="E48" s="45"/>
       <c r="F48" s="47"/>
-      <c r="G48" s="121" t="s">
+      <c r="G48" s="130" t="s">
         <v>47</v>
       </c>
-      <c r="H48" s="126"/>
+      <c r="H48" s="94"/>
       <c r="I48" s="1"/>
       <c r="J48" s="2"/>
       <c r="K48" s="3"/>
@@ -3087,10 +3106,10 @@
       <c r="D49" s="45"/>
       <c r="E49" s="45"/>
       <c r="F49" s="47"/>
-      <c r="G49" s="121" t="s">
+      <c r="G49" s="130" t="s">
         <v>48</v>
       </c>
-      <c r="H49" s="126"/>
+      <c r="H49" s="94"/>
       <c r="I49" s="1"/>
       <c r="J49" s="2"/>
       <c r="K49" s="3"/>
@@ -3111,18 +3130,18 @@
       <c r="Z49" s="4"/>
     </row>
     <row r="50" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A50" s="99" t="s">
+      <c r="A50" s="119" t="s">
         <v>49</v>
       </c>
-      <c r="B50" s="96"/>
-      <c r="C50" s="96"/>
-      <c r="D50" s="96"/>
-      <c r="E50" s="96"/>
-      <c r="F50" s="97"/>
-      <c r="G50" s="121" t="s">
+      <c r="B50" s="100"/>
+      <c r="C50" s="100"/>
+      <c r="D50" s="100"/>
+      <c r="E50" s="100"/>
+      <c r="F50" s="101"/>
+      <c r="G50" s="130" t="s">
         <v>121</v>
       </c>
-      <c r="H50" s="126"/>
+      <c r="H50" s="94"/>
       <c r="I50" s="1"/>
       <c r="J50" s="2"/>
       <c r="K50" s="3"/>
@@ -3151,10 +3170,10 @@
       <c r="D51" s="34"/>
       <c r="E51" s="34"/>
       <c r="F51" s="18"/>
-      <c r="G51" s="121" t="s">
+      <c r="G51" s="130" t="s">
         <v>50</v>
       </c>
-      <c r="H51" s="126"/>
+      <c r="H51" s="94"/>
       <c r="I51" s="1"/>
       <c r="J51" s="2"/>
       <c r="K51" s="3"/>
@@ -3183,10 +3202,10 @@
       <c r="D52" s="34"/>
       <c r="E52" s="34"/>
       <c r="F52" s="18"/>
-      <c r="G52" s="128" t="s">
+      <c r="G52" s="131" t="s">
         <v>51</v>
       </c>
-      <c r="H52" s="126"/>
+      <c r="H52" s="94"/>
       <c r="I52" s="1"/>
       <c r="J52" s="2"/>
       <c r="K52" s="3"/>
@@ -3207,16 +3226,16 @@
       <c r="Z52" s="4"/>
     </row>
     <row r="53" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A53" s="106" t="s">
+      <c r="A53" s="99" t="s">
         <v>52</v>
       </c>
-      <c r="B53" s="96"/>
-      <c r="C53" s="96"/>
-      <c r="D53" s="96"/>
-      <c r="E53" s="96"/>
-      <c r="F53" s="97"/>
-      <c r="G53" s="129"/>
-      <c r="H53" s="126"/>
+      <c r="B53" s="100"/>
+      <c r="C53" s="100"/>
+      <c r="D53" s="100"/>
+      <c r="E53" s="100"/>
+      <c r="F53" s="101"/>
+      <c r="G53" s="132"/>
+      <c r="H53" s="94"/>
       <c r="I53" s="1"/>
       <c r="J53" s="2"/>
       <c r="K53" s="3"/>
@@ -3245,10 +3264,10 @@
       <c r="D54" s="34"/>
       <c r="E54" s="38"/>
       <c r="F54" s="48"/>
-      <c r="G54" s="129" t="s">
+      <c r="G54" s="132" t="s">
         <v>53</v>
       </c>
-      <c r="H54" s="126"/>
+      <c r="H54" s="94"/>
       <c r="I54" s="1"/>
       <c r="J54" s="2"/>
       <c r="K54" s="3"/>
@@ -3277,10 +3296,10 @@
       <c r="D55" s="34"/>
       <c r="E55" s="38"/>
       <c r="F55" s="48"/>
-      <c r="G55" s="129" t="s">
+      <c r="G55" s="132" t="s">
         <v>54</v>
       </c>
-      <c r="H55" s="130"/>
+      <c r="H55" s="97"/>
       <c r="I55" s="1"/>
       <c r="J55" s="2"/>
       <c r="K55" s="3"/>
@@ -3309,10 +3328,10 @@
       <c r="D56" s="34"/>
       <c r="E56" s="50"/>
       <c r="F56" s="51"/>
-      <c r="G56" s="129" t="s">
+      <c r="G56" s="132" t="s">
         <v>55</v>
       </c>
-      <c r="H56" s="131"/>
+      <c r="H56" s="98"/>
       <c r="I56" s="1"/>
       <c r="J56" s="2"/>
       <c r="K56" s="3"/>
@@ -3341,10 +3360,10 @@
       <c r="D57" s="34"/>
       <c r="E57" s="38"/>
       <c r="F57" s="48"/>
-      <c r="G57" s="129" t="s">
+      <c r="G57" s="132" t="s">
         <v>56</v>
       </c>
-      <c r="H57" s="126"/>
+      <c r="H57" s="94"/>
       <c r="I57" s="1"/>
       <c r="J57" s="2"/>
       <c r="K57" s="3"/>
@@ -3373,10 +3392,10 @@
       <c r="D58" s="34"/>
       <c r="E58" s="38"/>
       <c r="F58" s="48"/>
-      <c r="G58" s="129" t="s">
+      <c r="G58" s="132" t="s">
         <v>57</v>
       </c>
-      <c r="H58" s="126"/>
+      <c r="H58" s="94"/>
       <c r="I58" s="1"/>
       <c r="J58" s="2"/>
       <c r="K58" s="3"/>
@@ -3405,10 +3424,10 @@
       <c r="D59" s="34"/>
       <c r="E59" s="38"/>
       <c r="F59" s="48"/>
-      <c r="G59" s="129" t="s">
+      <c r="G59" s="132" t="s">
         <v>58</v>
       </c>
-      <c r="H59" s="126"/>
+      <c r="H59" s="94"/>
       <c r="I59" s="1"/>
       <c r="J59" s="2"/>
       <c r="K59" s="3"/>
@@ -3437,10 +3456,10 @@
       <c r="D60" s="26"/>
       <c r="E60" s="26"/>
       <c r="F60" s="18"/>
-      <c r="G60" s="129" t="s">
+      <c r="G60" s="132" t="s">
         <v>59</v>
       </c>
-      <c r="H60" s="126"/>
+      <c r="H60" s="94"/>
       <c r="I60" s="1"/>
       <c r="J60" s="2"/>
       <c r="K60" s="3"/>
@@ -3469,10 +3488,10 @@
       <c r="D61" s="26"/>
       <c r="E61" s="26"/>
       <c r="F61" s="18"/>
-      <c r="G61" s="129" t="s">
+      <c r="G61" s="132" t="s">
         <v>60</v>
       </c>
-      <c r="H61" s="126"/>
+      <c r="H61" s="94"/>
       <c r="I61" s="1"/>
       <c r="J61" s="2"/>
       <c r="K61" s="3"/>
@@ -3501,10 +3520,10 @@
       <c r="D62" s="26"/>
       <c r="E62" s="26"/>
       <c r="F62" s="18"/>
-      <c r="G62" s="129" t="s">
+      <c r="G62" s="132" t="s">
         <v>61</v>
       </c>
-      <c r="H62" s="126"/>
+      <c r="H62" s="94"/>
       <c r="I62" s="1"/>
       <c r="J62" s="2"/>
       <c r="K62" s="3"/>
@@ -3533,10 +3552,10 @@
       <c r="D63" s="26"/>
       <c r="E63" s="53"/>
       <c r="F63" s="39"/>
-      <c r="G63" s="129" t="s">
+      <c r="G63" s="132" t="s">
         <v>62</v>
       </c>
-      <c r="H63" s="126"/>
+      <c r="H63" s="94"/>
       <c r="I63" s="1"/>
       <c r="J63" s="2"/>
       <c r="K63" s="3"/>
@@ -3565,10 +3584,10 @@
       <c r="D64" s="26"/>
       <c r="E64" s="53"/>
       <c r="F64" s="39"/>
-      <c r="G64" s="129" t="s">
+      <c r="G64" s="132" t="s">
         <v>63</v>
       </c>
-      <c r="H64" s="126"/>
+      <c r="H64" s="94"/>
       <c r="I64" s="1"/>
       <c r="J64" s="2"/>
       <c r="K64" s="3"/>
@@ -3597,10 +3616,10 @@
       <c r="D65" s="26"/>
       <c r="E65" s="26"/>
       <c r="F65" s="18"/>
-      <c r="G65" s="129" t="s">
+      <c r="G65" s="132" t="s">
         <v>64</v>
       </c>
-      <c r="H65" s="126"/>
+      <c r="H65" s="94"/>
       <c r="I65" s="1"/>
       <c r="J65" s="2"/>
       <c r="K65" s="3"/>
@@ -3621,16 +3640,16 @@
       <c r="Z65" s="4"/>
     </row>
     <row r="66" spans="1:26" ht="18" customHeight="1">
-      <c r="A66" s="107" t="s">
+      <c r="A66" s="111" t="s">
         <v>65</v>
       </c>
-      <c r="B66" s="108"/>
-      <c r="C66" s="108"/>
-      <c r="D66" s="108"/>
-      <c r="E66" s="108"/>
-      <c r="F66" s="109"/>
-      <c r="G66" s="132"/>
-      <c r="H66" s="126"/>
+      <c r="B66" s="112"/>
+      <c r="C66" s="112"/>
+      <c r="D66" s="112"/>
+      <c r="E66" s="112"/>
+      <c r="F66" s="113"/>
+      <c r="G66" s="133"/>
+      <c r="H66" s="94"/>
       <c r="I66" s="1"/>
       <c r="J66" s="2"/>
       <c r="K66" s="3"/>
@@ -3651,16 +3670,16 @@
       <c r="Z66" s="4"/>
     </row>
     <row r="67" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A67" s="105" t="s">
+      <c r="A67" s="109" t="s">
         <v>11</v>
       </c>
-      <c r="B67" s="96"/>
-      <c r="C67" s="96"/>
-      <c r="D67" s="96"/>
-      <c r="E67" s="96"/>
-      <c r="F67" s="97"/>
-      <c r="G67" s="132"/>
-      <c r="H67" s="126"/>
+      <c r="B67" s="100"/>
+      <c r="C67" s="100"/>
+      <c r="D67" s="100"/>
+      <c r="E67" s="100"/>
+      <c r="F67" s="101"/>
+      <c r="G67" s="133"/>
+      <c r="H67" s="94"/>
       <c r="I67" s="1"/>
       <c r="J67" s="2"/>
       <c r="K67" s="3"/>
@@ -3689,10 +3708,10 @@
       <c r="D68" s="54"/>
       <c r="E68" s="54"/>
       <c r="F68" s="55"/>
-      <c r="G68" s="133" t="s">
+      <c r="G68" s="134" t="s">
         <v>121</v>
       </c>
-      <c r="H68" s="126"/>
+      <c r="H68" s="94"/>
       <c r="I68" s="1"/>
       <c r="J68" s="2"/>
       <c r="K68" s="3"/>
@@ -3721,10 +3740,10 @@
       <c r="D69" s="56"/>
       <c r="E69" s="56"/>
       <c r="F69" s="55"/>
-      <c r="G69" s="129" t="s">
+      <c r="G69" s="132" t="s">
         <v>128</v>
       </c>
-      <c r="H69" s="131"/>
+      <c r="H69" s="98"/>
       <c r="I69" s="1"/>
       <c r="J69" s="2"/>
       <c r="K69" s="3"/>
@@ -3753,10 +3772,10 @@
       <c r="D70" s="57"/>
       <c r="E70" s="57"/>
       <c r="F70" s="55"/>
-      <c r="G70" s="129" t="s">
+      <c r="G70" s="132" t="s">
         <v>129</v>
       </c>
-      <c r="H70" s="131"/>
+      <c r="H70" s="98"/>
       <c r="I70" s="1"/>
       <c r="J70" s="2"/>
       <c r="K70" s="3"/>
@@ -3785,10 +3804,10 @@
       <c r="D71" s="58"/>
       <c r="E71" s="58"/>
       <c r="F71" s="59"/>
-      <c r="G71" s="129" t="s">
+      <c r="G71" s="132" t="s">
         <v>69</v>
       </c>
-      <c r="H71" s="131"/>
+      <c r="H71" s="98"/>
       <c r="I71" s="1"/>
       <c r="J71" s="2"/>
       <c r="K71" s="3"/>
@@ -3809,18 +3828,18 @@
       <c r="Z71" s="4"/>
     </row>
     <row r="72" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A72" s="110" t="s">
+      <c r="A72" s="114" t="s">
         <v>70</v>
       </c>
-      <c r="B72" s="91"/>
-      <c r="C72" s="91"/>
-      <c r="D72" s="91"/>
-      <c r="E72" s="91"/>
-      <c r="F72" s="111"/>
-      <c r="G72" s="129" t="s">
+      <c r="B72" s="105"/>
+      <c r="C72" s="105"/>
+      <c r="D72" s="105"/>
+      <c r="E72" s="105"/>
+      <c r="F72" s="115"/>
+      <c r="G72" s="132" t="s">
         <v>121</v>
       </c>
-      <c r="H72" s="131"/>
+      <c r="H72" s="98"/>
       <c r="I72" s="1"/>
       <c r="J72" s="2"/>
       <c r="K72" s="3"/>
@@ -3849,10 +3868,10 @@
       <c r="D73" s="60"/>
       <c r="E73" s="60"/>
       <c r="F73" s="59"/>
-      <c r="G73" s="129" t="s">
+      <c r="G73" s="132" t="s">
         <v>71</v>
       </c>
-      <c r="H73" s="131"/>
+      <c r="H73" s="98"/>
       <c r="I73" s="1"/>
       <c r="J73" s="2"/>
       <c r="K73" s="3"/>
@@ -3881,10 +3900,10 @@
       <c r="D74" s="45"/>
       <c r="E74" s="45"/>
       <c r="F74" s="59"/>
-      <c r="G74" s="129" t="s">
+      <c r="G74" s="132" t="s">
         <v>72</v>
       </c>
-      <c r="H74" s="131"/>
+      <c r="H74" s="98"/>
       <c r="I74" s="1"/>
       <c r="J74" s="2"/>
       <c r="K74" s="3"/>
@@ -3913,10 +3932,10 @@
       <c r="D75" s="45"/>
       <c r="E75" s="45"/>
       <c r="F75" s="59"/>
-      <c r="G75" s="129" t="s">
+      <c r="G75" s="132" t="s">
         <v>73</v>
       </c>
-      <c r="H75" s="131"/>
+      <c r="H75" s="98"/>
       <c r="I75" s="1"/>
       <c r="J75" s="2"/>
       <c r="K75" s="3"/>
@@ -3945,10 +3964,10 @@
       <c r="D76" s="45"/>
       <c r="E76" s="45"/>
       <c r="F76" s="59"/>
-      <c r="G76" s="129" t="s">
+      <c r="G76" s="132" t="s">
         <v>74</v>
       </c>
-      <c r="H76" s="131"/>
+      <c r="H76" s="98"/>
       <c r="I76" s="1"/>
       <c r="J76" s="2"/>
       <c r="K76" s="3"/>
@@ -3977,10 +3996,10 @@
       <c r="D77" s="45"/>
       <c r="E77" s="45"/>
       <c r="F77" s="59"/>
-      <c r="G77" s="129" t="s">
+      <c r="G77" s="132" t="s">
         <v>75</v>
       </c>
-      <c r="H77" s="131"/>
+      <c r="H77" s="98"/>
       <c r="I77" s="1"/>
       <c r="J77" s="2"/>
       <c r="K77" s="3"/>
@@ -4009,10 +4028,10 @@
       <c r="D78" s="38"/>
       <c r="E78" s="38"/>
       <c r="F78" s="39"/>
-      <c r="G78" s="129" t="s">
+      <c r="G78" s="132" t="s">
         <v>76</v>
       </c>
-      <c r="H78" s="131"/>
+      <c r="H78" s="98"/>
       <c r="I78" s="1"/>
       <c r="J78" s="2"/>
       <c r="K78" s="3"/>
@@ -4033,18 +4052,18 @@
       <c r="Z78" s="4"/>
     </row>
     <row r="79" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A79" s="112" t="s">
+      <c r="A79" s="116" t="s">
         <v>77</v>
       </c>
-      <c r="B79" s="113"/>
-      <c r="C79" s="113"/>
-      <c r="D79" s="113"/>
-      <c r="E79" s="113"/>
-      <c r="F79" s="114"/>
-      <c r="G79" s="131" t="s">
+      <c r="B79" s="117"/>
+      <c r="C79" s="117"/>
+      <c r="D79" s="117"/>
+      <c r="E79" s="117"/>
+      <c r="F79" s="118"/>
+      <c r="G79" s="135" t="s">
         <v>121</v>
       </c>
-      <c r="H79" s="131"/>
+      <c r="H79" s="98"/>
       <c r="I79" s="1"/>
       <c r="J79" s="2"/>
       <c r="K79" s="3"/>
@@ -4073,10 +4092,10 @@
       <c r="D80" s="50"/>
       <c r="E80" s="50"/>
       <c r="F80" s="15"/>
-      <c r="G80" s="131" t="s">
+      <c r="G80" s="135" t="s">
         <v>78</v>
       </c>
-      <c r="H80" s="131"/>
+      <c r="H80" s="98"/>
       <c r="I80" s="1"/>
       <c r="J80" s="2"/>
       <c r="K80" s="3"/>
@@ -4105,10 +4124,10 @@
       <c r="D81" s="50"/>
       <c r="E81" s="50"/>
       <c r="F81" s="15"/>
-      <c r="G81" s="131" t="s">
+      <c r="G81" s="135" t="s">
         <v>79</v>
       </c>
-      <c r="H81" s="131"/>
+      <c r="H81" s="98"/>
       <c r="I81" s="1"/>
       <c r="J81" s="2"/>
       <c r="K81" s="3"/>
@@ -4137,10 +4156,10 @@
       <c r="D82" s="50"/>
       <c r="E82" s="50"/>
       <c r="F82" s="15"/>
-      <c r="G82" s="131" t="s">
+      <c r="G82" s="135" t="s">
         <v>80</v>
       </c>
-      <c r="H82" s="131"/>
+      <c r="H82" s="98"/>
       <c r="I82" s="1"/>
       <c r="J82" s="2"/>
       <c r="K82" s="3"/>
@@ -4161,18 +4180,18 @@
       <c r="Z82" s="4"/>
     </row>
     <row r="83" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A83" s="119" t="s">
+      <c r="A83" s="107" t="s">
         <v>81</v>
       </c>
-      <c r="B83" s="96"/>
-      <c r="C83" s="96"/>
-      <c r="D83" s="96"/>
-      <c r="E83" s="96"/>
-      <c r="F83" s="97"/>
-      <c r="G83" s="131" t="s">
+      <c r="B83" s="100"/>
+      <c r="C83" s="100"/>
+      <c r="D83" s="100"/>
+      <c r="E83" s="100"/>
+      <c r="F83" s="101"/>
+      <c r="G83" s="135" t="s">
         <v>121</v>
       </c>
-      <c r="H83" s="131"/>
+      <c r="H83" s="98"/>
       <c r="I83" s="1"/>
       <c r="J83" s="2"/>
       <c r="K83" s="3"/>
@@ -4201,10 +4220,10 @@
       <c r="D84" s="34"/>
       <c r="E84" s="34"/>
       <c r="F84" s="18"/>
-      <c r="G84" s="131" t="s">
+      <c r="G84" s="135" t="s">
         <v>126</v>
       </c>
-      <c r="H84" s="131"/>
+      <c r="H84" s="98"/>
       <c r="I84" s="1"/>
       <c r="J84" s="2"/>
       <c r="K84" s="3"/>
@@ -4233,10 +4252,10 @@
       <c r="D85" s="61"/>
       <c r="E85" s="61"/>
       <c r="F85" s="18"/>
-      <c r="G85" s="131" t="s">
+      <c r="G85" s="135" t="s">
         <v>121</v>
       </c>
-      <c r="H85" s="131"/>
+      <c r="H85" s="98"/>
       <c r="I85" s="1"/>
       <c r="J85" s="2"/>
       <c r="K85" s="3"/>
@@ -4265,10 +4284,10 @@
       <c r="D86" s="34"/>
       <c r="E86" s="34"/>
       <c r="F86" s="18"/>
-      <c r="G86" s="131" t="s">
+      <c r="G86" s="135" t="s">
         <v>127</v>
       </c>
-      <c r="H86" s="131"/>
+      <c r="H86" s="98"/>
       <c r="I86" s="1"/>
       <c r="J86" s="2"/>
       <c r="K86" s="3"/>
@@ -4297,10 +4316,10 @@
       <c r="D87" s="34"/>
       <c r="E87" s="34"/>
       <c r="F87" s="18"/>
-      <c r="G87" s="131" t="s">
+      <c r="G87" s="135" t="s">
         <v>125</v>
       </c>
-      <c r="H87" s="131"/>
+      <c r="H87" s="98"/>
       <c r="I87" s="1"/>
       <c r="J87" s="2"/>
       <c r="K87" s="3"/>
@@ -4329,10 +4348,10 @@
       <c r="D88" s="61"/>
       <c r="E88" s="61"/>
       <c r="F88" s="18"/>
-      <c r="G88" s="131" t="s">
+      <c r="G88" s="135" t="s">
         <v>121</v>
       </c>
-      <c r="H88" s="131"/>
+      <c r="H88" s="98"/>
       <c r="I88" s="1"/>
       <c r="J88" s="2"/>
       <c r="K88" s="3"/>
@@ -4361,10 +4380,10 @@
       <c r="D89" s="34"/>
       <c r="E89" s="34"/>
       <c r="F89" s="18"/>
-      <c r="G89" s="131" t="s">
+      <c r="G89" s="135" t="s">
         <v>124</v>
       </c>
-      <c r="H89" s="131"/>
+      <c r="H89" s="98"/>
       <c r="I89" s="1"/>
       <c r="J89" s="2"/>
       <c r="K89" s="3"/>
@@ -4393,10 +4412,10 @@
       <c r="D90" s="34"/>
       <c r="E90" s="34"/>
       <c r="F90" s="18"/>
-      <c r="G90" s="131" t="s">
+      <c r="G90" s="135" t="s">
         <v>124</v>
       </c>
-      <c r="H90" s="131"/>
+      <c r="H90" s="98"/>
       <c r="I90" s="1"/>
       <c r="J90" s="2"/>
       <c r="K90" s="3"/>
@@ -4417,16 +4436,16 @@
       <c r="Z90" s="4"/>
     </row>
     <row r="91" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A91" s="106" t="s">
+      <c r="A91" s="99" t="s">
         <v>52</v>
       </c>
-      <c r="B91" s="96"/>
-      <c r="C91" s="96"/>
-      <c r="D91" s="96"/>
-      <c r="E91" s="96"/>
-      <c r="F91" s="97"/>
-      <c r="G91" s="126"/>
-      <c r="H91" s="126"/>
+      <c r="B91" s="100"/>
+      <c r="C91" s="100"/>
+      <c r="D91" s="100"/>
+      <c r="E91" s="100"/>
+      <c r="F91" s="101"/>
+      <c r="G91" s="136"/>
+      <c r="H91" s="94"/>
       <c r="I91" s="1"/>
       <c r="J91" s="2"/>
       <c r="K91" s="3"/>
@@ -4455,10 +4474,10 @@
       <c r="D92" s="34"/>
       <c r="E92" s="38"/>
       <c r="F92" s="38"/>
-      <c r="G92" s="129" t="s">
+      <c r="G92" s="132" t="s">
         <v>88</v>
       </c>
-      <c r="H92" s="129"/>
+      <c r="H92" s="96"/>
       <c r="I92" s="1"/>
       <c r="J92" s="2"/>
       <c r="K92" s="3"/>
@@ -4487,10 +4506,10 @@
       <c r="D93" s="34"/>
       <c r="E93" s="34"/>
       <c r="F93" s="62"/>
-      <c r="G93" s="129" t="s">
+      <c r="G93" s="132" t="s">
         <v>89</v>
       </c>
-      <c r="H93" s="129"/>
+      <c r="H93" s="96"/>
       <c r="I93" s="1"/>
       <c r="J93" s="2"/>
       <c r="K93" s="3"/>
@@ -4519,10 +4538,10 @@
       <c r="D94" s="34"/>
       <c r="E94" s="38"/>
       <c r="F94" s="48"/>
-      <c r="G94" s="129" t="s">
+      <c r="G94" s="132" t="s">
         <v>90</v>
       </c>
-      <c r="H94" s="129"/>
+      <c r="H94" s="96"/>
       <c r="I94" s="1"/>
       <c r="J94" s="2"/>
       <c r="K94" s="3"/>
@@ -4551,10 +4570,10 @@
       <c r="D95" s="34"/>
       <c r="E95" s="38"/>
       <c r="F95" s="48"/>
-      <c r="G95" s="129" t="s">
+      <c r="G95" s="132" t="s">
         <v>91</v>
       </c>
-      <c r="H95" s="129"/>
+      <c r="H95" s="96"/>
       <c r="I95" s="1"/>
       <c r="J95" s="2"/>
       <c r="K95" s="3"/>
@@ -4583,10 +4602,10 @@
       <c r="D96" s="34"/>
       <c r="E96" s="34"/>
       <c r="F96" s="62"/>
-      <c r="G96" s="129" t="s">
+      <c r="G96" s="132" t="s">
         <v>92</v>
       </c>
-      <c r="H96" s="129"/>
+      <c r="H96" s="96"/>
       <c r="I96" s="1"/>
       <c r="J96" s="2"/>
       <c r="K96" s="3"/>
@@ -4607,16 +4626,16 @@
       <c r="Z96" s="4"/>
     </row>
     <row r="97" spans="1:26" ht="21" customHeight="1">
-      <c r="A97" s="101" t="s">
+      <c r="A97" s="108" t="s">
         <v>93</v>
       </c>
-      <c r="B97" s="96"/>
-      <c r="C97" s="96"/>
-      <c r="D97" s="96"/>
-      <c r="E97" s="96"/>
-      <c r="F97" s="97"/>
-      <c r="G97" s="126"/>
-      <c r="H97" s="126"/>
+      <c r="B97" s="100"/>
+      <c r="C97" s="100"/>
+      <c r="D97" s="100"/>
+      <c r="E97" s="100"/>
+      <c r="F97" s="101"/>
+      <c r="G97" s="136"/>
+      <c r="H97" s="94"/>
       <c r="I97" s="1"/>
       <c r="J97" s="2"/>
       <c r="K97" s="3"/>
@@ -4637,16 +4656,16 @@
       <c r="Z97" s="4"/>
     </row>
     <row r="98" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A98" s="105" t="s">
+      <c r="A98" s="109" t="s">
         <v>11</v>
       </c>
-      <c r="B98" s="96"/>
-      <c r="C98" s="96"/>
-      <c r="D98" s="96"/>
-      <c r="E98" s="96"/>
-      <c r="F98" s="97"/>
-      <c r="G98" s="126"/>
-      <c r="H98" s="126"/>
+      <c r="B98" s="100"/>
+      <c r="C98" s="100"/>
+      <c r="D98" s="100"/>
+      <c r="E98" s="100"/>
+      <c r="F98" s="101"/>
+      <c r="G98" s="136"/>
+      <c r="H98" s="94"/>
       <c r="I98" s="1"/>
       <c r="J98" s="2"/>
       <c r="K98" s="3"/>
@@ -4675,10 +4694,10 @@
       <c r="D99" s="34"/>
       <c r="E99" s="34"/>
       <c r="F99" s="18"/>
-      <c r="G99" s="131" t="s">
+      <c r="G99" s="135" t="s">
         <v>94</v>
       </c>
-      <c r="H99" s="131"/>
+      <c r="H99" s="98"/>
       <c r="I99" s="1"/>
       <c r="J99" s="2"/>
       <c r="K99" s="3"/>
@@ -4699,16 +4718,16 @@
       <c r="Z99" s="4"/>
     </row>
     <row r="100" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A100" s="106" t="s">
+      <c r="A100" s="99" t="s">
         <v>52</v>
       </c>
-      <c r="B100" s="96"/>
-      <c r="C100" s="96"/>
-      <c r="D100" s="96"/>
-      <c r="E100" s="96"/>
-      <c r="F100" s="97"/>
-      <c r="G100" s="131"/>
-      <c r="H100" s="131"/>
+      <c r="B100" s="100"/>
+      <c r="C100" s="100"/>
+      <c r="D100" s="100"/>
+      <c r="E100" s="100"/>
+      <c r="F100" s="101"/>
+      <c r="G100" s="135"/>
+      <c r="H100" s="98"/>
       <c r="I100" s="1"/>
       <c r="J100" s="2"/>
       <c r="K100" s="3"/>
@@ -4737,10 +4756,10 @@
       <c r="D101" s="34"/>
       <c r="E101" s="38"/>
       <c r="F101" s="48"/>
-      <c r="G101" s="131" t="s">
+      <c r="G101" s="135" t="s">
         <v>95</v>
       </c>
-      <c r="H101" s="131"/>
+      <c r="H101" s="98"/>
       <c r="I101" s="1"/>
       <c r="J101" s="2"/>
       <c r="K101" s="3"/>
@@ -4769,10 +4788,10 @@
       <c r="D102" s="34"/>
       <c r="E102" s="38"/>
       <c r="F102" s="48"/>
-      <c r="G102" s="131" t="s">
+      <c r="G102" s="135" t="s">
         <v>96</v>
       </c>
-      <c r="H102" s="131"/>
+      <c r="H102" s="98"/>
       <c r="I102" s="1"/>
       <c r="J102" s="2"/>
       <c r="K102" s="3"/>
@@ -4801,10 +4820,10 @@
       <c r="D103" s="34"/>
       <c r="E103" s="38"/>
       <c r="F103" s="48"/>
-      <c r="G103" s="131" t="s">
+      <c r="G103" s="135" t="s">
         <v>97</v>
       </c>
-      <c r="H103" s="131"/>
+      <c r="H103" s="98"/>
       <c r="I103" s="1"/>
       <c r="J103" s="2"/>
       <c r="K103" s="3"/>
@@ -4833,10 +4852,10 @@
       <c r="D104" s="34"/>
       <c r="E104" s="38"/>
       <c r="F104" s="48"/>
-      <c r="G104" s="131" t="s">
+      <c r="G104" s="135" t="s">
         <v>98</v>
       </c>
-      <c r="H104" s="131"/>
+      <c r="H104" s="98"/>
       <c r="I104" s="1"/>
       <c r="J104" s="2"/>
       <c r="K104" s="3"/>
@@ -4857,16 +4876,16 @@
       <c r="Z104" s="4"/>
     </row>
     <row r="105" spans="1:26" ht="21" customHeight="1">
-      <c r="A105" s="101" t="s">
+      <c r="A105" s="108" t="s">
         <v>99</v>
       </c>
-      <c r="B105" s="96"/>
-      <c r="C105" s="96"/>
-      <c r="D105" s="96"/>
-      <c r="E105" s="96"/>
-      <c r="F105" s="97"/>
-      <c r="G105" s="131"/>
-      <c r="H105" s="131"/>
+      <c r="B105" s="100"/>
+      <c r="C105" s="100"/>
+      <c r="D105" s="100"/>
+      <c r="E105" s="100"/>
+      <c r="F105" s="101"/>
+      <c r="G105" s="135"/>
+      <c r="H105" s="98"/>
       <c r="I105" s="1"/>
       <c r="J105" s="2"/>
       <c r="K105" s="3"/>
@@ -4887,16 +4906,16 @@
       <c r="Z105" s="4"/>
     </row>
     <row r="106" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A106" s="105" t="s">
+      <c r="A106" s="109" t="s">
         <v>11</v>
       </c>
-      <c r="B106" s="96"/>
-      <c r="C106" s="96"/>
-      <c r="D106" s="96"/>
-      <c r="E106" s="96"/>
-      <c r="F106" s="97"/>
-      <c r="G106" s="131"/>
-      <c r="H106" s="131"/>
+      <c r="B106" s="100"/>
+      <c r="C106" s="100"/>
+      <c r="D106" s="100"/>
+      <c r="E106" s="100"/>
+      <c r="F106" s="101"/>
+      <c r="G106" s="135"/>
+      <c r="H106" s="98"/>
       <c r="I106" s="1"/>
       <c r="J106" s="2"/>
       <c r="K106" s="3"/>
@@ -4925,10 +4944,10 @@
       <c r="D107" s="34"/>
       <c r="E107" s="34"/>
       <c r="F107" s="62"/>
-      <c r="G107" s="131" t="s">
+      <c r="G107" s="135" t="s">
         <v>100</v>
       </c>
-      <c r="H107" s="131"/>
+      <c r="H107" s="98"/>
       <c r="I107" s="1"/>
       <c r="J107" s="2"/>
       <c r="K107" s="3"/>
@@ -4957,10 +4976,10 @@
       <c r="D108" s="34"/>
       <c r="E108" s="34"/>
       <c r="F108" s="62"/>
-      <c r="G108" s="131" t="s">
+      <c r="G108" s="135" t="s">
         <v>101</v>
       </c>
-      <c r="H108" s="131"/>
+      <c r="H108" s="98"/>
       <c r="I108" s="1"/>
       <c r="J108" s="2"/>
       <c r="K108" s="3"/>
@@ -4989,10 +5008,10 @@
       <c r="D109" s="34"/>
       <c r="E109" s="34"/>
       <c r="F109" s="63"/>
-      <c r="G109" s="131" t="s">
+      <c r="G109" s="135" t="s">
         <v>102</v>
       </c>
-      <c r="H109" s="131"/>
+      <c r="H109" s="98"/>
       <c r="I109" s="1"/>
       <c r="J109" s="2"/>
       <c r="K109" s="3"/>
@@ -5013,16 +5032,16 @@
       <c r="Z109" s="4"/>
     </row>
     <row r="110" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A110" s="106" t="s">
+      <c r="A110" s="99" t="s">
         <v>52</v>
       </c>
-      <c r="B110" s="96"/>
-      <c r="C110" s="96"/>
-      <c r="D110" s="96"/>
-      <c r="E110" s="96"/>
-      <c r="F110" s="97"/>
-      <c r="G110" s="126"/>
-      <c r="H110" s="126"/>
+      <c r="B110" s="100"/>
+      <c r="C110" s="100"/>
+      <c r="D110" s="100"/>
+      <c r="E110" s="100"/>
+      <c r="F110" s="101"/>
+      <c r="G110" s="136"/>
+      <c r="H110" s="94"/>
       <c r="I110" s="1"/>
       <c r="J110" s="2"/>
       <c r="K110" s="3"/>
@@ -5051,10 +5070,10 @@
       <c r="D111" s="34"/>
       <c r="E111" s="38"/>
       <c r="F111" s="48"/>
-      <c r="G111" s="131" t="s">
+      <c r="G111" s="135" t="s">
         <v>103</v>
       </c>
-      <c r="H111" s="131"/>
+      <c r="H111" s="98"/>
       <c r="I111" s="1"/>
       <c r="J111" s="2"/>
       <c r="K111" s="3"/>
@@ -5083,10 +5102,10 @@
       <c r="D112" s="34"/>
       <c r="E112" s="38"/>
       <c r="F112" s="48"/>
-      <c r="G112" s="131" t="s">
+      <c r="G112" s="135" t="s">
         <v>104</v>
       </c>
-      <c r="H112" s="131"/>
+      <c r="H112" s="98"/>
       <c r="I112" s="1"/>
       <c r="J112" s="2"/>
       <c r="K112" s="3"/>
@@ -5115,10 +5134,10 @@
       <c r="D113" s="45"/>
       <c r="E113" s="45"/>
       <c r="F113" s="47"/>
-      <c r="G113" s="131" t="s">
+      <c r="G113" s="135" t="s">
         <v>105</v>
       </c>
-      <c r="H113" s="131"/>
+      <c r="H113" s="98"/>
       <c r="I113" s="1"/>
       <c r="J113" s="2"/>
       <c r="K113" s="3"/>
@@ -5147,10 +5166,10 @@
       <c r="D114" s="45"/>
       <c r="E114" s="45"/>
       <c r="F114" s="47"/>
-      <c r="G114" s="131" t="s">
+      <c r="G114" s="135" t="s">
         <v>106</v>
       </c>
-      <c r="H114" s="131"/>
+      <c r="H114" s="98"/>
       <c r="I114" s="1"/>
       <c r="J114" s="2"/>
       <c r="K114" s="3"/>
@@ -5179,10 +5198,10 @@
       <c r="D115" s="45"/>
       <c r="E115" s="38"/>
       <c r="F115" s="48"/>
-      <c r="G115" s="131" t="s">
+      <c r="G115" s="135" t="s">
         <v>107</v>
       </c>
-      <c r="H115" s="131"/>
+      <c r="H115" s="98"/>
       <c r="I115" s="1"/>
       <c r="J115" s="2"/>
       <c r="K115" s="3"/>
@@ -5211,10 +5230,10 @@
       <c r="D116" s="41"/>
       <c r="E116" s="53"/>
       <c r="F116" s="39"/>
-      <c r="G116" s="131" t="s">
+      <c r="G116" s="135" t="s">
         <v>108</v>
       </c>
-      <c r="H116" s="131"/>
+      <c r="H116" s="98"/>
       <c r="I116" s="1"/>
       <c r="J116" s="2"/>
       <c r="K116" s="3"/>
@@ -5267,12 +5286,12 @@
         <v>110</v>
       </c>
       <c r="B118" s="69"/>
-      <c r="C118" s="120" t="s">
+      <c r="C118" s="110" t="s">
         <v>111</v>
       </c>
-      <c r="D118" s="120"/>
-      <c r="E118" s="120"/>
-      <c r="F118" s="120"/>
+      <c r="D118" s="110"/>
+      <c r="E118" s="110"/>
+      <c r="F118" s="110"/>
       <c r="G118" s="1"/>
       <c r="H118" s="1"/>
       <c r="I118" s="1"/>
@@ -5383,10 +5402,10 @@
     <row r="122" spans="1:26" ht="15.75" customHeight="1">
       <c r="A122" s="83"/>
       <c r="B122" s="69"/>
-      <c r="C122" s="115" t="s">
+      <c r="C122" s="102" t="s">
         <v>112</v>
       </c>
-      <c r="D122" s="116"/>
+      <c r="D122" s="103"/>
       <c r="E122" s="7"/>
       <c r="F122" s="7"/>
       <c r="G122" s="1"/>
@@ -5495,8 +5514,8 @@
       <c r="Z125" s="4"/>
     </row>
     <row r="126" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A126" s="117"/>
-      <c r="B126" s="91"/>
+      <c r="A126" s="104"/>
+      <c r="B126" s="105"/>
       <c r="C126" s="7"/>
       <c r="D126" s="7"/>
       <c r="E126" s="7"/>
@@ -5523,9 +5542,9 @@
       <c r="Z126" s="4"/>
     </row>
     <row r="127" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A127" s="118"/>
-      <c r="B127" s="91"/>
-      <c r="C127" s="91"/>
+      <c r="A127" s="106"/>
+      <c r="B127" s="105"/>
+      <c r="C127" s="105"/>
       <c r="D127" s="7"/>
       <c r="E127" s="7"/>
       <c r="F127" s="7"/>
@@ -15080,6 +15099,26 @@
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="A50:F50"/>
+    <mergeCell ref="G5:J6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A53:F53"/>
+    <mergeCell ref="A66:F66"/>
+    <mergeCell ref="A67:F67"/>
+    <mergeCell ref="A72:F72"/>
+    <mergeCell ref="A79:F79"/>
     <mergeCell ref="A110:F110"/>
     <mergeCell ref="C122:D122"/>
     <mergeCell ref="A126:B126"/>
@@ -15092,26 +15131,6 @@
     <mergeCell ref="A105:F105"/>
     <mergeCell ref="A106:F106"/>
     <mergeCell ref="C118:F118"/>
-    <mergeCell ref="A53:F53"/>
-    <mergeCell ref="A66:F66"/>
-    <mergeCell ref="A67:F67"/>
-    <mergeCell ref="A72:F72"/>
-    <mergeCell ref="A79:F79"/>
-    <mergeCell ref="A26:F26"/>
-    <mergeCell ref="A35:F35"/>
-    <mergeCell ref="A47:F47"/>
-    <mergeCell ref="A50:F50"/>
-    <mergeCell ref="G5:J6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="F5:F6"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="46" fitToHeight="0" orientation="portrait" r:id="rId1"/>
